--- a/excel/红利成分股汇总.xlsx
+++ b/excel/红利成分股汇总.xlsx
@@ -558,12 +558,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PE(TTM)</t>
+          <t>PE(TTM)(倍)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PB(倍)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">

--- a/excel/红利成分股汇总.xlsx
+++ b/excel/红利成分股汇总.xlsx
@@ -623,19 +623,19 @@
         <v>2.42</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.97</v>
+        <v>4.89</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-1.39</v>
+        <v>-2.2</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17.28</v>
+        <v>17</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>4.46</v>
@@ -687,19 +687,19 @@
         <v>2.35</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>11.35</v>
+        <v>10.92</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4.22</v>
+        <v>-3.28</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>16.97</v>
+        <v>16.33</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>7.4</v>
@@ -751,19 +751,19 @@
         <v>1.9</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>-1.22</v>
+        <v>-3.23</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>13.77</v>
+        <v>13.6</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>4.12</v>
@@ -815,19 +815,19 @@
         <v>7.03</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>15.63</v>
+        <v>15.36</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>-0.45</v>
+        <v>-2.29</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>9.529999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>2386</v>
+        <v>2345</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>6.4</v>
@@ -879,19 +879,19 @@
         <v>4.69</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>10.78</v>
+        <v>10.58</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.47</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>11.43</v>
+        <v>11.21</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>6.22</v>
@@ -943,19 +943,19 @@
         <v>2.14</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>14.56</v>
+        <v>14.34</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>2.1</v>
+        <v>-1.92</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>19.08</v>
+        <v>18.79</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>4.15</v>
@@ -1007,19 +1007,19 @@
         <v>1.74</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>17</v>
+        <v>16.64</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>-2.86</v>
+        <v>-1.94</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>15.59</v>
+        <v>15.26</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>3.88</v>
@@ -1071,19 +1071,19 @@
         <v>1.93</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>8.98</v>
+        <v>8.85</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>-1.1</v>
+        <v>-3.07</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>-2.43</v>
+        <v>-2.4</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>7.8</v>
@@ -1135,19 +1135,19 @@
         <v>1.75</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>5.9</v>
+        <v>5.81</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.68</v>
+        <v>-2.19</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>36.9</v>
+        <v>36.33</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>3.73</v>
@@ -1199,19 +1199,19 @@
         <v>2</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>10.11</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>-2.13</v>
+        <v>-2.59</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>14.84</v>
+        <v>14.35</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>687</v>
+        <v>665</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>3.69</v>
@@ -1263,19 +1263,19 @@
         <v>1.94</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>6.54</v>
+        <v>6.38</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>-1.06</v>
+        <v>-3.33</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>11.56</v>
+        <v>11.28</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>4.59</v>
@@ -1327,19 +1327,19 @@
         <v>4.24</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>1.94</v>
+        <v>-1.47</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>17.14</v>
+        <v>17.13</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>3.15</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1.91</v>
@@ -1391,19 +1391,19 @@
         <v>0.59</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>6.7</v>
+        <v>6.47</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>-0.15</v>
+        <v>-2.71</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>14.57</v>
+        <v>14.07</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>3.28</v>
@@ -1455,19 +1455,19 @@
         <v>0.46</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>11.49</v>
+        <v>11.39</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>-0.78</v>
+        <v>-2.4</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>13.71</v>
+        <v>13.59</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>5.66</v>
@@ -1519,19 +1519,19 @@
         <v>2.03</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>11.31</v>
+        <v>11.58</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>3.01</v>
+        <v>2.03</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>16.86</v>
+        <v>17.26</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>5.34</v>
@@ -1583,16 +1583,16 @@
         <v>1.84</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>-0.37</v>
+        <v>-1.47</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>15.16</v>
+        <v>15.13</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="L17" s="13" t="n">
         <v>70</v>
@@ -1647,19 +1647,19 @@
         <v>1.54</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>22.14</v>
+        <v>22.21</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>-0.27</v>
+        <v>0.5</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>11.81</v>
+        <v>11.85</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>3.61</v>
@@ -1711,19 +1711,19 @@
         <v>1.26</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>5.29</v>
+        <v>5.19</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0.38</v>
+        <v>-1.89</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>9.01</v>
+        <v>8.84</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1232</v>
+        <v>1208</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>3.69</v>
@@ -1775,19 +1775,19 @@
         <v>1.08</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>12.18</v>
+        <v>12</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>-1.69</v>
+        <v>-3.15</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>12.92</v>
+        <v>12.73</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>4.02</v>
@@ -1839,19 +1839,19 @@
         <v>0.89</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9.039999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>11.19</v>
+        <v>11.07</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6.04</v>
@@ -1903,19 +1903,19 @@
         <v>0.48</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>13.01</v>
+        <v>12.95</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>-2.03</v>
+        <v>-1.3</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>14.75</v>
+        <v>14.68</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>3.07</v>
@@ -1967,19 +1967,19 @@
         <v>0.44</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>11.47</v>
+        <v>11.31</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.7</v>
+        <v>-1.91</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>10.04</v>
+        <v>9.9</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>7.08</v>
@@ -2031,19 +2031,19 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>7.93</v>
+        <v>7.82</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0</v>
+        <v>-2.13</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>15.25</v>
+        <v>15.04</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>3.59</v>
@@ -2095,19 +2095,19 @@
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>17.07</v>
+        <v>17.03</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.47</v>
+        <v>-0.76</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>9.960000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>3.97</v>
@@ -2159,19 +2159,19 @@
         <v>0</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>24.35</v>
+        <v>24.51</v>
       </c>
       <c r="K26" s="8" t="n">
         <v>0.89</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>1.89</v>
@@ -2223,19 +2223,19 @@
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>11.07</v>
+        <v>11.02</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>1.47</v>
+        <v>-1.52</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>21.15</v>
+        <v>21.06</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>1.81</v>
@@ -2287,19 +2287,19 @@
         <v>1.57</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.74</v>
+        <v>-1.09</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>10.49</v>
+        <v>10.42</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>5</v>
@@ -2351,19 +2351,19 @@
         <v>1.79</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>10.02</v>
+        <v>9.76</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>2.04</v>
+        <v>-1.51</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>14.9</v>
+        <v>14.51</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>1</v>
@@ -2415,19 +2415,19 @@
         <v>4.68</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>29.28</v>
+        <v>29.94</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>5.78</v>
+        <v>2.92</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>22.38</v>
+        <v>22.88</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>1.16</v>
@@ -2479,13 +2479,13 @@
         <v>1.23</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>10.99</v>
+        <v>10.96</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>3.39</v>
+        <v>-1.44</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>12.29</v>
+        <v>12.26</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>1.25</v>
@@ -2543,19 +2543,19 @@
         <v>4.28</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>389.35</v>
+        <v>392.49</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>13.83</v>
+        <v>13.94</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>5.03</v>
@@ -2607,16 +2607,16 @@
         <v>0.33</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>35.37</v>
+        <v>35.5</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>12.54</v>
+        <v>12.58</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="L33" s="13" t="n">
         <v>81</v>
@@ -2671,19 +2671,19 @@
         <v>0.66</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>7.51</v>
+        <v>7.45</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>-1.18</v>
+        <v>-1.72</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>13.29</v>
+        <v>13.19</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>3.86</v>
@@ -2735,19 +2735,19 @@
         <v>0.65</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>7.71</v>
+        <v>7.62</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>2.39</v>
+        <v>-0.91</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>48.75</v>
+        <v>48.19</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>2.59</v>
@@ -2799,19 +2799,19 @@
         <v>6.95</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>19.91</v>
+        <v>20.18</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>3.27</v>
+        <v>0.95</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>13.66</v>
+        <v>13.85</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="M36" s="8" t="n">
         <v>5.17</v>
@@ -2863,19 +2863,19 @@
         <v>1.19</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>7.33</v>
+        <v>7.36</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.34</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>12.98</v>
+        <v>13.04</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>4.37</v>
@@ -2927,19 +2927,19 @@
         <v>0</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>5.62</v>
+        <v>5.32</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>22.54</v>
+        <v>21.34</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>6.39</v>
+        <v>6.05</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>812</v>
+        <v>768</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>10.14</v>
@@ -2991,19 +2991,19 @@
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>13.54</v>
+        <v>14.12</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>15.89</v>
+        <v>16.57</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>3.13</v>
+        <v>3.27</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>998</v>
+        <v>1041</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0.44</v>
@@ -3055,19 +3055,19 @@
         <v>0</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>8.56</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>4.77</v>
+        <v>2.21</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>22.94</v>
+        <v>23.53</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="M40" s="8" t="n">
         <v>0.7</v>
@@ -3119,19 +3119,19 @@
         <v>1.79</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>9.33</v>
+        <v>9.06</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0.54</v>
+        <v>-1.95</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>10.17</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>5.01</v>
@@ -3183,19 +3183,19 @@
         <v>2.21</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>4.93</v>
+        <v>4.85</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>-1.99</v>
+        <v>-1.42</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>17.04</v>
+        <v>16.77</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="M42" s="8" t="n">
         <v>4.46</v>
@@ -3247,19 +3247,19 @@
         <v>2.31</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>29.09</v>
+        <v>28.3</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-1.36</v>
+        <v>-2.58</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>19.73</v>
+        <v>19.19</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>7118</v>
+        <v>6925</v>
       </c>
       <c r="M43" s="4" t="n">
         <v>3.44</v>
@@ -3311,19 +3311,19 @@
         <v>2.05</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>10.82</v>
+        <v>11.08</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>1.12</v>
+        <v>0.27</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>22.15</v>
+        <v>22.68</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>4.71</v>
+        <v>4.83</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="M44" s="8" t="n">
         <v>2.71</v>
@@ -3375,19 +3375,19 @@
         <v>1.24</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1.2</v>
+        <v>-1.17</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>13.43</v>
+        <v>13.35</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="M45" s="4" t="n">
         <v>4.74</v>
@@ -3439,19 +3439,19 @@
         <v>1.7</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>17.8</v>
+        <v>17.64</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>-0.84</v>
+        <v>-2.6</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>12.64</v>
+        <v>12.53</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>6.4</v>
@@ -3503,19 +3503,19 @@
         <v>0.92</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>14.13</v>
+        <v>13.76</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0</v>
+        <v>-2.41</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14.61</v>
+        <v>14.22</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>4.62</v>
@@ -3567,16 +3567,16 @@
         <v>0.47</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>18.95</v>
+        <v>18.87</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>2.54</v>
+        <v>-2.73</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>15.11</v>
+        <v>15.04</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>36</v>
@@ -3631,16 +3631,16 @@
         <v>0.45</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>-0.27</v>
+        <v>-2.01</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>16.54</v>
+        <v>16.43</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="L49" s="13" t="n">
         <v>82</v>
@@ -3695,19 +3695,19 @@
         <v>2.38</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>20.15</v>
+        <v>19.89</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.55</v>
+        <v>-2.26</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>13.51</v>
+        <v>13.34</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M50" s="8" t="n">
         <v>2.43</v>
@@ -3759,19 +3759,19 @@
         <v>1.91</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>30.96</v>
+        <v>30.72</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>-1.96</v>
+        <v>-1.54</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>11.42</v>
+        <v>11.33</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>3.39</v>
@@ -3823,19 +3823,19 @@
         <v>1.39</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.34</v>
+        <v>-2.33</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>12.01</v>
+        <v>11.93</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M52" s="8" t="n">
         <v>4.07</v>
@@ -3887,19 +3887,19 @@
         <v>0.99</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>11.04</v>
+        <v>10.76</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>5.38</v>
@@ -3951,19 +3951,19 @@
         <v>0.86</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.21</v>
+        <v>-1.65</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>9.51</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K54" s="8" t="n">
         <v>1.15</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="M54" s="8" t="n">
         <v>4.78</v>
@@ -4015,19 +4015,19 @@
         <v>0.65</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>-0.29</v>
+        <v>0.1</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>12.29</v>
+        <v>12.06</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>3.92</v>
@@ -4079,13 +4079,13 @@
         <v>0.62</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>10.87</v>
+        <v>10.86</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>-0.82</v>
+        <v>-1.9</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>10.58</v>
+        <v>10.57</v>
       </c>
       <c r="K56" s="8" t="n">
         <v>1.12</v>
@@ -4143,19 +4143,19 @@
         <v>2.17</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>12.55</v>
+        <v>12.81</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>27.11</v>
+        <v>27.67</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>2.31</v>
+        <v>2.51</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>5.98</v>
@@ -4207,19 +4207,19 @@
         <v>0.62</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.24</v>
+        <v>-1.43</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M58" s="8" t="n">
         <v>2.56</v>
@@ -4271,10 +4271,10 @@
         <v>4.78</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>54.62</v>
+        <v>54.6</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>-1.12</v>
+        <v>-1.44</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>19.75</v>
@@ -4335,19 +4335,19 @@
         <v>0.78</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>16.12</v>
+        <v>15.85</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>1.51</v>
+        <v>-0.31</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>19.69</v>
+        <v>19.36</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M60" s="8" t="n">
         <v>1.92</v>
@@ -4399,19 +4399,19 @@
         <v>2.62</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>26.39</v>
+        <v>25.98</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>0.5</v>
+        <v>-1.44</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>18.44</v>
+        <v>18.15</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>5.23</v>
@@ -4463,19 +4463,19 @@
         <v>1.07</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>25.81</v>
+        <v>25.75</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>-0.42</v>
+        <v>-1.57</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>13.11</v>
+        <v>13.07</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M62" s="8" t="n">
         <v>4.03</v>
@@ -4527,19 +4527,19 @@
         <v>1.03</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>18.85</v>
+        <v>18.59</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>-1.46</v>
+        <v>0.49</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>16.69</v>
+        <v>16.46</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>4.4</v>
@@ -4591,19 +4591,19 @@
         <v>0.8</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>23</v>
+        <v>22.82</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>-2.04</v>
+        <v>-1.17</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>16.53</v>
+        <v>16.4</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M64" s="8" t="n">
         <v>4.78</v>
@@ -4655,19 +4655,19 @@
         <v>0.27</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>22.73</v>
+        <v>22.44</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>0.13</v>
+        <v>-1.19</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>15.94</v>
+        <v>15.74</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>3.08</v>
@@ -4719,19 +4719,19 @@
         <v>0.15</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>31.13</v>
+        <v>30.82</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>0.39</v>
+        <v>-0.64</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>14.08</v>
+        <v>13.94</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M66" s="8" t="n">
         <v>4.59</v>
@@ -4783,19 +4783,19 @@
         <v>1.93</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>26.84</v>
+        <v>26.38</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>-0.33</v>
+        <v>-1.75</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>14.24</v>
+        <v>13.99</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="M67" s="4" t="n">
         <v>6.48</v>
@@ -4847,19 +4847,19 @@
         <v>0.41</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>13.52</v>
+        <v>13.43</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>-1.02</v>
+        <v>-1.68</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>-38.58</v>
+        <v>-38.32</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M68" s="8" t="n">
         <v>1.48</v>
@@ -4911,19 +4911,19 @@
         <v>3.69</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>111.2</v>
+        <v>108.62</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>-3.77</v>
+        <v>2.59</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>20.72</v>
+        <v>20.24</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>6.7</v>
+        <v>6.54</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>0.9</v>
@@ -4975,19 +4975,19 @@
         <v>3.51</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>38.68</v>
+        <v>39.1</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>-0.28</v>
+        <v>0.13</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>12.89</v>
+        <v>13.03</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M70" s="8" t="n">
         <v>4.54</v>
@@ -5039,19 +5039,19 @@
         <v>3.01</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>46.25</v>
+        <v>46.82</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>26.53</v>
+        <v>26.86</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>1.08</v>
@@ -5103,19 +5103,19 @@
         <v>2.14</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>52.86</v>
+        <v>51.7</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>0.21</v>
+        <v>-1.13</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>17.94</v>
+        <v>17.55</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>943</v>
+        <v>922</v>
       </c>
       <c r="M72" s="8" t="n">
         <v>2.99</v>
@@ -5167,19 +5167,19 @@
         <v>1.66</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>57.5</v>
+        <v>58.16</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>54.84</v>
+        <v>55.81</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0.26</v>
@@ -5234,7 +5234,7 @@
         <v>43.2</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>-2.28</v>
+        <v>1.17</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>27.81</v>
@@ -5295,19 +5295,19 @@
         <v>1.38</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>22.28</v>
+        <v>21.89</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>0.36</v>
+        <v>-1.35</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>12.3</v>
+        <v>12.08</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>3.82</v>
@@ -5359,19 +5359,19 @@
         <v>1.15</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>42.48</v>
+        <v>42.33</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>20.07</v>
+        <v>20</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M76" s="8" t="n">
         <v>4</v>
@@ -5423,19 +5423,19 @@
         <v>0.96</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>0</v>
+        <v>-1.75</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>12.87</v>
+        <v>12.64</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>3.88</v>
@@ -5487,19 +5487,19 @@
         <v>0.9</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>22.79</v>
+        <v>22.95</v>
       </c>
       <c r="K78" s="8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M78" s="8" t="n">
         <v>3.46</v>
@@ -5551,19 +5551,19 @@
         <v>0.89</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>15.77</v>
+        <v>15.59</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>0.83</v>
+        <v>-1.52</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>9.539999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>4.31</v>
@@ -5615,19 +5615,19 @@
         <v>0.87</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>33.11</v>
+        <v>33.56</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>-1.02</v>
+        <v>-1.79</v>
       </c>
       <c r="J80" s="8" t="n">
-        <v>18.29</v>
+        <v>18.54</v>
       </c>
       <c r="K80" s="8" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M80" s="8" t="n">
         <v>3.96</v>
@@ -5679,19 +5679,19 @@
         <v>0.84</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>8.57</v>
+        <v>8.68</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>21.22</v>
+        <v>21.49</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>3.5</v>
@@ -5743,19 +5743,19 @@
         <v>0.67</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>47.87</v>
+        <v>46.89</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>-1.81</v>
+        <v>-2.21</v>
       </c>
       <c r="J82" s="8" t="n">
-        <v>23.15</v>
+        <v>22.68</v>
       </c>
       <c r="K82" s="8" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="M82" s="8" t="n">
         <v>2.51</v>
@@ -5807,19 +5807,19 @@
         <v>0.65</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>6.47</v>
+        <v>6.88</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.43</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>13.85</v>
+        <v>14.73</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>5.41</v>
@@ -5871,19 +5871,19 @@
         <v>0.37</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>158.88</v>
+        <v>154.27</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>-1.7</v>
+        <v>-1.67</v>
       </c>
       <c r="J84" s="8" t="n">
-        <v>24.58</v>
+        <v>23.87</v>
       </c>
       <c r="K84" s="8" t="n">
-        <v>4.99</v>
+        <v>4.85</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>1926</v>
+        <v>1870</v>
       </c>
       <c r="M84" s="8" t="n">
         <v>1.83</v>
@@ -5935,19 +5935,19 @@
         <v>0.19</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>9.74</v>
+        <v>9.6</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>-0.1</v>
+        <v>-2.24</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>18.19</v>
+        <v>17.93</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>3.08</v>
@@ -5999,19 +5999,19 @@
         <v>0.15</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>47.1</v>
+        <v>48.8</v>
       </c>
       <c r="I86" s="8" t="n">
-        <v>4.02</v>
+        <v>4.43</v>
       </c>
       <c r="J86" s="8" t="n">
-        <v>27.1</v>
+        <v>28.08</v>
       </c>
       <c r="K86" s="8" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M86" s="8" t="n">
         <v>2.3</v>
@@ -6063,13 +6063,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>21.54</v>
+        <v>21.53</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>0.37</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>18.54</v>
+        <v>18.53</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>2.21</v>
@@ -6127,19 +6127,19 @@
         <v>0</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>10.25</v>
+        <v>10.19</v>
       </c>
       <c r="I88" s="8" t="n">
-        <v>0.1</v>
+        <v>-0.68</v>
       </c>
       <c r="J88" s="8" t="n">
-        <v>14.26</v>
+        <v>14.18</v>
       </c>
       <c r="K88" s="8" t="n">
         <v>1.23</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M88" s="8" t="n">
         <v>2.15</v>
@@ -6191,19 +6191,19 @@
         <v>1.13</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>-0.47</v>
+        <v>-1.43</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>15.99</v>
+        <v>15.49</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>702</v>
+        <v>680</v>
       </c>
       <c r="M89" s="12" t="n">
         <v>3.91</v>
@@ -6255,19 +6255,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>10.01</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I90" s="8" t="n">
-        <v>0.5</v>
+        <v>-2.86</v>
       </c>
       <c r="J90" s="8" t="n">
-        <v>32.97</v>
+        <v>32.48</v>
       </c>
       <c r="K90" s="8" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M90" s="8" t="n">
         <v>5</v>
@@ -6319,19 +6319,19 @@
         <v>0.59</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>21.22</v>
+        <v>20.7</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>0.09</v>
+        <v>-2.17</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>13.02</v>
+        <v>12.7</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M91" s="12" t="n">
         <v>0.75</v>
@@ -6383,19 +6383,19 @@
         <v>1.78</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>11.18</v>
+        <v>10.83</v>
       </c>
       <c r="I92" s="8" t="n">
-        <v>-0.09</v>
+        <v>-2.78</v>
       </c>
       <c r="J92" s="8" t="n">
-        <v>10.41</v>
+        <v>10.09</v>
       </c>
       <c r="K92" s="8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M92" s="8" t="n">
         <v>3.71</v>
@@ -6447,19 +6447,19 @@
         <v>2.54</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>29.87</v>
+        <v>29.4</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>-1.65</v>
+        <v>-0.51</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>10.29</v>
+        <v>10.13</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>4.69</v>
@@ -6511,19 +6511,19 @@
         <v>1.69</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>5.76</v>
+        <v>5.87</v>
       </c>
       <c r="I94" s="8" t="n">
-        <v>1.23</v>
+        <v>-0.34</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>27.9</v>
+        <v>28.43</v>
       </c>
       <c r="K94" s="8" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M94" s="8" t="n">
         <v>5.21</v>
@@ -6575,19 +6575,19 @@
         <v>1.47</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>0.49</v>
+        <v>-2.2</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>9.58</v>
+        <v>9.43</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M95" s="12" t="n">
         <v>5.27</v>
@@ -6639,19 +6639,19 @@
         <v>0.93</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="I96" s="8" t="n">
-        <v>-0.21</v>
+        <v>-0.84</v>
       </c>
       <c r="J96" s="8" t="n">
-        <v>13.21</v>
+        <v>13.13</v>
       </c>
       <c r="K96" s="8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M96" s="8" t="n">
         <v>8.02</v>
@@ -6703,19 +6703,19 @@
         <v>2.32</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>80.62</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>27.03</v>
+        <v>27.14</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>7.17</v>
+        <v>7.2</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>3.1</v>
@@ -6767,19 +6767,19 @@
         <v>0.98</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>16.38</v>
+        <v>16.52</v>
       </c>
       <c r="I98" s="8" t="n">
-        <v>-2.38</v>
+        <v>-0.9</v>
       </c>
       <c r="J98" s="8" t="n">
-        <v>52.39</v>
+        <v>52.84</v>
       </c>
       <c r="K98" s="8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M98" s="8" t="n">
         <v>0.61</v>
@@ -6831,19 +6831,19 @@
         <v>0.78</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>7.01</v>
+        <v>6.95</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>-0.85</v>
+        <v>-1.84</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>11.27</v>
+        <v>11.18</v>
       </c>
       <c r="K99" s="12" t="n">
         <v>0.93</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M99" s="12" t="n">
         <v>6.42</v>
@@ -6895,19 +6895,19 @@
         <v>2.67</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>23.29</v>
+        <v>23.09</v>
       </c>
       <c r="I100" s="8" t="n">
-        <v>-2.47</v>
+        <v>0.79</v>
       </c>
       <c r="J100" s="8" t="n">
-        <v>13.58</v>
+        <v>13.47</v>
       </c>
       <c r="K100" s="8" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>1708</v>
+        <v>1693</v>
       </c>
       <c r="M100" s="8" t="n">
         <v>3.01</v>
@@ -6959,19 +6959,19 @@
         <v>2.54</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>25.39</v>
+        <v>25.2</v>
       </c>
       <c r="I101" s="12" t="n">
-        <v>0.08</v>
+        <v>-0.32</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>14.6</v>
+        <v>14.49</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="M101" s="12" t="n">
         <v>1.97</v>
@@ -7023,19 +7023,19 @@
         <v>1.24</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>12.64</v>
+        <v>12.8</v>
       </c>
       <c r="I102" s="8" t="n">
-        <v>-0.71</v>
+        <v>-2.29</v>
       </c>
       <c r="J102" s="8" t="n">
-        <v>25.83</v>
+        <v>26.16</v>
       </c>
       <c r="K102" s="8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M102" s="8" t="n">
         <v>1.58</v>
@@ -7087,19 +7087,19 @@
         <v>0.46</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>74.51000000000001</v>
+        <v>73.64</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>-2.68</v>
+        <v>-2.2</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>17.72</v>
+        <v>17.51</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>2333</v>
+        <v>2305</v>
       </c>
       <c r="M103" s="12" t="n">
         <v>1.68</v>
@@ -7151,16 +7151,16 @@
         <v>0.05</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>19.39</v>
+        <v>19.82</v>
       </c>
       <c r="I104" s="8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="J104" s="8" t="n">
-        <v>13.51</v>
+        <v>13.81</v>
       </c>
       <c r="K104" s="8" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="L104" s="9" t="n">
         <v>32</v>
@@ -7215,19 +7215,19 @@
         <v>0</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>30.01</v>
+        <v>30.11</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>-1.67</v>
+        <v>-1.18</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>13.74</v>
+        <v>13.79</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="M105" s="12" t="n">
         <v>3.33</v>
@@ -7279,19 +7279,19 @@
         <v>10.26</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>42.3</v>
+        <v>40.52</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>-0.4</v>
+        <v>-1.07</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>8.119999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>2369</v>
+        <v>2270</v>
       </c>
       <c r="M106" s="4" t="n">
         <v>7.09</v>
@@ -7343,19 +7343,19 @@
         <v>1.78</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>87.59999999999999</v>
+        <v>85.14</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>-1.52</v>
+        <v>-0.88</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>15.12</v>
+        <v>14.69</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>6681</v>
+        <v>6494</v>
       </c>
       <c r="M107" s="4" t="n">
         <v>4.91</v>
@@ -7407,19 +7407,19 @@
         <v>1.69</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>43.59</v>
+        <v>42.08</v>
       </c>
       <c r="I108" s="8" t="n">
-        <v>-3</v>
+        <v>-1.36</v>
       </c>
       <c r="J108" s="8" t="n">
-        <v>17.22</v>
+        <v>16.63</v>
       </c>
       <c r="K108" s="8" t="n">
-        <v>6.91</v>
+        <v>6.67</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="M108" s="8" t="n">
         <v>6.03</v>
@@ -7471,19 +7471,19 @@
         <v>1.28</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>15.94</v>
+        <v>15.81</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>-3.63</v>
+        <v>-1.62</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>12.32</v>
+        <v>12.22</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M109" s="12" t="n">
         <v>6.27</v>
@@ -7535,19 +7535,19 @@
         <v>1</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>23.19</v>
+        <v>22.49</v>
       </c>
       <c r="I110" s="8" t="n">
-        <v>-0.34</v>
+        <v>-1.88</v>
       </c>
       <c r="J110" s="8" t="n">
-        <v>11.62</v>
+        <v>11.27</v>
       </c>
       <c r="K110" s="8" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>2175</v>
+        <v>2109</v>
       </c>
       <c r="M110" s="8" t="n">
         <v>1.16</v>
@@ -7599,19 +7599,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>4.98</v>
+        <v>5.01</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>1.43</v>
+        <v>-0.4</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>17.15</v>
+        <v>17.26</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M111" s="12" t="n">
         <v>4.22</v>
@@ -7663,19 +7663,19 @@
         <v>1.91</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>-0.42</v>
+        <v>-2.52</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>5.12</v>
+        <v>5.05</v>
       </c>
       <c r="K112" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>1942</v>
+        <v>1917</v>
       </c>
       <c r="M112" s="4" t="n">
         <v>5.78</v>
@@ -7727,19 +7727,19 @@
         <v>2.1</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>0.42</v>
+        <v>-2.29</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>5.3</v>
+        <v>5.21</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M113" s="12" t="n">
         <v>5.65</v>
@@ -7791,19 +7791,19 @@
         <v>2.41</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>9.029999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I114" s="8" t="n">
-        <v>0.89</v>
+        <v>-1.36</v>
       </c>
       <c r="J114" s="8" t="n">
-        <v>11.19</v>
+        <v>10.78</v>
       </c>
       <c r="K114" s="8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>785</v>
+        <v>757</v>
       </c>
       <c r="M114" s="8" t="n">
         <v>5.45</v>
@@ -7855,19 +7855,19 @@
         <v>1.93</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>5.65</v>
+        <v>5.59</v>
       </c>
       <c r="I115" s="12" t="n">
-        <v>1.44</v>
+        <v>-2.61</v>
       </c>
       <c r="J115" s="12" t="n">
-        <v>8.15</v>
+        <v>8.06</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M115" s="12" t="n">
         <v>7.43</v>
@@ -7919,19 +7919,19 @@
         <v>1.42</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>6.41</v>
+        <v>6.25</v>
       </c>
       <c r="I116" s="8" t="n">
-        <v>0.47</v>
+        <v>-2.5</v>
       </c>
       <c r="J116" s="8" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="K116" s="8" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="M116" s="8" t="n">
         <v>4.68</v>
@@ -7983,19 +7983,19 @@
         <v>1.66</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>5.23</v>
+        <v>5.19</v>
       </c>
       <c r="I117" s="12" t="n">
-        <v>1.36</v>
+        <v>-1.89</v>
       </c>
       <c r="J117" s="12" t="n">
-        <v>17.12</v>
+        <v>16.99</v>
       </c>
       <c r="K117" s="12" t="n">
         <v>0.9</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M117" s="12" t="n">
         <v>4.02</v>
@@ -8047,19 +8047,19 @@
         <v>1.38</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>7.97</v>
+        <v>7.9</v>
       </c>
       <c r="I118" s="8" t="n">
-        <v>-0.75</v>
+        <v>-2.59</v>
       </c>
       <c r="J118" s="8" t="n">
-        <v>7.87</v>
+        <v>7.8</v>
       </c>
       <c r="K118" s="8" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M118" s="8" t="n">
         <v>6.02</v>
@@ -8111,19 +8111,19 @@
         <v>1.16</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>0.22</v>
+        <v>-2.38</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>5.33</v>
+        <v>5.22</v>
       </c>
       <c r="K119" s="12" t="n">
         <v>0.35</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>1131</v>
+        <v>1109</v>
       </c>
       <c r="M119" s="12" t="n">
         <v>3.64</v>
@@ -8175,19 +8175,19 @@
         <v>1.01</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="I120" s="8" t="n">
-        <v>-0.16</v>
+        <v>-2.36</v>
       </c>
       <c r="J120" s="8" t="n">
-        <v>7.67</v>
+        <v>7.51</v>
       </c>
       <c r="K120" s="8" t="n">
         <v>0.35</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>1026</v>
+        <v>1005</v>
       </c>
       <c r="M120" s="8" t="n">
         <v>3.09</v>
@@ -8239,19 +8239,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="I121" s="12" t="n">
-        <v>-0.82</v>
+        <v>-2.41</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>9.93</v>
+        <v>10.01</v>
       </c>
       <c r="K121" s="12" t="n">
         <v>0.61</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M121" s="12" t="n">
         <v>3.05</v>
@@ -8303,19 +8303,19 @@
         <v>1.87</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="I122" s="8" t="n">
-        <v>-4.09</v>
+        <v>-2.36</v>
       </c>
       <c r="J122" s="8" t="n">
-        <v>21.06</v>
+        <v>20.89</v>
       </c>
       <c r="K122" s="8" t="n">
         <v>0.75</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M122" s="8" t="n">
         <v>6.4</v>
@@ -8367,19 +8367,19 @@
         <v>5.27</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>13.22</v>
+        <v>13.29</v>
       </c>
       <c r="I123" s="12" t="n">
-        <v>5.42</v>
+        <v>3.42</v>
       </c>
       <c r="J123" s="12" t="n">
-        <v>21.74</v>
+        <v>21.85</v>
       </c>
       <c r="K123" s="12" t="n">
         <v>1.49</v>
       </c>
       <c r="L123" s="13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M123" s="12" t="n">
         <v>3.63</v>
@@ -8431,19 +8431,19 @@
         <v>1.5</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>18.56</v>
+        <v>17.8</v>
       </c>
       <c r="I124" s="8" t="n">
-        <v>-0.43</v>
+        <v>-2.79</v>
       </c>
       <c r="J124" s="8" t="n">
-        <v>12.61</v>
+        <v>12.09</v>
       </c>
       <c r="K124" s="8" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>979</v>
+        <v>939</v>
       </c>
       <c r="M124" s="8" t="n">
         <v>4.58</v>
@@ -8495,19 +8495,19 @@
         <v>0.86</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>13.18</v>
+        <v>12.88</v>
       </c>
       <c r="I125" s="12" t="n">
-        <v>-2.95</v>
+        <v>-4.31</v>
       </c>
       <c r="J125" s="12" t="n">
-        <v>14.6</v>
+        <v>14.27</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="L125" s="13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M125" s="12" t="n">
         <v>4.49</v>
@@ -8559,19 +8559,19 @@
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>22.3</v>
+        <v>21.46</v>
       </c>
       <c r="I126" s="8" t="n">
-        <v>-0.76</v>
+        <v>1.23</v>
       </c>
       <c r="J126" s="8" t="n">
-        <v>14.27</v>
+        <v>13.73</v>
       </c>
       <c r="K126" s="8" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="M126" s="8" t="n">
         <v>2.47</v>
@@ -8623,19 +8623,19 @@
         <v>0.96</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>7.91</v>
+        <v>7.8</v>
       </c>
       <c r="I127" s="12" t="n">
-        <v>0.25</v>
+        <v>-2.13</v>
       </c>
       <c r="J127" s="12" t="n">
-        <v>7.75</v>
+        <v>7.65</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M127" s="12" t="n">
         <v>4.05</v>
@@ -8687,19 +8687,19 @@
         <v>2.18</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>19.2</v>
+        <v>18.6</v>
       </c>
       <c r="I128" s="8" t="n">
-        <v>2.13</v>
+        <v>-2.05</v>
       </c>
       <c r="J128" s="8" t="n">
-        <v>16.17</v>
+        <v>15.66</v>
       </c>
       <c r="K128" s="8" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M128" s="8" t="n">
         <v>5.57</v>
@@ -8751,13 +8751,13 @@
         <v>0.42</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="I129" s="12" t="n">
-        <v>2.13</v>
+        <v>-2.32</v>
       </c>
       <c r="J129" s="12" t="n">
-        <v>39.29</v>
+        <v>39.41</v>
       </c>
       <c r="K129" s="12" t="n">
         <v>0.5600000000000001</v>
@@ -8815,19 +8815,19 @@
         <v>1.1</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>5.28</v>
+        <v>5.11</v>
       </c>
       <c r="I130" s="8" t="n">
-        <v>-0.38</v>
+        <v>-2.67</v>
       </c>
       <c r="J130" s="8" t="n">
-        <v>251.07</v>
+        <v>242.99</v>
       </c>
       <c r="K130" s="8" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>632</v>
+        <v>612</v>
       </c>
       <c r="M130" s="8" t="n">
         <v>3.88</v>
@@ -8879,19 +8879,19 @@
         <v>2.41</v>
       </c>
       <c r="H131" s="12" t="n">
-        <v>38.44</v>
+        <v>38.21</v>
       </c>
       <c r="I131" s="12" t="n">
-        <v>4.88</v>
+        <v>1.89</v>
       </c>
       <c r="J131" s="12" t="n">
-        <v>15.41</v>
+        <v>15.32</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="M131" s="12" t="n">
         <v>0.26</v>
@@ -8943,19 +8943,19 @@
         <v>2.31</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>13.2</v>
+        <v>13.16</v>
       </c>
       <c r="I132" s="8" t="n">
-        <v>0.53</v>
+        <v>1.46</v>
       </c>
       <c r="J132" s="8" t="n">
-        <v>10.22</v>
+        <v>10.19</v>
       </c>
       <c r="K132" s="8" t="n">
         <v>2.02</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M132" s="8" t="n">
         <v>4.17</v>
@@ -9007,19 +9007,19 @@
         <v>2</v>
       </c>
       <c r="H133" s="12" t="n">
-        <v>23.38</v>
+        <v>22.56</v>
       </c>
       <c r="I133" s="12" t="n">
-        <v>0.91</v>
+        <v>-1.18</v>
       </c>
       <c r="J133" s="12" t="n">
-        <v>17.65</v>
+        <v>17.04</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="M133" s="12" t="n">
         <v>2.05</v>
@@ -9071,19 +9071,19 @@
         <v>2.52</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>26.07</v>
+        <v>25.69</v>
       </c>
       <c r="I134" s="8" t="n">
-        <v>-1.1</v>
+        <v>1.26</v>
       </c>
       <c r="J134" s="8" t="n">
-        <v>8.52</v>
+        <v>8.4</v>
       </c>
       <c r="K134" s="8" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="M134" s="8" t="n">
         <v>3.07</v>
@@ -9135,19 +9135,19 @@
         <v>6.45</v>
       </c>
       <c r="H135" s="12" t="n">
-        <v>9.57</v>
+        <v>9.58</v>
       </c>
       <c r="I135" s="12" t="n">
-        <v>0.21</v>
+        <v>1.05</v>
       </c>
       <c r="J135" s="12" t="n">
-        <v>11.19</v>
+        <v>11.21</v>
       </c>
       <c r="K135" s="12" t="n">
         <v>2.04</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="M135" s="12" t="n">
         <v>2.7</v>
@@ -9199,19 +9199,19 @@
         <v>1.25</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>45.12</v>
+        <v>46.84</v>
       </c>
       <c r="I136" s="8" t="n">
-        <v>-1.46</v>
+        <v>1.06</v>
       </c>
       <c r="J136" s="8" t="n">
-        <v>25.36</v>
+        <v>26.33</v>
       </c>
       <c r="K136" s="8" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M136" s="8" t="n">
         <v>1.55</v>
@@ -9263,19 +9263,19 @@
         <v>0.34</v>
       </c>
       <c r="H137" s="12" t="n">
-        <v>5.01</v>
+        <v>5.22</v>
       </c>
       <c r="I137" s="12" t="n">
-        <v>0.8</v>
+        <v>-0.19</v>
       </c>
       <c r="J137" s="12" t="n">
-        <v>16.82</v>
+        <v>17.53</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M137" s="12" t="n">
         <v>3.59</v>
@@ -9327,19 +9327,19 @@
         <v>2.8</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>40.1</v>
+        <v>39.34</v>
       </c>
       <c r="I138" s="8" t="n">
-        <v>3.06</v>
+        <v>0.2</v>
       </c>
       <c r="J138" s="8" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="K138" s="8" t="n">
-        <v>8.9</v>
+        <v>8.73</v>
       </c>
       <c r="L138" s="9" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M138" s="8" t="n">
         <v>1.25</v>
@@ -9391,19 +9391,19 @@
         <v>2.65</v>
       </c>
       <c r="H139" s="12" t="n">
-        <v>20.99</v>
+        <v>21.95</v>
       </c>
       <c r="I139" s="12" t="n">
-        <v>2.39</v>
+        <v>3.54</v>
       </c>
       <c r="J139" s="12" t="n">
-        <v>19.28</v>
+        <v>20.16</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="M139" s="12" t="n">
         <v>3.81</v>
@@ -9455,19 +9455,19 @@
         <v>2.5</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>11.09</v>
+        <v>11.38</v>
       </c>
       <c r="I140" s="8" t="n">
-        <v>1.19</v>
+        <v>2.89</v>
       </c>
       <c r="J140" s="8" t="n">
-        <v>9.31</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K140" s="8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="L140" s="9" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M140" s="8" t="n">
         <v>2.93</v>
@@ -9519,19 +9519,19 @@
         <v>0.14</v>
       </c>
       <c r="H141" s="12" t="n">
-        <v>16.08</v>
+        <v>17.11</v>
       </c>
       <c r="I141" s="12" t="n">
-        <v>2.94</v>
+        <v>0.59</v>
       </c>
       <c r="J141" s="12" t="n">
-        <v>24.07</v>
+        <v>25.61</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>4.94</v>
+        <v>5.25</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="M141" s="12" t="n">
         <v>2.67</v>
@@ -9583,19 +9583,19 @@
         <v>1.43</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>16.15</v>
+        <v>15.99</v>
       </c>
       <c r="I142" s="8" t="n">
-        <v>-1.04</v>
+        <v>-2.26</v>
       </c>
       <c r="J142" s="8" t="n">
-        <v>7.04</v>
+        <v>6.97</v>
       </c>
       <c r="K142" s="8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="L142" s="9" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="M142" s="8" t="n">
         <v>7.74</v>
@@ -9647,19 +9647,19 @@
         <v>1.41</v>
       </c>
       <c r="H143" s="12" t="n">
-        <v>17.4</v>
+        <v>17.09</v>
       </c>
       <c r="I143" s="12" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="J143" s="12" t="n">
-        <v>9.57</v>
+        <v>9.4</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M143" s="12" t="n">
         <v>4.02</v>
@@ -9711,19 +9711,19 @@
         <v>1.64</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>-0.4</v>
+        <v>-1.21</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>14.14</v>
+        <v>14.08</v>
       </c>
       <c r="K144" s="4" t="n">
         <v>0.82</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M144" s="4" t="n">
         <v>6.09</v>
@@ -9775,19 +9775,19 @@
         <v>1.62</v>
       </c>
       <c r="H145" s="12" t="n">
-        <v>7.6</v>
+        <v>7.34</v>
       </c>
       <c r="I145" s="12" t="n">
-        <v>-1.68</v>
+        <v>-2.65</v>
       </c>
       <c r="J145" s="12" t="n">
-        <v>15.17</v>
+        <v>14.65</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="L145" s="13" t="n">
-        <v>657</v>
+        <v>635</v>
       </c>
       <c r="M145" s="12" t="n">
         <v>5.26</v>
@@ -9839,19 +9839,19 @@
         <v>1.39</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="I146" s="8" t="n">
-        <v>-1.35</v>
+        <v>-0.98</v>
       </c>
       <c r="J146" s="8" t="n">
-        <v>14.84</v>
+        <v>14.73</v>
       </c>
       <c r="K146" s="8" t="n">
         <v>1.17</v>
       </c>
       <c r="L146" s="9" t="n">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="M146" s="8" t="n">
         <v>3.33</v>
@@ -9903,19 +9903,19 @@
         <v>1.1</v>
       </c>
       <c r="H147" s="12" t="n">
-        <v>6.16</v>
+        <v>6.03</v>
       </c>
       <c r="I147" s="12" t="n">
-        <v>-2.69</v>
+        <v>-3.05</v>
       </c>
       <c r="J147" s="12" t="n">
-        <v>13.09</v>
+        <v>12.81</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="L147" s="13" t="n">
-        <v>1768</v>
+        <v>1731</v>
       </c>
       <c r="M147" s="12" t="n">
         <v>5.19</v>
@@ -9967,16 +9967,16 @@
         <v>2.39</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>9.6</v>
+        <v>9.56</v>
       </c>
       <c r="I148" s="8" t="n">
-        <v>1.69</v>
+        <v>-0.62</v>
       </c>
       <c r="J148" s="8" t="n">
-        <v>23.91</v>
+        <v>23.81</v>
       </c>
       <c r="K148" s="8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="L148" s="9" t="n">
         <v>165</v>
@@ -10031,19 +10031,19 @@
         <v>3.82</v>
       </c>
       <c r="H149" s="12" t="n">
-        <v>20.55</v>
+        <v>19.53</v>
       </c>
       <c r="I149" s="12" t="n">
-        <v>-1.34</v>
+        <v>-3.32</v>
       </c>
       <c r="J149" s="12" t="n">
-        <v>22.44</v>
+        <v>21.33</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="L149" s="13" t="n">
-        <v>1890</v>
+        <v>1796</v>
       </c>
       <c r="M149" s="12" t="n">
         <v>2.38</v>
@@ -10095,19 +10095,19 @@
         <v>1.57</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>45.58</v>
+        <v>50.4</v>
       </c>
       <c r="I150" s="8" t="n">
-        <v>2.38</v>
+        <v>3.79</v>
       </c>
       <c r="J150" s="8" t="n">
-        <v>20.99</v>
+        <v>23.21</v>
       </c>
       <c r="K150" s="8" t="n">
-        <v>8.41</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L150" s="9" t="n">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="M150" s="8" t="n">
         <v>3.53</v>
@@ -10159,19 +10159,19 @@
         <v>1.11</v>
       </c>
       <c r="H151" s="12" t="n">
-        <v>15.83</v>
+        <v>15.62</v>
       </c>
       <c r="I151" s="12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.51</v>
       </c>
       <c r="J151" s="12" t="n">
-        <v>19.22</v>
+        <v>18.96</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>5.8</v>
+        <v>5.72</v>
       </c>
       <c r="L151" s="13" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M151" s="12" t="n">
         <v>4.42</v>
@@ -10223,19 +10223,19 @@
         <v>1.04</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>278</v>
+        <v>301.3</v>
       </c>
       <c r="I152" s="8" t="n">
-        <v>9.27</v>
+        <v>12.61</v>
       </c>
       <c r="J152" s="8" t="n">
-        <v>77.62</v>
+        <v>84.13</v>
       </c>
       <c r="K152" s="8" t="n">
-        <v>11.39</v>
+        <v>12.34</v>
       </c>
       <c r="L152" s="9" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="M152" s="8" t="n">
         <v>0.32</v>
@@ -10287,19 +10287,19 @@
         <v>0.29</v>
       </c>
       <c r="H153" s="12" t="n">
-        <v>17.77</v>
+        <v>17.87</v>
       </c>
       <c r="I153" s="12" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="J153" s="12" t="n">
-        <v>17.19</v>
+        <v>17.29</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L153" s="13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M153" s="12" t="n">
         <v>5.06</v>
@@ -10351,19 +10351,19 @@
         <v>0.24</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="I154" s="8" t="n">
-        <v>1.28</v>
+        <v>0.15</v>
       </c>
       <c r="J154" s="8" t="n">
-        <v>19.33</v>
+        <v>19.62</v>
       </c>
       <c r="K154" s="8" t="n">
-        <v>6.12</v>
+        <v>6.21</v>
       </c>
       <c r="L154" s="9" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M154" s="8" t="n">
         <v>3.33</v>
@@ -10415,19 +10415,19 @@
         <v>0.06</v>
       </c>
       <c r="H155" s="12" t="n">
-        <v>19.01</v>
+        <v>19.6</v>
       </c>
       <c r="I155" s="12" t="n">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="J155" s="12" t="n">
-        <v>43.19</v>
+        <v>44.53</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>9.130000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="L155" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M155" s="12" t="n">
         <v>1.58</v>
@@ -10479,19 +10479,19 @@
         <v>0</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="I156" s="8" t="n">
-        <v>-0.34</v>
+        <v>-1.71</v>
       </c>
       <c r="J156" s="8" t="n">
-        <v>-410.05</v>
+        <v>-406.74</v>
       </c>
       <c r="K156" s="8" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L156" s="9" t="n">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="M156" s="8" t="n">
         <v>0</v>
@@ -10543,19 +10543,19 @@
         <v>1.2</v>
       </c>
       <c r="H157" s="12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="I157" s="12" t="n">
-        <v>-2.5</v>
+        <v>-3.43</v>
       </c>
       <c r="J157" s="12" t="n">
-        <v>15.92</v>
+        <v>15</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="L157" s="13" t="n">
-        <v>1049</v>
+        <v>988</v>
       </c>
       <c r="M157" s="12" t="n">
         <v>2.23</v>
@@ -10607,19 +10607,19 @@
         <v>1.76</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>16.86</v>
+        <v>16.18</v>
       </c>
       <c r="I158" s="8" t="n">
-        <v>-0.35</v>
+        <v>-2.94</v>
       </c>
       <c r="J158" s="8" t="n">
-        <v>7.41</v>
+        <v>7.11</v>
       </c>
       <c r="K158" s="8" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="L158" s="9" t="n">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="M158" s="8" t="n">
         <v>5.93</v>
@@ -10671,19 +10671,19 @@
         <v>9.31</v>
       </c>
       <c r="H159" s="12" t="n">
-        <v>16.81</v>
+        <v>16.07</v>
       </c>
       <c r="I159" s="12" t="n">
-        <v>-1.23</v>
+        <v>-3.71</v>
       </c>
       <c r="J159" s="12" t="n">
-        <v>15.87</v>
+        <v>15.17</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="L159" s="13" t="n">
-        <v>1438</v>
+        <v>1375</v>
       </c>
       <c r="M159" s="12" t="n">
         <v>2.08</v>
@@ -10735,19 +10735,19 @@
         <v>2.25</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>253</v>
+        <v>246.5</v>
       </c>
       <c r="I160" s="8" t="n">
-        <v>11.8</v>
+        <v>-0.8</v>
       </c>
       <c r="J160" s="8" t="n">
-        <v>30.44</v>
+        <v>29.66</v>
       </c>
       <c r="K160" s="8" t="n">
-        <v>7.63</v>
+        <v>7.44</v>
       </c>
       <c r="L160" s="9" t="n">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M160" s="8" t="n">
         <v>1.19</v>
@@ -10799,19 +10799,19 @@
         <v>0.82</v>
       </c>
       <c r="H161" s="12" t="n">
-        <v>7.87</v>
+        <v>7.62</v>
       </c>
       <c r="I161" s="12" t="n">
-        <v>0.51</v>
+        <v>-2.43</v>
       </c>
       <c r="J161" s="12" t="n">
-        <v>25.39</v>
+        <v>24.58</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="L161" s="13" t="n">
-        <v>780</v>
+        <v>755</v>
       </c>
       <c r="M161" s="12" t="n">
         <v>2.12</v>
@@ -10866,7 +10866,7 @@
         <v>4.37</v>
       </c>
       <c r="I162" s="8" t="n">
-        <v>-0.23</v>
+        <v>-0.91</v>
       </c>
       <c r="J162" s="8" t="n">
         <v>9.25</v>
@@ -10927,19 +10927,19 @@
         <v>0</v>
       </c>
       <c r="H163" s="12" t="n">
-        <v>14.71</v>
+        <v>14.38</v>
       </c>
       <c r="I163" s="12" t="n">
-        <v>-1.41</v>
+        <v>-2.57</v>
       </c>
       <c r="J163" s="12" t="n">
-        <v>18.74</v>
+        <v>18.32</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="L163" s="13" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="M163" s="12" t="n">
         <v>4.76</v>
@@ -10991,19 +10991,19 @@
         <v>2.65</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>45.69</v>
+        <v>43.15</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-0.02</v>
+        <v>-1.33</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>19.22</v>
+        <v>18.15</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>9910</v>
+        <v>9359</v>
       </c>
       <c r="M164" s="4" t="n">
         <v>4.4</v>
@@ -11055,19 +11055,19 @@
         <v>3.32</v>
       </c>
       <c r="H165" s="12" t="n">
-        <v>15.1</v>
+        <v>14.74</v>
       </c>
       <c r="I165" s="12" t="n">
-        <v>-0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J165" s="12" t="n">
-        <v>38.38</v>
+        <v>37.46</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="L165" s="13" t="n">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="M165" s="12" t="n">
         <v>1.24</v>
@@ -11119,19 +11119,19 @@
         <v>2.97</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>12.63</v>
+        <v>12.31</v>
       </c>
       <c r="I166" s="8" t="n">
-        <v>1.28</v>
+        <v>-0.16</v>
       </c>
       <c r="J166" s="8" t="n">
-        <v>18.68</v>
+        <v>18.21</v>
       </c>
       <c r="K166" s="8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="L166" s="9" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M166" s="8" t="n">
         <v>2.81</v>
@@ -11183,19 +11183,19 @@
         <v>2.61</v>
       </c>
       <c r="H167" s="12" t="n">
-        <v>16.45</v>
+        <v>16.17</v>
       </c>
       <c r="I167" s="12" t="n">
-        <v>2.43</v>
+        <v>1.25</v>
       </c>
       <c r="J167" s="12" t="n">
-        <v>16.61</v>
+        <v>16.32</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="L167" s="13" t="n">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M167" s="12" t="n">
         <v>3.33</v>
@@ -11247,19 +11247,19 @@
         <v>3.31</v>
       </c>
       <c r="H168" s="8" t="n">
-        <v>20.19</v>
+        <v>18.96</v>
       </c>
       <c r="I168" s="8" t="n">
-        <v>-0.39</v>
+        <v>0.05</v>
       </c>
       <c r="J168" s="8" t="n">
-        <v>19.91</v>
+        <v>18.69</v>
       </c>
       <c r="K168" s="8" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="L168" s="9" t="n">
-        <v>2026</v>
+        <v>1903</v>
       </c>
       <c r="M168" s="8" t="n">
         <v>2.48</v>
@@ -11311,19 +11311,19 @@
         <v>2.43</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>24.8</v>
+        <v>23.92</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>0.24</v>
+        <v>-1.08</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>14.87</v>
+        <v>14.34</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>2404</v>
+        <v>2319</v>
       </c>
       <c r="M169" s="4" t="n">
         <v>3.82</v>
@@ -11375,19 +11375,19 @@
         <v>5.91</v>
       </c>
       <c r="H170" s="8" t="n">
-        <v>26.98</v>
+        <v>26.63</v>
       </c>
       <c r="I170" s="8" t="n">
-        <v>-0.44</v>
+        <v>-0.26</v>
       </c>
       <c r="J170" s="8" t="n">
-        <v>14.39</v>
+        <v>14.21</v>
       </c>
       <c r="K170" s="8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="L170" s="9" t="n">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="M170" s="8" t="n">
         <v>4.82</v>
@@ -11439,19 +11439,19 @@
         <v>3.23</v>
       </c>
       <c r="H171" s="12" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="I171" s="12" t="n">
-        <v>-0.73</v>
+        <v>-0.37</v>
       </c>
       <c r="J171" s="12" t="n">
-        <v>39.21</v>
+        <v>38.78</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="L171" s="13" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M171" s="12" t="n">
         <v>1.16</v>
@@ -11503,19 +11503,19 @@
         <v>2.73</v>
       </c>
       <c r="H172" s="8" t="n">
-        <v>15.11</v>
+        <v>14.79</v>
       </c>
       <c r="I172" s="8" t="n">
-        <v>-1.88</v>
+        <v>1.09</v>
       </c>
       <c r="J172" s="8" t="n">
-        <v>31.17</v>
+        <v>30.51</v>
       </c>
       <c r="K172" s="8" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L172" s="9" t="n">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="M172" s="8" t="n">
         <v>1.65</v>
@@ -11567,19 +11567,19 @@
         <v>2.49</v>
       </c>
       <c r="H173" s="12" t="n">
-        <v>7.99</v>
+        <v>8.02</v>
       </c>
       <c r="I173" s="12" t="n">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="J173" s="12" t="n">
-        <v>98.81</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="K173" s="12" t="n">
         <v>0.91</v>
       </c>
       <c r="L173" s="13" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M173" s="12" t="n">
         <v>0.75</v>
@@ -11631,13 +11631,13 @@
         <v>1.1</v>
       </c>
       <c r="H174" s="8" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="I174" s="8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="J174" s="8" t="n">
-        <v>-50.31</v>
+        <v>-50.38</v>
       </c>
       <c r="K174" s="8" t="n">
         <v>0.82</v>
@@ -11695,19 +11695,19 @@
         <v>0.89</v>
       </c>
       <c r="H175" s="12" t="n">
-        <v>6.99</v>
+        <v>6.87</v>
       </c>
       <c r="I175" s="12" t="n">
-        <v>1.16</v>
+        <v>-1.58</v>
       </c>
       <c r="J175" s="12" t="n">
-        <v>-17.14</v>
+        <v>-16.85</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="L175" s="13" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M175" s="12" t="n">
         <v>0</v>
@@ -11759,19 +11759,19 @@
         <v>0.83</v>
       </c>
       <c r="H176" s="8" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="I176" s="8" t="n">
-        <v>5.57</v>
+        <v>0.35</v>
       </c>
       <c r="J176" s="8" t="n">
-        <v>-43.24</v>
+        <v>-43.62</v>
       </c>
       <c r="K176" s="8" t="n">
         <v>0.67</v>
       </c>
       <c r="L176" s="9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M176" s="8" t="n">
         <v>0.35</v>
@@ -11823,19 +11823,19 @@
         <v>2.87</v>
       </c>
       <c r="H177" s="12" t="n">
-        <v>11.78</v>
+        <v>11.16</v>
       </c>
       <c r="I177" s="12" t="n">
-        <v>4.9</v>
+        <v>0.54</v>
       </c>
       <c r="J177" s="12" t="n">
-        <v>30.53</v>
+        <v>28.92</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="L177" s="13" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="M177" s="12" t="n">
         <v>2.12</v>
@@ -11887,19 +11887,19 @@
         <v>1.88</v>
       </c>
       <c r="H178" s="8" t="n">
-        <v>13.8</v>
+        <v>13.53</v>
       </c>
       <c r="I178" s="8" t="n">
-        <v>-1.64</v>
+        <v>0.3</v>
       </c>
       <c r="J178" s="8" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="K178" s="8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="L178" s="9" t="n">
-        <v>1830</v>
+        <v>1794</v>
       </c>
       <c r="M178" s="8" t="n">
         <v>3.07</v>
@@ -11951,19 +11951,19 @@
         <v>1.38</v>
       </c>
       <c r="H179" s="12" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="I179" s="12" t="n">
-        <v>-0.31</v>
+        <v>-1.37</v>
       </c>
       <c r="J179" s="12" t="n">
-        <v>27.8</v>
+        <v>27.62</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="L179" s="13" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M179" s="12" t="n">
         <v>1.94</v>
@@ -12015,19 +12015,19 @@
         <v>1.22</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>8.619999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="I180" s="8" t="n">
-        <v>-0.35</v>
+        <v>-1.75</v>
       </c>
       <c r="J180" s="8" t="n">
-        <v>19.56</v>
+        <v>19.11</v>
       </c>
       <c r="K180" s="8" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="L180" s="9" t="n">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="M180" s="8" t="n">
         <v>2.75</v>
@@ -12079,19 +12079,19 @@
         <v>2.57</v>
       </c>
       <c r="H181" s="12" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="I181" s="12" t="n">
-        <v>-0.21</v>
+        <v>-1.68</v>
       </c>
       <c r="J181" s="12" t="n">
-        <v>45.48</v>
+        <v>44.81</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="L181" s="13" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M181" s="12" t="n">
         <v>2.11</v>
@@ -12143,19 +12143,19 @@
         <v>1.54</v>
       </c>
       <c r="H182" s="8" t="n">
-        <v>8.57</v>
+        <v>8.52</v>
       </c>
       <c r="I182" s="8" t="n">
-        <v>-1.15</v>
+        <v>-1.5</v>
       </c>
       <c r="J182" s="8" t="n">
-        <v>45.68</v>
+        <v>45.42</v>
       </c>
       <c r="K182" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L182" s="9" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M182" s="8" t="n">
         <v>3.5</v>
@@ -12207,19 +12207,19 @@
         <v>5.08</v>
       </c>
       <c r="H183" s="12" t="n">
-        <v>25.22</v>
+        <v>25.88</v>
       </c>
       <c r="I183" s="12" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="J183" s="12" t="n">
-        <v>11.77</v>
+        <v>12.08</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="L183" s="13" t="n">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="M183" s="12" t="n">
         <v>2.38</v>
@@ -12271,19 +12271,19 @@
         <v>3.87</v>
       </c>
       <c r="H184" s="8" t="n">
-        <v>81.81</v>
+        <v>82.48</v>
       </c>
       <c r="I184" s="8" t="n">
-        <v>-1.71</v>
+        <v>1.9</v>
       </c>
       <c r="J184" s="8" t="n">
-        <v>28.51</v>
+        <v>28.75</v>
       </c>
       <c r="K184" s="8" t="n">
-        <v>10.49</v>
+        <v>10.57</v>
       </c>
       <c r="L184" s="9" t="n">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="M184" s="8" t="n">
         <v>3.55</v>
@@ -12335,19 +12335,19 @@
         <v>1</v>
       </c>
       <c r="H185" s="12" t="n">
-        <v>33.99</v>
+        <v>36.06</v>
       </c>
       <c r="I185" s="12" t="n">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
       <c r="J185" s="12" t="n">
-        <v>21.77</v>
+        <v>23.09</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>5.07</v>
+        <v>5.38</v>
       </c>
       <c r="L185" s="13" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M185" s="12" t="n">
         <v>1.47</v>
@@ -12399,19 +12399,19 @@
         <v>0</v>
       </c>
       <c r="H186" s="8" t="n">
-        <v>26.76</v>
+        <v>27.92</v>
       </c>
       <c r="I186" s="8" t="n">
-        <v>-1.55</v>
+        <v>3.6</v>
       </c>
       <c r="J186" s="8" t="n">
-        <v>40.65</v>
+        <v>42.41</v>
       </c>
       <c r="K186" s="8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="L186" s="9" t="n">
-        <v>607</v>
+        <v>633</v>
       </c>
       <c r="M186" s="8" t="n">
         <v>1.06</v>
@@ -12463,19 +12463,19 @@
         <v>0</v>
       </c>
       <c r="H187" s="12" t="n">
-        <v>13.57</v>
+        <v>14.29</v>
       </c>
       <c r="I187" s="12" t="n">
-        <v>-1.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J187" s="12" t="n">
-        <v>-5.3</v>
+        <v>-5.58</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="L187" s="13" t="n">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="M187" s="12" t="n">
         <v>0</v>
@@ -12527,19 +12527,19 @@
         <v>0</v>
       </c>
       <c r="H188" s="8" t="n">
-        <v>22.59</v>
+        <v>22.72</v>
       </c>
       <c r="I188" s="8" t="n">
-        <v>-0.79</v>
+        <v>-1</v>
       </c>
       <c r="J188" s="8" t="n">
-        <v>17.62</v>
+        <v>17.72</v>
       </c>
       <c r="K188" s="8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="L188" s="9" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M188" s="8" t="n">
         <v>2.43</v>
@@ -12591,19 +12591,19 @@
         <v>6.21</v>
       </c>
       <c r="H189" s="12" t="n">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="I189" s="12" t="n">
-        <v>0.21</v>
+        <v>1.49</v>
       </c>
       <c r="J189" s="12" t="n">
-        <v>19.44</v>
+        <v>19.61</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="L189" s="13" t="n">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="M189" s="12" t="n">
         <v>1.9</v>
@@ -12655,19 +12655,19 @@
         <v>4.18</v>
       </c>
       <c r="H190" s="8" t="n">
-        <v>105.64</v>
+        <v>112.23</v>
       </c>
       <c r="I190" s="8" t="n">
-        <v>5.56</v>
+        <v>10</v>
       </c>
       <c r="J190" s="8" t="n">
-        <v>65.31999999999999</v>
+        <v>69.39</v>
       </c>
       <c r="K190" s="8" t="n">
-        <v>16.05</v>
+        <v>17.06</v>
       </c>
       <c r="L190" s="9" t="n">
-        <v>2566</v>
+        <v>2726</v>
       </c>
       <c r="M190" s="8" t="n">
         <v>1.14</v>
@@ -12719,19 +12719,19 @@
         <v>2.65</v>
       </c>
       <c r="H191" s="12" t="n">
-        <v>59.29</v>
+        <v>60.5</v>
       </c>
       <c r="I191" s="12" t="n">
-        <v>4.77</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="J191" s="12" t="n">
-        <v>50.9</v>
+        <v>51.94</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>10.87</v>
+        <v>11.09</v>
       </c>
       <c r="L191" s="13" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="M191" s="12" t="n">
         <v>0.51</v>
@@ -12783,19 +12783,19 @@
         <v>2.45</v>
       </c>
       <c r="H192" s="8" t="n">
-        <v>83.92</v>
+        <v>86.8</v>
       </c>
       <c r="I192" s="8" t="n">
-        <v>2.43</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J192" s="8" t="n">
-        <v>33.27</v>
+        <v>34.41</v>
       </c>
       <c r="K192" s="8" t="n">
-        <v>4.73</v>
+        <v>4.89</v>
       </c>
       <c r="L192" s="9" t="n">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="M192" s="8" t="n">
         <v>1.1</v>
@@ -12847,19 +12847,19 @@
         <v>1.34</v>
       </c>
       <c r="H193" s="12" t="n">
-        <v>188</v>
+        <v>189.27</v>
       </c>
       <c r="I193" s="12" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="J193" s="12" t="n">
-        <v>68.56999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="K193" s="12" t="n">
-        <v>16.45</v>
+        <v>16.56</v>
       </c>
       <c r="L193" s="13" t="n">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="M193" s="12" t="n">
         <v>0.51</v>
@@ -12911,19 +12911,19 @@
         <v>0.67</v>
       </c>
       <c r="H194" s="8" t="n">
-        <v>308</v>
+        <v>332.54</v>
       </c>
       <c r="I194" s="8" t="n">
-        <v>8.26</v>
+        <v>10</v>
       </c>
       <c r="J194" s="8" t="n">
-        <v>57.72</v>
+        <v>62.32</v>
       </c>
       <c r="K194" s="8" t="n">
-        <v>12.75</v>
+        <v>13.77</v>
       </c>
       <c r="L194" s="9" t="n">
-        <v>2098</v>
+        <v>2265</v>
       </c>
       <c r="M194" s="8" t="n">
         <v>0.78</v>
@@ -12975,19 +12975,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H195" s="4" t="n">
-        <v>32.26</v>
+        <v>31.56</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>-0.89</v>
+        <v>-0.91</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>12.3</v>
+        <v>12.03</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>15333</v>
+        <v>15000</v>
       </c>
       <c r="M195" s="4" t="n">
         <v>3.55</v>
@@ -13039,19 +13039,19 @@
         <v>2.8</v>
       </c>
       <c r="H196" s="4" t="n">
-        <v>11.08</v>
+        <v>10.86</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-1.69</v>
+        <v>-1.72</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>12.82</v>
+        <v>12.57</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>20279</v>
+        <v>19876</v>
       </c>
       <c r="M196" s="4" t="n">
         <v>4.24</v>
@@ -13103,19 +13103,19 @@
         <v>2.07</v>
       </c>
       <c r="H197" s="12" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="I197" s="12" t="n">
-        <v>-0.19</v>
+        <v>-3.41</v>
       </c>
       <c r="J197" s="12" t="n">
-        <v>17.89</v>
+        <v>17.35</v>
       </c>
       <c r="K197" s="12" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="L197" s="13" t="n">
-        <v>6361</v>
+        <v>6167</v>
       </c>
       <c r="M197" s="12" t="n">
         <v>3.8</v>
@@ -13167,19 +13167,19 @@
         <v>2.03</v>
       </c>
       <c r="H198" s="8" t="n">
-        <v>25.26</v>
+        <v>26.15</v>
       </c>
       <c r="I198" s="8" t="n">
-        <v>2.14</v>
+        <v>1.2</v>
       </c>
       <c r="J198" s="8" t="n">
-        <v>19.34</v>
+        <v>20.03</v>
       </c>
       <c r="K198" s="8" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="L198" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M198" s="8" t="n">
         <v>3.1</v>
@@ -13231,19 +13231,19 @@
         <v>1.28</v>
       </c>
       <c r="H199" s="12" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="I199" s="12" t="n">
-        <v>0.52</v>
+        <v>-0.76</v>
       </c>
       <c r="J199" s="12" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
       <c r="K199" s="12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="L199" s="13" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M199" s="12" t="n">
         <v>3.77</v>
@@ -13295,16 +13295,16 @@
         <v>0.48</v>
       </c>
       <c r="H200" s="8" t="n">
-        <v>8.68</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I200" s="8" t="n">
-        <v>1.05</v>
+        <v>-0.8</v>
       </c>
       <c r="J200" s="8" t="n">
-        <v>19.42</v>
+        <v>19.51</v>
       </c>
       <c r="K200" s="8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="L200" s="9" t="n">
         <v>48</v>
@@ -13359,19 +13359,19 @@
         <v>2.73</v>
       </c>
       <c r="H201" s="12" t="n">
-        <v>7.85</v>
+        <v>7.69</v>
       </c>
       <c r="I201" s="12" t="n">
-        <v>-0.38</v>
+        <v>-1.16</v>
       </c>
       <c r="J201" s="12" t="n">
-        <v>14.15</v>
+        <v>13.86</v>
       </c>
       <c r="K201" s="12" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="L201" s="13" t="n">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="M201" s="12" t="n">
         <v>5.61</v>
@@ -13423,19 +13423,19 @@
         <v>1.91</v>
       </c>
       <c r="H202" s="8" t="n">
-        <v>6.3</v>
+        <v>6.13</v>
       </c>
       <c r="I202" s="8" t="n">
-        <v>0.16</v>
+        <v>-3.31</v>
       </c>
       <c r="J202" s="8" t="n">
-        <v>13.88</v>
+        <v>13.5</v>
       </c>
       <c r="K202" s="8" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="L202" s="9" t="n">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="M202" s="8" t="n">
         <v>6.51</v>
@@ -13487,19 +13487,19 @@
         <v>1.04</v>
       </c>
       <c r="H203" s="12" t="n">
-        <v>12.92</v>
+        <v>12.74</v>
       </c>
       <c r="I203" s="12" t="n">
-        <v>1.41</v>
+        <v>-2.15</v>
       </c>
       <c r="J203" s="12" t="n">
-        <v>12.25</v>
+        <v>12.08</v>
       </c>
       <c r="K203" s="12" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="L203" s="13" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M203" s="12" t="n">
         <v>6.97</v>
@@ -13551,19 +13551,19 @@
         <v>0.84</v>
       </c>
       <c r="H204" s="8" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="I204" s="8" t="n">
-        <v>-2.36</v>
+        <v>-3.16</v>
       </c>
       <c r="J204" s="8" t="n">
-        <v>16.91</v>
+        <v>16.69</v>
       </c>
       <c r="K204" s="8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="L204" s="9" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M204" s="8" t="n">
         <v>4.83</v>
@@ -13615,19 +13615,19 @@
         <v>0.48</v>
       </c>
       <c r="H205" s="12" t="n">
-        <v>3.92</v>
+        <v>4.12</v>
       </c>
       <c r="I205" s="12" t="n">
-        <v>1.03</v>
+        <v>-1.67</v>
       </c>
       <c r="J205" s="12" t="n">
-        <v>14.01</v>
+        <v>14.73</v>
       </c>
       <c r="K205" s="12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="L205" s="13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M205" s="12" t="n">
         <v>4.34</v>
@@ -13679,13 +13679,13 @@
         <v>2.1</v>
       </c>
       <c r="H206" s="8" t="n">
-        <v>16.37</v>
+        <v>16.34</v>
       </c>
       <c r="I206" s="8" t="n">
-        <v>1.05</v>
+        <v>4.01</v>
       </c>
       <c r="J206" s="8" t="n">
-        <v>62.03</v>
+        <v>61.91</v>
       </c>
       <c r="K206" s="8" t="n">
         <v>1.98</v>
@@ -13743,19 +13743,19 @@
         <v>1.9</v>
       </c>
       <c r="H207" s="12" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="I207" s="12" t="n">
-        <v>0.74</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J207" s="12" t="n">
-        <v>24.5</v>
+        <v>23.85</v>
       </c>
       <c r="K207" s="12" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="L207" s="13" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M207" s="12" t="n">
         <v>4.69</v>
@@ -13807,19 +13807,19 @@
         <v>1.55</v>
       </c>
       <c r="H208" s="8" t="n">
-        <v>7.71</v>
+        <v>7.69</v>
       </c>
       <c r="I208" s="8" t="n">
-        <v>1.31</v>
+        <v>-2.53</v>
       </c>
       <c r="J208" s="8" t="n">
-        <v>42.52</v>
+        <v>42.41</v>
       </c>
       <c r="K208" s="8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="L208" s="9" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M208" s="8" t="n">
         <v>1.92</v>
@@ -13871,19 +13871,19 @@
         <v>1.34</v>
       </c>
       <c r="H209" s="12" t="n">
-        <v>7.99</v>
+        <v>8.17</v>
       </c>
       <c r="I209" s="12" t="n">
-        <v>-1.96</v>
+        <v>-0.24</v>
       </c>
       <c r="J209" s="12" t="n">
-        <v>16.52</v>
+        <v>16.89</v>
       </c>
       <c r="K209" s="12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="L209" s="13" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M209" s="12" t="n">
         <v>5.01</v>
@@ -13935,19 +13935,19 @@
         <v>2.37</v>
       </c>
       <c r="H210" s="8" t="n">
-        <v>34.6</v>
+        <v>33.79</v>
       </c>
       <c r="I210" s="8" t="n">
-        <v>2.31</v>
+        <v>-1.03</v>
       </c>
       <c r="J210" s="8" t="n">
-        <v>26.97</v>
+        <v>26.34</v>
       </c>
       <c r="K210" s="8" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="L210" s="9" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M210" s="8" t="n">
         <v>1.88</v>
@@ -13999,19 +13999,19 @@
         <v>5.89</v>
       </c>
       <c r="H211" s="12" t="n">
-        <v>37.65</v>
+        <v>38.63</v>
       </c>
       <c r="I211" s="12" t="n">
-        <v>5.7</v>
+        <v>1.79</v>
       </c>
       <c r="J211" s="12" t="n">
-        <v>21</v>
+        <v>21.54</v>
       </c>
       <c r="K211" s="12" t="n">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="L211" s="13" t="n">
-        <v>3451</v>
+        <v>3540</v>
       </c>
       <c r="M211" s="12" t="n">
         <v>3.05</v>
@@ -14063,19 +14063,19 @@
         <v>2.29</v>
       </c>
       <c r="H212" s="8" t="n">
-        <v>104.71</v>
+        <v>105.49</v>
       </c>
       <c r="I212" s="8" t="n">
-        <v>-0.59</v>
+        <v>1.92</v>
       </c>
       <c r="J212" s="8" t="n">
-        <v>36.19</v>
+        <v>36.46</v>
       </c>
       <c r="K212" s="8" t="n">
-        <v>7.25</v>
+        <v>7.3</v>
       </c>
       <c r="L212" s="9" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="M212" s="8" t="n">
         <v>2.48</v>
@@ -14127,19 +14127,19 @@
         <v>4.47</v>
       </c>
       <c r="H213" s="12" t="n">
-        <v>234.96</v>
+        <v>233.51</v>
       </c>
       <c r="I213" s="12" t="n">
-        <v>4.02</v>
+        <v>1.05</v>
       </c>
       <c r="J213" s="12" t="n">
-        <v>52.94</v>
+        <v>52.61</v>
       </c>
       <c r="K213" s="12" t="n">
-        <v>25.3</v>
+        <v>25.14</v>
       </c>
       <c r="L213" s="13" t="n">
-        <v>1768</v>
+        <v>1757</v>
       </c>
       <c r="M213" s="12" t="n">
         <v>2.21</v>
@@ -14191,19 +14191,19 @@
         <v>2.8</v>
       </c>
       <c r="H214" s="8" t="n">
-        <v>269.58</v>
+        <v>274.45</v>
       </c>
       <c r="I214" s="8" t="n">
-        <v>6.9</v>
+        <v>0.16</v>
       </c>
       <c r="J214" s="8" t="n">
-        <v>34.47</v>
+        <v>35.09</v>
       </c>
       <c r="K214" s="8" t="n">
-        <v>8.539999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L214" s="9" t="n">
-        <v>1251</v>
+        <v>1273</v>
       </c>
       <c r="M214" s="8" t="n">
         <v>0.46</v>
@@ -14255,19 +14255,19 @@
         <v>0.2</v>
       </c>
       <c r="H215" s="12" t="n">
-        <v>28.15</v>
+        <v>29.23</v>
       </c>
       <c r="I215" s="12" t="n">
-        <v>2.77</v>
+        <v>3.29</v>
       </c>
       <c r="J215" s="12" t="n">
-        <v>42.31</v>
+        <v>43.94</v>
       </c>
       <c r="K215" s="12" t="n">
-        <v>7.75</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L215" s="13" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M215" s="12" t="n">
         <v>2.13</v>
@@ -14319,19 +14319,19 @@
         <v>0</v>
       </c>
       <c r="H216" s="8" t="n">
-        <v>15.66</v>
+        <v>16.17</v>
       </c>
       <c r="I216" s="8" t="n">
-        <v>-0.25</v>
+        <v>0.68</v>
       </c>
       <c r="J216" s="8" t="n">
-        <v>30.13</v>
+        <v>31.07</v>
       </c>
       <c r="K216" s="8" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="L216" s="9" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M216" s="8" t="n">
         <v>0.32</v>
@@ -14383,19 +14383,19 @@
         <v>2.68</v>
       </c>
       <c r="H217" s="12" t="n">
-        <v>41.73</v>
+        <v>41.85</v>
       </c>
       <c r="I217" s="12" t="n">
-        <v>-1.28</v>
+        <v>-0.85</v>
       </c>
       <c r="J217" s="12" t="n">
-        <v>18.12</v>
+        <v>18.17</v>
       </c>
       <c r="K217" s="12" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
       <c r="L217" s="13" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M217" s="12" t="n">
         <v>4.55</v>
@@ -14447,19 +14447,19 @@
         <v>0.57</v>
       </c>
       <c r="H218" s="8" t="n">
-        <v>8.640000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="I218" s="8" t="n">
-        <v>-3.79</v>
+        <v>-1.96</v>
       </c>
       <c r="J218" s="8" t="n">
-        <v>9.779999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K218" s="8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="L218" s="9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M218" s="8" t="n">
         <v>9.26</v>
@@ -14511,19 +14511,19 @@
         <v>0.19</v>
       </c>
       <c r="H219" s="12" t="n">
-        <v>32.85</v>
+        <v>32.66</v>
       </c>
       <c r="I219" s="12" t="n">
-        <v>0.77</v>
+        <v>-1.42</v>
       </c>
       <c r="J219" s="12" t="n">
-        <v>18.55</v>
+        <v>18.44</v>
       </c>
       <c r="K219" s="12" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="L219" s="13" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M219" s="12" t="n">
         <v>2.53</v>
@@ -14575,19 +14575,19 @@
         <v>0</v>
       </c>
       <c r="H220" s="8" t="n">
-        <v>15.06</v>
+        <v>15.02</v>
       </c>
       <c r="I220" s="8" t="n">
-        <v>-0.79</v>
+        <v>-1.18</v>
       </c>
       <c r="J220" s="8" t="n">
-        <v>15.35</v>
+        <v>15.31</v>
       </c>
       <c r="K220" s="8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="L220" s="9" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M220" s="8" t="n">
         <v>3.98</v>
@@ -14639,19 +14639,19 @@
         <v>0</v>
       </c>
       <c r="H221" s="12" t="n">
-        <v>25.2</v>
+        <v>25.26</v>
       </c>
       <c r="I221" s="12" t="n">
-        <v>-2.36</v>
+        <v>-4.14</v>
       </c>
       <c r="J221" s="12" t="n">
-        <v>11.71</v>
+        <v>11.74</v>
       </c>
       <c r="K221" s="12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="L221" s="13" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M221" s="12" t="n">
         <v>5.48</v>
@@ -14703,19 +14703,19 @@
         <v>1.75</v>
       </c>
       <c r="H222" s="8" t="n">
-        <v>97.41</v>
+        <v>96.42</v>
       </c>
       <c r="I222" s="8" t="n">
-        <v>-1.31</v>
+        <v>-2.58</v>
       </c>
       <c r="J222" s="8" t="n">
-        <v>15.55</v>
+        <v>15.4</v>
       </c>
       <c r="K222" s="8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="L222" s="9" t="n">
-        <v>21122</v>
+        <v>20907</v>
       </c>
       <c r="M222" s="8" t="n">
         <v>4.83</v>
@@ -14767,19 +14767,19 @@
         <v>1.37</v>
       </c>
       <c r="H223" s="12" t="n">
-        <v>6.3</v>
+        <v>6.29</v>
       </c>
       <c r="I223" s="12" t="n">
-        <v>-2.93</v>
+        <v>-2.78</v>
       </c>
       <c r="J223" s="12" t="n">
-        <v>18.2</v>
+        <v>18.17</v>
       </c>
       <c r="K223" s="12" t="n">
         <v>1.25</v>
       </c>
       <c r="L223" s="13" t="n">
-        <v>5765</v>
+        <v>5756</v>
       </c>
       <c r="M223" s="12" t="n">
         <v>4.32</v>
@@ -14831,19 +14831,19 @@
         <v>4.27</v>
       </c>
       <c r="H224" s="8" t="n">
-        <v>38.9</v>
+        <v>39.65</v>
       </c>
       <c r="I224" s="8" t="n">
-        <v>-0.46</v>
+        <v>1.04</v>
       </c>
       <c r="J224" s="8" t="n">
-        <v>18.29</v>
+        <v>18.64</v>
       </c>
       <c r="K224" s="8" t="n">
-        <v>5.91</v>
+        <v>6.03</v>
       </c>
       <c r="L224" s="9" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="M224" s="8" t="n">
         <v>4.63</v>
@@ -14895,19 +14895,19 @@
         <v>2.79</v>
       </c>
       <c r="H225" s="12" t="n">
-        <v>271.5</v>
+        <v>284</v>
       </c>
       <c r="I225" s="12" t="n">
-        <v>3.37</v>
+        <v>8.27</v>
       </c>
       <c r="J225" s="12" t="n">
-        <v>194.25</v>
+        <v>203.19</v>
       </c>
       <c r="K225" s="12" t="n">
-        <v>15.79</v>
+        <v>16.52</v>
       </c>
       <c r="L225" s="13" t="n">
-        <v>2248</v>
+        <v>2351</v>
       </c>
       <c r="M225" s="12" t="n">
         <v>0.1</v>
@@ -14959,19 +14959,19 @@
         <v>0.76</v>
       </c>
       <c r="H226" s="8" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="I226" s="8" t="n">
-        <v>-0.45</v>
+        <v>-0.89</v>
       </c>
       <c r="J226" s="8" t="n">
-        <v>16.11</v>
+        <v>16.14</v>
       </c>
       <c r="K226" s="8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L226" s="9" t="n">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="M226" s="8" t="n">
         <v>3.67</v>
@@ -15023,19 +15023,19 @@
         <v>3.75</v>
       </c>
       <c r="H227" s="12" t="n">
-        <v>14.98</v>
+        <v>14.33</v>
       </c>
       <c r="I227" s="12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.45</v>
       </c>
       <c r="J227" s="12" t="n">
-        <v>12.48</v>
+        <v>11.94</v>
       </c>
       <c r="K227" s="12" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="L227" s="13" t="n">
-        <v>756</v>
+        <v>723</v>
       </c>
       <c r="M227" s="12" t="n">
         <v>4.31</v>
@@ -15087,19 +15087,19 @@
         <v>2.42</v>
       </c>
       <c r="H228" s="8" t="n">
-        <v>5.03</v>
+        <v>4.86</v>
       </c>
       <c r="I228" s="8" t="n">
-        <v>-2.14</v>
+        <v>-2.8</v>
       </c>
       <c r="J228" s="8" t="n">
-        <v>10.74</v>
+        <v>10.38</v>
       </c>
       <c r="K228" s="8" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="L228" s="9" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="M228" s="8" t="n">
         <v>5.09</v>
@@ -15151,19 +15151,19 @@
         <v>2.33</v>
       </c>
       <c r="H229" s="12" t="n">
-        <v>12.75</v>
+        <v>12.35</v>
       </c>
       <c r="I229" s="12" t="n">
-        <v>0.39</v>
+        <v>-1.04</v>
       </c>
       <c r="J229" s="12" t="n">
-        <v>13.94</v>
+        <v>13.51</v>
       </c>
       <c r="K229" s="12" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="L229" s="13" t="n">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="M229" s="12" t="n">
         <v>5.49</v>
@@ -15215,19 +15215,19 @@
         <v>1.6</v>
       </c>
       <c r="H230" s="4" t="n">
-        <v>6.13</v>
+        <v>5.94</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>-2.08</v>
+        <v>-2.78</v>
       </c>
       <c r="J230" s="4" t="n">
-        <v>13.17</v>
+        <v>12.76</v>
       </c>
       <c r="K230" s="4" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>1335</v>
+        <v>1294</v>
       </c>
       <c r="M230" s="4" t="n">
         <v>4.89</v>
@@ -15279,19 +15279,19 @@
         <v>2.41</v>
       </c>
       <c r="H231" s="12" t="n">
-        <v>7.18</v>
+        <v>7.04</v>
       </c>
       <c r="I231" s="12" t="n">
-        <v>-1.91</v>
+        <v>-2.9</v>
       </c>
       <c r="J231" s="12" t="n">
-        <v>6.58</v>
+        <v>6.45</v>
       </c>
       <c r="K231" s="12" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="L231" s="13" t="n">
-        <v>6345</v>
+        <v>6221</v>
       </c>
       <c r="M231" s="12" t="n">
         <v>4.52</v>
@@ -15343,19 +15343,19 @@
         <v>2.4</v>
       </c>
       <c r="H232" s="8" t="n">
-        <v>7.99</v>
+        <v>7.66</v>
       </c>
       <c r="I232" s="8" t="n">
-        <v>-1.96</v>
+        <v>-3.77</v>
       </c>
       <c r="J232" s="8" t="n">
-        <v>7.67</v>
+        <v>7.35</v>
       </c>
       <c r="K232" s="8" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="L232" s="9" t="n">
-        <v>28477</v>
+        <v>27301</v>
       </c>
       <c r="M232" s="8" t="n">
         <v>3.88</v>
@@ -15407,19 +15407,19 @@
         <v>2.76</v>
       </c>
       <c r="H233" s="12" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="I233" s="12" t="n">
-        <v>-1.46</v>
+        <v>-1.67</v>
       </c>
       <c r="J233" s="12" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="K233" s="12" t="n">
         <v>0.54</v>
       </c>
       <c r="L233" s="13" t="n">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="M233" s="12" t="n">
         <v>5.5</v>
@@ -15471,19 +15471,19 @@
         <v>2.62</v>
       </c>
       <c r="H234" s="8" t="n">
-        <v>6.06</v>
+        <v>5.82</v>
       </c>
       <c r="I234" s="8" t="n">
-        <v>-1.3</v>
+        <v>-3.48</v>
       </c>
       <c r="J234" s="8" t="n">
-        <v>7.96</v>
+        <v>7.65</v>
       </c>
       <c r="K234" s="8" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="L234" s="9" t="n">
-        <v>19526</v>
+        <v>18753</v>
       </c>
       <c r="M234" s="8" t="n">
         <v>3.73</v>
@@ -15535,19 +15535,19 @@
         <v>2.54</v>
       </c>
       <c r="H235" s="4" t="n">
-        <v>18.5</v>
+        <v>18.07</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-1.12</v>
+        <v>-2.17</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>5.84</v>
+        <v>5.7</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="M235" s="4" t="n">
         <v>4.98</v>
@@ -15599,19 +15599,19 @@
         <v>2.39</v>
       </c>
       <c r="H236" s="8" t="n">
-        <v>11.83</v>
+        <v>11.46</v>
       </c>
       <c r="I236" s="8" t="n">
-        <v>0.08</v>
+        <v>-1.97</v>
       </c>
       <c r="J236" s="8" t="n">
-        <v>6.15</v>
+        <v>5.96</v>
       </c>
       <c r="K236" s="8" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L236" s="9" t="n">
-        <v>2171</v>
+        <v>2103</v>
       </c>
       <c r="M236" s="8" t="n">
         <v>4.77</v>
@@ -15663,19 +15663,19 @@
         <v>2.37</v>
       </c>
       <c r="H237" s="12" t="n">
-        <v>7.82</v>
+        <v>7.74</v>
       </c>
       <c r="I237" s="12" t="n">
-        <v>-1.39</v>
+        <v>-2.03</v>
       </c>
       <c r="J237" s="12" t="n">
-        <v>6.11</v>
+        <v>6.05</v>
       </c>
       <c r="K237" s="12" t="n">
         <v>0.59</v>
       </c>
       <c r="L237" s="13" t="n">
-        <v>4351</v>
+        <v>4307</v>
       </c>
       <c r="M237" s="12" t="n">
         <v>4.87</v>
@@ -15727,19 +15727,19 @@
         <v>2.35</v>
       </c>
       <c r="H238" s="8" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="I238" s="8" t="n">
-        <v>0.19</v>
+        <v>-2.49</v>
       </c>
       <c r="J238" s="8" t="n">
-        <v>5.38</v>
+        <v>5.26</v>
       </c>
       <c r="K238" s="8" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="L238" s="9" t="n">
-        <v>1104</v>
+        <v>1078</v>
       </c>
       <c r="M238" s="8" t="n">
         <v>5.33</v>
@@ -15791,19 +15791,19 @@
         <v>2.34</v>
       </c>
       <c r="H239" s="12" t="n">
-        <v>6.97</v>
+        <v>6.89</v>
       </c>
       <c r="I239" s="12" t="n">
-        <v>-0.85</v>
+        <v>-1.85</v>
       </c>
       <c r="J239" s="12" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="K239" s="12" t="n">
         <v>0.35</v>
       </c>
       <c r="L239" s="13" t="n">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="M239" s="12" t="n">
         <v>6.03</v>
@@ -15855,19 +15855,19 @@
         <v>2.08</v>
       </c>
       <c r="H240" s="8" t="n">
-        <v>6.9</v>
+        <v>6.61</v>
       </c>
       <c r="I240" s="8" t="n">
-        <v>-2.95</v>
+        <v>-4.06</v>
       </c>
       <c r="J240" s="8" t="n">
-        <v>8.210000000000001</v>
+        <v>7.86</v>
       </c>
       <c r="K240" s="8" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="L240" s="9" t="n">
-        <v>24149</v>
+        <v>23134</v>
       </c>
       <c r="M240" s="8" t="n">
         <v>3.62</v>
@@ -15919,19 +15919,19 @@
         <v>2.19</v>
       </c>
       <c r="H241" s="12" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
       <c r="I241" s="12" t="n">
-        <v>-0.77</v>
+        <v>-2.33</v>
       </c>
       <c r="J241" s="12" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="K241" s="12" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="L241" s="13" t="n">
-        <v>6221</v>
+        <v>6029</v>
       </c>
       <c r="M241" s="12" t="n">
         <v>4.21</v>
@@ -15983,19 +15983,19 @@
         <v>2.14</v>
       </c>
       <c r="H242" s="4" t="n">
-        <v>39.62</v>
+        <v>39.28</v>
       </c>
       <c r="I242" s="4" t="n">
-        <v>-2.29</v>
+        <v>-2.68</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>6.63</v>
+        <v>6.57</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>9992</v>
+        <v>9906</v>
       </c>
       <c r="M242" s="4" t="n">
         <v>5.09</v>
@@ -16047,19 +16047,19 @@
         <v>2.64</v>
       </c>
       <c r="H243" s="12" t="n">
-        <v>10.85</v>
+        <v>10.1</v>
       </c>
       <c r="I243" s="12" t="n">
-        <v>-1.09</v>
+        <v>-3.35</v>
       </c>
       <c r="J243" s="12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="K243" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="L243" s="13" t="n">
-        <v>28384</v>
+        <v>26422</v>
       </c>
       <c r="M243" s="12" t="n">
         <v>3.58</v>
@@ -16111,19 +16111,19 @@
         <v>2.63</v>
       </c>
       <c r="H244" s="8" t="n">
-        <v>11.63</v>
+        <v>11.37</v>
       </c>
       <c r="I244" s="8" t="n">
-        <v>-1.27</v>
+        <v>-2.32</v>
       </c>
       <c r="J244" s="8" t="n">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="K244" s="8" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="L244" s="9" t="n">
-        <v>1438</v>
+        <v>1406</v>
       </c>
       <c r="M244" s="8" t="n">
         <v>4.55</v>
@@ -16175,19 +16175,19 @@
         <v>2.21</v>
       </c>
       <c r="H245" s="12" t="n">
-        <v>6.76</v>
+        <v>6.49</v>
       </c>
       <c r="I245" s="12" t="n">
-        <v>-1.02</v>
+        <v>-3.57</v>
       </c>
       <c r="J245" s="12" t="n">
-        <v>6.09</v>
+        <v>5.85</v>
       </c>
       <c r="K245" s="12" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="L245" s="13" t="n">
-        <v>768</v>
+        <v>737</v>
       </c>
       <c r="M245" s="12" t="n">
         <v>4.75</v>
@@ -16239,19 +16239,19 @@
         <v>2.21</v>
       </c>
       <c r="H246" s="8" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="I246" s="8" t="n">
-        <v>-0.28</v>
+        <v>-2.47</v>
       </c>
       <c r="J246" s="8" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="K246" s="8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="L246" s="9" t="n">
-        <v>1585</v>
+        <v>1559</v>
       </c>
       <c r="M246" s="8" t="n">
         <v>5.22</v>
@@ -16303,19 +16303,19 @@
         <v>2.31</v>
       </c>
       <c r="H247" s="12" t="n">
-        <v>8.59</v>
+        <v>8.57</v>
       </c>
       <c r="I247" s="12" t="n">
-        <v>-1.49</v>
+        <v>-2.17</v>
       </c>
       <c r="J247" s="12" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="K247" s="12" t="n">
         <v>0.64</v>
       </c>
       <c r="L247" s="13" t="n">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="M247" s="12" t="n">
         <v>5.06</v>
@@ -16367,19 +16367,19 @@
         <v>2.3</v>
       </c>
       <c r="H248" s="8" t="n">
-        <v>18.9</v>
+        <v>18.56</v>
       </c>
       <c r="I248" s="8" t="n">
-        <v>-1.05</v>
+        <v>-2.83</v>
       </c>
       <c r="J248" s="8" t="n">
-        <v>5.16</v>
+        <v>5.07</v>
       </c>
       <c r="K248" s="8" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="L248" s="9" t="n">
-        <v>4000</v>
+        <v>3928</v>
       </c>
       <c r="M248" s="8" t="n">
         <v>5.64</v>
@@ -16431,19 +16431,19 @@
         <v>2.22</v>
       </c>
       <c r="H249" s="12" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="I249" s="12" t="n">
-        <v>-0.63</v>
+        <v>-2.19</v>
       </c>
       <c r="J249" s="12" t="n">
-        <v>4.95</v>
+        <v>4.89</v>
       </c>
       <c r="K249" s="12" t="n">
         <v>0.37</v>
       </c>
       <c r="L249" s="13" t="n">
-        <v>1873</v>
+        <v>1849</v>
       </c>
       <c r="M249" s="12" t="n">
         <v>5.52</v>
@@ -16495,19 +16495,19 @@
         <v>2.07</v>
       </c>
       <c r="H250" s="8" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="I250" s="8" t="n">
-        <v>0.33</v>
+        <v>-2.29</v>
       </c>
       <c r="J250" s="8" t="n">
-        <v>6.41</v>
+        <v>6.33</v>
       </c>
       <c r="K250" s="8" t="n">
         <v>0.46</v>
       </c>
       <c r="L250" s="9" t="n">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="M250" s="8" t="n">
         <v>4.32</v>
@@ -16559,19 +16559,19 @@
         <v>2.6</v>
       </c>
       <c r="H251" s="12" t="n">
-        <v>11.63</v>
+        <v>11.44</v>
       </c>
       <c r="I251" s="12" t="n">
-        <v>0.17</v>
+        <v>-1.55</v>
       </c>
       <c r="J251" s="12" t="n">
-        <v>5.24</v>
+        <v>5.16</v>
       </c>
       <c r="K251" s="12" t="n">
         <v>0.49</v>
       </c>
       <c r="L251" s="13" t="n">
-        <v>2257</v>
+        <v>2220</v>
       </c>
       <c r="M251" s="12" t="n">
         <v>5.12</v>
@@ -16623,19 +16623,19 @@
         <v>2.06</v>
       </c>
       <c r="H252" s="8" t="n">
-        <v>7.79</v>
+        <v>7.56</v>
       </c>
       <c r="I252" s="8" t="n">
-        <v>1.3</v>
+        <v>-3.82</v>
       </c>
       <c r="J252" s="8" t="n">
-        <v>7.66</v>
+        <v>7.44</v>
       </c>
       <c r="K252" s="8" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="L252" s="9" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="M252" s="8" t="n">
         <v>3.21</v>
@@ -16687,19 +16687,19 @@
         <v>2.01</v>
       </c>
       <c r="H253" s="12" t="n">
-        <v>11.42</v>
+        <v>11.14</v>
       </c>
       <c r="I253" s="12" t="n">
-        <v>-1.21</v>
+        <v>-2.88</v>
       </c>
       <c r="J253" s="12" t="n">
-        <v>6.92</v>
+        <v>6.75</v>
       </c>
       <c r="K253" s="12" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="L253" s="13" t="n">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="M253" s="12" t="n">
         <v>3.92</v>
@@ -16751,19 +16751,19 @@
         <v>2.19</v>
       </c>
       <c r="H254" s="8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="I254" s="8" t="n">
-        <v>-1.45</v>
+        <v>-2.78</v>
       </c>
       <c r="J254" s="8" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="K254" s="8" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="L254" s="9" t="n">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M254" s="8" t="n">
         <v>4.51</v>
@@ -16815,19 +16815,19 @@
         <v>2.02</v>
       </c>
       <c r="H255" s="12" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="I255" s="12" t="n">
-        <v>-0.65</v>
+        <v>-2.59</v>
       </c>
       <c r="J255" s="12" t="n">
-        <v>5.62</v>
+        <v>5.54</v>
       </c>
       <c r="K255" s="12" t="n">
         <v>0.59</v>
       </c>
       <c r="L255" s="13" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M255" s="12" t="n">
         <v>4.8</v>
@@ -16879,19 +16879,19 @@
         <v>1.88</v>
       </c>
       <c r="H256" s="8" t="n">
-        <v>6.37</v>
+        <v>6.17</v>
       </c>
       <c r="I256" s="8" t="n">
-        <v>0.16</v>
+        <v>-2.83</v>
       </c>
       <c r="J256" s="8" t="n">
-        <v>6.64</v>
+        <v>6.43</v>
       </c>
       <c r="K256" s="8" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="L256" s="9" t="n">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="M256" s="8" t="n">
         <v>3.91</v>
@@ -16943,19 +16943,19 @@
         <v>1.81</v>
       </c>
       <c r="H257" s="12" t="n">
-        <v>8.49</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I257" s="12" t="n">
-        <v>-1.05</v>
+        <v>-2.58</v>
       </c>
       <c r="J257" s="12" t="n">
-        <v>6.93</v>
+        <v>6.78</v>
       </c>
       <c r="K257" s="12" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="L257" s="13" t="n">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="M257" s="12" t="n">
         <v>4.24</v>
@@ -17007,19 +17007,19 @@
         <v>1.72</v>
       </c>
       <c r="H258" s="8" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="I258" s="8" t="n">
-        <v>0.73</v>
+        <v>-2.61</v>
       </c>
       <c r="J258" s="8" t="n">
-        <v>5.46</v>
+        <v>5.39</v>
       </c>
       <c r="K258" s="8" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L258" s="9" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M258" s="8" t="n">
         <v>5.3</v>
@@ -17071,19 +17071,19 @@
         <v>0.88</v>
       </c>
       <c r="H259" s="12" t="n">
-        <v>5.78</v>
+        <v>5.72</v>
       </c>
       <c r="I259" s="12" t="n">
-        <v>0.17</v>
+        <v>-2.72</v>
       </c>
       <c r="J259" s="12" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="K259" s="12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="L259" s="13" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M259" s="12" t="n">
         <v>5.19</v>
@@ -17135,19 +17135,19 @@
         <v>1.44</v>
       </c>
       <c r="H260" s="8" t="n">
-        <v>16.45</v>
+        <v>16.14</v>
       </c>
       <c r="I260" s="8" t="n">
-        <v>-0.3</v>
+        <v>-1.65</v>
       </c>
       <c r="J260" s="8" t="n">
-        <v>6.07</v>
+        <v>5.96</v>
       </c>
       <c r="K260" s="8" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L260" s="9" t="n">
-        <v>1192</v>
+        <v>1170</v>
       </c>
       <c r="M260" s="8" t="n">
         <v>4.01</v>
@@ -17199,13 +17199,13 @@
         <v>0.98</v>
       </c>
       <c r="H261" s="12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="I261" s="12" t="n">
-        <v>-0.45</v>
+        <v>-2.2</v>
       </c>
       <c r="J261" s="12" t="n">
-        <v>6.85</v>
+        <v>6.88</v>
       </c>
       <c r="K261" s="12" t="n">
         <v>0.41</v>
@@ -17263,19 +17263,19 @@
         <v>0.62</v>
       </c>
       <c r="H262" s="8" t="n">
-        <v>5.65</v>
+        <v>5.59</v>
       </c>
       <c r="I262" s="8" t="n">
-        <v>-0.18</v>
+        <v>-2.95</v>
       </c>
       <c r="J262" s="8" t="n">
-        <v>5.33</v>
+        <v>5.27</v>
       </c>
       <c r="K262" s="8" t="n">
         <v>0.54</v>
       </c>
       <c r="L262" s="9" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M262" s="8" t="n">
         <v>4.25</v>
@@ -17327,19 +17327,19 @@
         <v>0.61</v>
       </c>
       <c r="H263" s="12" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="I263" s="12" t="n">
-        <v>-0.37</v>
+        <v>-2.95</v>
       </c>
       <c r="J263" s="12" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="K263" s="12" t="n">
         <v>0.48</v>
       </c>
       <c r="L263" s="13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M263" s="12" t="n">
         <v>3.76</v>
@@ -17391,19 +17391,19 @@
         <v>0.51</v>
       </c>
       <c r="H264" s="8" t="n">
-        <v>6.43</v>
+        <v>6.29</v>
       </c>
       <c r="I264" s="8" t="n">
-        <v>-0.31</v>
+        <v>-2.63</v>
       </c>
       <c r="J264" s="8" t="n">
-        <v>5.41</v>
+        <v>5.29</v>
       </c>
       <c r="K264" s="8" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="L264" s="9" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="M264" s="8" t="n">
         <v>4.2</v>
@@ -17455,19 +17455,19 @@
         <v>0.5</v>
       </c>
       <c r="H265" s="12" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="I265" s="12" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="J265" s="12" t="n">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="K265" s="12" t="n">
         <v>0.51</v>
       </c>
       <c r="L265" s="13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M265" s="12" t="n">
         <v>4.76</v>
@@ -17519,19 +17519,19 @@
         <v>1.51</v>
       </c>
       <c r="H266" s="8" t="n">
-        <v>9.51</v>
+        <v>9.4</v>
       </c>
       <c r="I266" s="8" t="n">
-        <v>-2.06</v>
+        <v>-2.39</v>
       </c>
       <c r="J266" s="8" t="n">
-        <v>6.3</v>
+        <v>6.23</v>
       </c>
       <c r="K266" s="8" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="L266" s="9" t="n">
-        <v>3167</v>
+        <v>3131</v>
       </c>
       <c r="M266" s="8" t="n">
         <v>4.42</v>
@@ -17583,19 +17583,19 @@
         <v>2.07</v>
       </c>
       <c r="H267" s="12" t="n">
-        <v>6.54</v>
+        <v>6.29</v>
       </c>
       <c r="I267" s="12" t="n">
-        <v>-0.15</v>
+        <v>-2.33</v>
       </c>
       <c r="J267" s="12" t="n">
-        <v>11.51</v>
+        <v>11.07</v>
       </c>
       <c r="K267" s="12" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="L267" s="13" t="n">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="M267" s="12" t="n">
         <v>4.59</v>
@@ -17647,19 +17647,19 @@
         <v>1.91</v>
       </c>
       <c r="H268" s="8" t="n">
-        <v>54.9</v>
+        <v>53.93</v>
       </c>
       <c r="I268" s="8" t="n">
-        <v>-1.61</v>
+        <v>-2.92</v>
       </c>
       <c r="J268" s="8" t="n">
-        <v>7.49</v>
+        <v>7.35</v>
       </c>
       <c r="K268" s="8" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="L268" s="9" t="n">
-        <v>9941</v>
+        <v>9765</v>
       </c>
       <c r="M268" s="8" t="n">
         <v>4.92</v>
@@ -17711,19 +17711,19 @@
         <v>2.22</v>
       </c>
       <c r="H269" s="12" t="n">
-        <v>8.6</v>
+        <v>8.83</v>
       </c>
       <c r="I269" s="12" t="n">
-        <v>0.35</v>
+        <v>2.56</v>
       </c>
       <c r="J269" s="12" t="n">
-        <v>11.32</v>
+        <v>11.62</v>
       </c>
       <c r="K269" s="12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="L269" s="13" t="n">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="M269" s="12" t="n">
         <v>3.49</v>
@@ -17775,19 +17775,19 @@
         <v>1.5</v>
       </c>
       <c r="H270" s="8" t="n">
-        <v>63.14</v>
+        <v>62.29</v>
       </c>
       <c r="I270" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="J270" s="8" t="n">
-        <v>5.34</v>
+        <v>5.27</v>
       </c>
       <c r="K270" s="8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="L270" s="9" t="n">
-        <v>1970</v>
+        <v>1943</v>
       </c>
       <c r="M270" s="8" t="n">
         <v>7.48</v>
@@ -17839,13 +17839,13 @@
         <v>0.9</v>
       </c>
       <c r="H271" s="12" t="n">
-        <v>7.86</v>
+        <v>7.85</v>
       </c>
       <c r="I271" s="12" t="n">
-        <v>0.9</v>
+        <v>-0.13</v>
       </c>
       <c r="J271" s="12" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K271" s="12" t="n">
         <v>1.21</v>
@@ -17903,19 +17903,19 @@
         <v>2.79</v>
       </c>
       <c r="H272" s="4" t="n">
-        <v>25.99</v>
+        <v>25.52</v>
       </c>
       <c r="I272" s="4" t="n">
-        <v>-3.2</v>
+        <v>-2.56</v>
       </c>
       <c r="J272" s="4" t="n">
-        <v>17.12</v>
+        <v>16.81</v>
       </c>
       <c r="K272" s="4" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="M272" s="4" t="n">
         <v>5.58</v>
@@ -17967,19 +17967,19 @@
         <v>1.58</v>
       </c>
       <c r="H273" s="12" t="n">
-        <v>27.1</v>
+        <v>26.37</v>
       </c>
       <c r="I273" s="12" t="n">
-        <v>-2.13</v>
+        <v>-2.77</v>
       </c>
       <c r="J273" s="12" t="n">
-        <v>14.18</v>
+        <v>13.8</v>
       </c>
       <c r="K273" s="12" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="L273" s="13" t="n">
-        <v>1714</v>
+        <v>1668</v>
       </c>
       <c r="M273" s="12" t="n">
         <v>5.09</v>
@@ -18031,19 +18031,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="H274" s="8" t="n">
-        <v>1350.6</v>
+        <v>1328.36</v>
       </c>
       <c r="I274" s="8" t="n">
-        <v>-0.82</v>
+        <v>-2.25</v>
       </c>
       <c r="J274" s="8" t="n">
-        <v>20.41</v>
+        <v>20.08</v>
       </c>
       <c r="K274" s="8" t="n">
-        <v>7.25</v>
+        <v>7.13</v>
       </c>
       <c r="L274" s="9" t="n">
-        <v>16884</v>
+        <v>16606</v>
       </c>
       <c r="M274" s="8" t="n">
         <v>3.85</v>
@@ -18095,19 +18095,19 @@
         <v>2.54</v>
       </c>
       <c r="H275" s="12" t="n">
-        <v>52.03</v>
+        <v>50.56</v>
       </c>
       <c r="I275" s="12" t="n">
-        <v>-0.42</v>
+        <v>-3.27</v>
       </c>
       <c r="J275" s="12" t="n">
-        <v>17.55</v>
+        <v>17.06</v>
       </c>
       <c r="K275" s="12" t="n">
-        <v>7.67</v>
+        <v>7.45</v>
       </c>
       <c r="L275" s="13" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M275" s="12" t="n">
         <v>2.69</v>
@@ -18159,19 +18159,19 @@
         <v>1.38</v>
       </c>
       <c r="H276" s="8" t="n">
-        <v>46.52</v>
+        <v>45.84</v>
       </c>
       <c r="I276" s="8" t="n">
-        <v>-1.75</v>
+        <v>-2.61</v>
       </c>
       <c r="J276" s="8" t="n">
-        <v>18.83</v>
+        <v>18.55</v>
       </c>
       <c r="K276" s="8" t="n">
-        <v>18.04</v>
+        <v>17.78</v>
       </c>
       <c r="L276" s="9" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M276" s="8" t="n">
         <v>5.37</v>
@@ -18223,19 +18223,19 @@
         <v>1.84</v>
       </c>
       <c r="H277" s="12" t="n">
-        <v>38.44</v>
+        <v>37.33</v>
       </c>
       <c r="I277" s="12" t="n">
-        <v>-0.57</v>
+        <v>-1.81</v>
       </c>
       <c r="J277" s="12" t="n">
-        <v>30.9</v>
+        <v>30.01</v>
       </c>
       <c r="K277" s="12" t="n">
-        <v>6.02</v>
+        <v>5.85</v>
       </c>
       <c r="L277" s="13" t="n">
-        <v>2249</v>
+        <v>2184</v>
       </c>
       <c r="M277" s="12" t="n">
         <v>2.76</v>
@@ -18287,19 +18287,19 @@
         <v>1.37</v>
       </c>
       <c r="H278" s="4" t="n">
-        <v>78</v>
+        <v>76.88</v>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-0.71</v>
+        <v>-1.51</v>
       </c>
       <c r="J278" s="4" t="n">
-        <v>24.03</v>
+        <v>23.68</v>
       </c>
       <c r="K278" s="4" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>3028</v>
+        <v>2984</v>
       </c>
       <c r="M278" s="4" t="n">
         <v>6.61</v>
@@ -18351,19 +18351,19 @@
         <v>1.36</v>
       </c>
       <c r="H279" s="12" t="n">
-        <v>20.84</v>
+        <v>20.28</v>
       </c>
       <c r="I279" s="12" t="n">
-        <v>0.29</v>
+        <v>-2.12</v>
       </c>
       <c r="J279" s="12" t="n">
-        <v>31.83</v>
+        <v>30.98</v>
       </c>
       <c r="K279" s="12" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="L279" s="13" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M279" s="12" t="n">
         <v>2.4</v>
@@ -18415,19 +18415,19 @@
         <v>1.23</v>
       </c>
       <c r="H280" s="8" t="n">
-        <v>10.44</v>
+        <v>10.25</v>
       </c>
       <c r="I280" s="8" t="n">
-        <v>2.86</v>
+        <v>-0.68</v>
       </c>
       <c r="J280" s="8" t="n">
-        <v>24.22</v>
+        <v>23.78</v>
       </c>
       <c r="K280" s="8" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="L280" s="9" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M280" s="8" t="n">
         <v>4.31</v>
@@ -18479,19 +18479,19 @@
         <v>1.07</v>
       </c>
       <c r="H281" s="12" t="n">
-        <v>12.19</v>
+        <v>11.91</v>
       </c>
       <c r="I281" s="12" t="n">
-        <v>0</v>
+        <v>-1.98</v>
       </c>
       <c r="J281" s="12" t="n">
-        <v>18.31</v>
+        <v>17.89</v>
       </c>
       <c r="K281" s="12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="L281" s="13" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M281" s="12" t="n">
         <v>3.45</v>
@@ -18543,19 +18543,19 @@
         <v>0.98</v>
       </c>
       <c r="H282" s="8" t="n">
-        <v>20.43</v>
+        <v>19.75</v>
       </c>
       <c r="I282" s="8" t="n">
-        <v>-1.83</v>
+        <v>-2.47</v>
       </c>
       <c r="J282" s="8" t="n">
-        <v>25.24</v>
+        <v>24.4</v>
       </c>
       <c r="K282" s="8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="L282" s="9" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M282" s="8" t="n">
         <v>4.89</v>
@@ -18607,19 +18607,19 @@
         <v>0.85</v>
       </c>
       <c r="H283" s="12" t="n">
-        <v>56</v>
+        <v>54.68</v>
       </c>
       <c r="I283" s="12" t="n">
-        <v>-2.52</v>
+        <v>-2.69</v>
       </c>
       <c r="J283" s="12" t="n">
-        <v>16.33</v>
+        <v>15.95</v>
       </c>
       <c r="K283" s="12" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="L283" s="13" t="n">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="M283" s="12" t="n">
         <v>4.2</v>
@@ -18671,19 +18671,19 @@
         <v>0.75</v>
       </c>
       <c r="H284" s="8" t="n">
-        <v>15.16</v>
+        <v>14.93</v>
       </c>
       <c r="I284" s="8" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J284" s="8" t="n">
-        <v>21.61</v>
+        <v>21.28</v>
       </c>
       <c r="K284" s="8" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="L284" s="9" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M284" s="8" t="n">
         <v>3.63</v>
@@ -18735,19 +18735,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H285" s="12" t="n">
-        <v>12.55</v>
+        <v>12.26</v>
       </c>
       <c r="I285" s="12" t="n">
-        <v>0.32</v>
+        <v>-2</v>
       </c>
       <c r="J285" s="12" t="n">
-        <v>25.93</v>
+        <v>25.33</v>
       </c>
       <c r="K285" s="12" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="L285" s="13" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M285" s="12" t="n">
         <v>1.59</v>
@@ -18799,19 +18799,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H286" s="8" t="n">
-        <v>89.89</v>
+        <v>85.8</v>
       </c>
       <c r="I286" s="8" t="n">
-        <v>-1.06</v>
+        <v>-0.84</v>
       </c>
       <c r="J286" s="8" t="n">
-        <v>19.61</v>
+        <v>18.72</v>
       </c>
       <c r="K286" s="8" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="L286" s="9" t="n">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="M286" s="8" t="n">
         <v>3.19</v>
@@ -18863,19 +18863,19 @@
         <v>0.12</v>
       </c>
       <c r="H287" s="12" t="n">
-        <v>13.25</v>
+        <v>12.85</v>
       </c>
       <c r="I287" s="12" t="n">
-        <v>-1.19</v>
+        <v>-1.46</v>
       </c>
       <c r="J287" s="12" t="n">
-        <v>19.24</v>
+        <v>18.66</v>
       </c>
       <c r="K287" s="12" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="L287" s="13" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M287" s="12" t="n">
         <v>4.38</v>
@@ -18927,19 +18927,19 @@
         <v>0.11</v>
       </c>
       <c r="H288" s="8" t="n">
-        <v>19.43</v>
+        <v>19.06</v>
       </c>
       <c r="I288" s="8" t="n">
-        <v>0.78</v>
+        <v>-1.5</v>
       </c>
       <c r="J288" s="8" t="n">
-        <v>16.44</v>
+        <v>16.13</v>
       </c>
       <c r="K288" s="8" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="L288" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M288" s="8" t="n">
         <v>6.18</v>
@@ -18991,16 +18991,16 @@
         <v>0.08</v>
       </c>
       <c r="H289" s="12" t="n">
-        <v>10.86</v>
+        <v>10.77</v>
       </c>
       <c r="I289" s="12" t="n">
-        <v>0.09</v>
+        <v>-1.64</v>
       </c>
       <c r="J289" s="12" t="n">
-        <v>19.87</v>
+        <v>19.71</v>
       </c>
       <c r="K289" s="12" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="L289" s="13" t="n">
         <v>49</v>
@@ -19055,19 +19055,19 @@
         <v>0</v>
       </c>
       <c r="H290" s="8" t="n">
-        <v>218.5</v>
+        <v>205.3</v>
       </c>
       <c r="I290" s="8" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="J290" s="8" t="n">
-        <v>24.51</v>
+        <v>23.02</v>
       </c>
       <c r="K290" s="8" t="n">
-        <v>20.64</v>
+        <v>19.39</v>
       </c>
       <c r="L290" s="9" t="n">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="M290" s="8" t="n">
         <v>0.45</v>
@@ -19147,7 +19147,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4. 股息率：东财分红历史接口，近12个月每股派息合计÷最新价（近12个月无派息者记 0.00%）</t>
+          <t>4. 股息率：东财分红历史接口，近12个月（精确365天）每股派息合计÷最新价（近12个月无派息者记 0.00%）</t>
         </is>
       </c>
     </row>

--- a/excel/红利成分股汇总.xlsx
+++ b/excel/红利成分股汇总.xlsx
@@ -623,19 +623,19 @@
         <v>2.42</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-1.64</v>
+        <v>-1.03</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>16.72</v>
+        <v>16.65</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.59</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>4.46</v>
@@ -687,19 +687,19 @@
         <v>2.35</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>10.78</v>
+        <v>10.86</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-1.28</v>
+        <v>0.46</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>16.12</v>
+        <v>16.24</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>7.4</v>
@@ -751,19 +751,19 @@
         <v>1.9</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>-0.84</v>
+        <v>-1.05</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>13.48</v>
+        <v>13.31</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>4.12</v>
@@ -815,19 +815,19 @@
         <v>7.03</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>15.4</v>
+        <v>15.46</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>9.390000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>1.03</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>2351</v>
+        <v>2360</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>6.4</v>
@@ -879,19 +879,19 @@
         <v>4.69</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>10.64</v>
+        <v>10.41</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.57</v>
+        <v>-0.76</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>11.28</v>
+        <v>11.03</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>6.22</v>
@@ -943,19 +943,19 @@
         <v>2.14</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>14.2</v>
+        <v>14.81</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>-0.98</v>
+        <v>4.37</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>18.61</v>
+        <v>19.4</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>4.15</v>
@@ -1007,19 +1007,19 @@
         <v>1.74</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>16.31</v>
+        <v>16.17</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>-1.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>14.96</v>
+        <v>14.83</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>3.88</v>
@@ -1071,19 +1071,19 @@
         <v>1.93</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>-2.39</v>
+        <v>-2.35</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>7.8</v>
@@ -1135,19 +1135,19 @@
         <v>1.75</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>5.77</v>
+        <v>5.72</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>36.08</v>
+        <v>35.77</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>3.73</v>
@@ -1199,19 +1199,19 @@
         <v>2</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>9.58</v>
+        <v>9.42</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>-2.04</v>
+        <v>-1.05</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>14.06</v>
+        <v>13.82</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>3.69</v>
@@ -1263,19 +1263,19 @@
         <v>1.94</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>6.36</v>
+        <v>6.49</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>-0.31</v>
+        <v>0.46</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>11.24</v>
+        <v>11.47</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>4.59</v>
@@ -1327,19 +1327,19 @@
         <v>4.24</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>18.1</v>
+        <v>17.96</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>7.87</v>
+        <v>0.45</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>18.48</v>
+        <v>18.33</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1461</v>
+        <v>1450</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1.91</v>
@@ -1391,19 +1391,19 @@
         <v>0.59</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>6.43</v>
+        <v>6.27</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>-0.62</v>
+        <v>-1.26</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>13.99</v>
+        <v>13.64</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>3.28</v>
@@ -1455,16 +1455,16 @@
         <v>0.46</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>11.51</v>
+        <v>11.42</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>13.73</v>
+        <v>13.63</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="L15" s="13" t="n">
         <v>40</v>
@@ -1519,19 +1519,19 @@
         <v>2.03</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>11.73</v>
+        <v>11.92</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>1.3</v>
+        <v>-0.67</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>17.49</v>
+        <v>17.77</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>5.34</v>
@@ -1583,19 +1583,19 @@
         <v>1.84</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>15.05</v>
+        <v>14.93</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>4.18</v>
@@ -1647,19 +1647,19 @@
         <v>1.54</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>21.95</v>
+        <v>21.73</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>-1.17</v>
+        <v>-1.45</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>11.71</v>
+        <v>11.59</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>3.61</v>
@@ -1714,7 +1714,7 @@
         <v>5.17</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>-0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8.81</v>
@@ -1775,19 +1775,19 @@
         <v>1.08</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>11.94</v>
+        <v>11.87</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>-0.5</v>
+        <v>-0.17</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>12.67</v>
+        <v>12.59</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>4.02</v>
@@ -1839,19 +1839,19 @@
         <v>0.89</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>8.99</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.45</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>11.13</v>
+        <v>11.01</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6.04</v>
@@ -1903,19 +1903,19 @@
         <v>0.48</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>12.92</v>
+        <v>12.51</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>-0.23</v>
+        <v>-2.04</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>14.64</v>
+        <v>14.18</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>3.07</v>
@@ -1967,19 +1967,19 @@
         <v>0.44</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>11.32</v>
+        <v>11.12</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.09</v>
+        <v>-0.71</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>9.91</v>
+        <v>9.73</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>7.08</v>
@@ -2031,19 +2031,19 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>7.72</v>
+        <v>7.58</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>-1.28</v>
+        <v>-1.04</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>14.85</v>
+        <v>14.58</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>3.59</v>
@@ -2095,19 +2095,19 @@
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>17.04</v>
+        <v>17.31</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.06</v>
+        <v>-0.35</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>9.94</v>
+        <v>10.1</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>3.97</v>
@@ -2159,19 +2159,19 @@
         <v>0</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>-1.97</v>
+        <v>-0.68</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>24.03</v>
+        <v>23.54</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>1.89</v>
@@ -2223,19 +2223,19 @@
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>10.32</v>
+        <v>10.14</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>3.36</v>
@@ -2287,19 +2287,19 @@
         <v>0</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>14.77</v>
+        <v>14.6</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>-0.27</v>
+        <v>-0.75</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>12.09</v>
+        <v>11.95</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>2.57</v>
@@ -2351,19 +2351,19 @@
         <v>1.57</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.95</v>
+        <v>7.78</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.33</v>
+        <v>0.13</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>10.17</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M29" s="4" t="n">
         <v>5</v>
@@ -2415,19 +2415,19 @@
         <v>1.79</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>9.57</v>
+        <v>9.23</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>-1.95</v>
+        <v>-1.7</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>14.23</v>
+        <v>13.73</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>1</v>
@@ -2479,19 +2479,19 @@
         <v>4.68</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>30.07</v>
+        <v>29.16</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0.43</v>
+        <v>-0.34</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>22.98</v>
+        <v>22.28</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>3.58</v>
+        <v>3.47</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>1.16</v>
@@ -2543,19 +2543,19 @@
         <v>1.23</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>10.75</v>
+        <v>10.43</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>-1.92</v>
+        <v>-1.32</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>12.02</v>
+        <v>11.67</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>5</v>
@@ -2607,19 +2607,19 @@
         <v>4.28</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>392</v>
+        <v>382.02</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>-0.12</v>
+        <v>-0.39</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>13.93</v>
+        <v>13.57</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>5.03</v>
@@ -2671,19 +2671,19 @@
         <v>0.33</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>34.88</v>
+        <v>34.03</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>-1.75</v>
+        <v>-0.79</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>12.36</v>
+        <v>12.06</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>7.92</v>
@@ -2735,19 +2735,19 @@
         <v>0.66</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>7.26</v>
+        <v>6.99</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>-2.55</v>
+        <v>-2.24</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>12.85</v>
+        <v>12.37</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>3.86</v>
@@ -2799,19 +2799,19 @@
         <v>0.65</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>7.49</v>
+        <v>7.19</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>-1.71</v>
+        <v>-1.64</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>47.36</v>
+        <v>45.47</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M36" s="8" t="n">
         <v>2.59</v>
@@ -2863,19 +2863,19 @@
         <v>6.95</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>20.23</v>
+        <v>19.7</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.25</v>
+        <v>-0.51</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>13.88</v>
+        <v>13.52</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>5.17</v>
@@ -2927,19 +2927,19 @@
         <v>1.19</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>7.25</v>
+        <v>7.15</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>-1.49</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>12.84</v>
+        <v>12.66</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>4.37</v>
@@ -2991,19 +2991,19 @@
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>12.48</v>
+        <v>12.18</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>-1.89</v>
+        <v>-1.62</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>9.27</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>5.29</v>
@@ -3055,19 +3055,19 @@
         <v>0</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>5.59</v>
+        <v>5.47</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
+        <v>-1.44</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>14.6</v>
+        <v>14.28</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M40" s="8" t="n">
         <v>5.37</v>
@@ -3119,19 +3119,19 @@
         <v>1.79</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>8.949999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>-1.21</v>
+        <v>-0.22</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>9.76</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>1.19</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>5.01</v>
@@ -3183,19 +3183,19 @@
         <v>2.21</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>-1.03</v>
+        <v>-0.85</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>16.59</v>
+        <v>16.21</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M42" s="8" t="n">
         <v>4.46</v>
@@ -3250,7 +3250,7 @@
         <v>27.76</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-1.91</v>
+        <v>0.04</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>18.82</v>
@@ -3311,19 +3311,19 @@
         <v>2.05</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>11.13</v>
+        <v>10.69</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.45</v>
+        <v>-2.55</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>22.78</v>
+        <v>21.88</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>4.85</v>
+        <v>4.66</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>877</v>
+        <v>843</v>
       </c>
       <c r="M44" s="8" t="n">
         <v>2.71</v>
@@ -3375,19 +3375,19 @@
         <v>1.24</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>-0.99</v>
+        <v>-0.6</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>13.21</v>
+        <v>13.19</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>1.52</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="M45" s="4" t="n">
         <v>4.74</v>
@@ -3439,19 +3439,19 @@
         <v>1.7</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>17.27</v>
+        <v>17.41</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>-2.1</v>
+        <v>0.23</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>12.26</v>
+        <v>12.36</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>6.4</v>
@@ -3503,19 +3503,19 @@
         <v>0.92</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>13.76</v>
+        <v>13.56</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14.22</v>
+        <v>14.02</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>4.62</v>
@@ -3567,16 +3567,16 @@
         <v>0.47</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>18.87</v>
+        <v>19.16</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>15.04</v>
+        <v>15.28</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>36</v>
@@ -3631,19 +3631,19 @@
         <v>0.45</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>7.21</v>
+        <v>7.09</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>-1.64</v>
+        <v>-0.98</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>16.16</v>
+        <v>15.89</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>2.71</v>
@@ -3695,19 +3695,19 @@
         <v>2.38</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>19.93</v>
+        <v>19.67</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.2</v>
+        <v>-0.46</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>13.37</v>
+        <v>13.19</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M50" s="8" t="n">
         <v>2.43</v>
@@ -3759,19 +3759,19 @@
         <v>1.91</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>30.34</v>
+        <v>29.48</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>-1.24</v>
+        <v>-2.42</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>11.19</v>
+        <v>10.87</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>3.39</v>
@@ -3823,19 +3823,19 @@
         <v>1.39</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>-1.71</v>
+        <v>-0.35</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>11.73</v>
+        <v>11.61</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M52" s="8" t="n">
         <v>4.07</v>
@@ -3887,19 +3887,19 @@
         <v>0.99</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>8.369999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>0.48</v>
+        <v>-0.36</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>10.81</v>
+        <v>10.74</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>1.14</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>5.38</v>
@@ -3951,19 +3951,19 @@
         <v>0.86</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>-1.26</v>
+        <v>-0.64</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>9.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="M54" s="8" t="n">
         <v>4.78</v>
@@ -4015,19 +4015,19 @@
         <v>0.65</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>10.29</v>
+        <v>10.45</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>0.19</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>12.08</v>
+        <v>12.27</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>3.92</v>
@@ -4079,19 +4079,19 @@
         <v>0.62</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>-1.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>10.47</v>
+        <v>10.28</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M56" s="8" t="n">
         <v>3.92</v>
@@ -4143,19 +4143,19 @@
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>4.9</v>
+        <v>4.79</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>-1.01</v>
+        <v>-0.83</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>10.3</v>
+        <v>10.07</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>5.1</v>
@@ -4207,19 +4207,19 @@
         <v>0</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>5.31</v>
+        <v>5.22</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>-1.12</v>
+        <v>-0.76</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>21.65</v>
+        <v>21.28</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M58" s="8" t="n">
         <v>0.5600000000000001</v>
@@ -4271,13 +4271,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>5.55</v>
+        <v>5.51</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>9.859999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>0.85</v>
@@ -4335,19 +4335,19 @@
         <v>2.17</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>12.97</v>
+        <v>13.55</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>1.25</v>
+        <v>5.69</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>28.01</v>
+        <v>29.27</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="M60" s="8" t="n">
         <v>5.98</v>
@@ -4399,19 +4399,19 @@
         <v>0.62</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>-0.85</v>
+        <v>-0.6</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>23.7</v>
+        <v>23.84</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>2.56</v>
@@ -4463,19 +4463,19 @@
         <v>0</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>-0.57</v>
+        <v>-1.6</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>22.15</v>
+        <v>21.77</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M62" s="8" t="n">
         <v>2.73</v>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>6.52</v>
+        <v>6.56</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>-0.46</v>
+        <v>0.31</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>50.64</v>
+        <v>50.95</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="L63" s="13" t="n">
         <v>67</v>
@@ -4591,19 +4591,19 @@
         <v>4.78</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>54.25</v>
+        <v>53.39</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>-0.64</v>
+        <v>-0.85</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>19.62</v>
+        <v>19.31</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="M64" s="4" t="n">
         <v>4.95</v>
@@ -4655,13 +4655,13 @@
         <v>0.78</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>15.72</v>
+        <v>15.73</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>-0.82</v>
+        <v>1.55</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>19.2</v>
+        <v>19.22</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>1.8</v>
@@ -4719,19 +4719,19 @@
         <v>2.62</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>25.32</v>
+        <v>24.81</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>-2.54</v>
+        <v>-0.76</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>17.69</v>
+        <v>17.33</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="M66" s="8" t="n">
         <v>5.23</v>
@@ -4783,19 +4783,19 @@
         <v>1.07</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>25.32</v>
+        <v>25.15</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>-1.67</v>
+        <v>0.72</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>12.86</v>
+        <v>12.77</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>4.03</v>
@@ -4847,19 +4847,19 @@
         <v>1.03</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>18.26</v>
+        <v>17.48</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>-1.78</v>
+        <v>-2.4</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>16.17</v>
+        <v>15.48</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M68" s="8" t="n">
         <v>4.4</v>
@@ -4911,19 +4911,19 @@
         <v>0.8</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>22.47</v>
+        <v>22.23</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>-1.53</v>
+        <v>0.18</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>16.15</v>
+        <v>15.98</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>4.78</v>
@@ -4975,19 +4975,19 @@
         <v>0.27</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>22.62</v>
+        <v>22.15</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0.8</v>
+        <v>-1.42</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>15.87</v>
+        <v>15.54</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="M70" s="8" t="n">
         <v>3.08</v>
@@ -5039,19 +5039,19 @@
         <v>0.15</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>30.37</v>
+        <v>30.59</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>-1.46</v>
+        <v>1.53</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>13.73</v>
+        <v>13.83</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>4.59</v>
@@ -5103,19 +5103,19 @@
         <v>1.93</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>26.22</v>
+        <v>26.01</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>-0.61</v>
+        <v>-3.99</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>13.91</v>
+        <v>13.8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M72" s="4" t="n">
         <v>6.48</v>
@@ -5167,19 +5167,19 @@
         <v>0.41</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>13.23</v>
+        <v>13.37</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>-1.49</v>
+        <v>2.3</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>-37.75</v>
+        <v>-38.15</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>1.48</v>
@@ -5231,19 +5231,19 @@
         <v>3.69</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>111.12</v>
+        <v>116.12</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>2.3</v>
+        <v>4.88</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>20.71</v>
+        <v>21.64</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>6.69</v>
+        <v>6.99</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="M74" s="8" t="n">
         <v>0.9</v>
@@ -5295,19 +5295,19 @@
         <v>3.51</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>38.6</v>
+        <v>39.35</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>-1.28</v>
+        <v>3.8</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>12.86</v>
+        <v>13.11</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>4.54</v>
@@ -5359,19 +5359,19 @@
         <v>3.01</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>46.79</v>
+        <v>47.93</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>-0.06</v>
+        <v>5.18</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>26.84</v>
+        <v>27.49</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M76" s="8" t="n">
         <v>1.08</v>
@@ -5423,19 +5423,19 @@
         <v>2.14</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>50.9</v>
+        <v>50.74</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>-1.55</v>
+        <v>0.1</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>17.28</v>
+        <v>17.22</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>2.31</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>2.99</v>
@@ -5487,19 +5487,19 @@
         <v>1.66</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>59.59</v>
+        <v>69.66</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>2.46</v>
+        <v>13.47</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>57.18</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="K78" s="8" t="n">
-        <v>3.69</v>
+        <v>4.31</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="M78" s="8" t="n">
         <v>0.26</v>
@@ -5551,19 +5551,19 @@
         <v>1.45</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>43.42</v>
+        <v>44.31</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>0.51</v>
+        <v>2.38</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>27.95</v>
+        <v>28.53</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>5.16</v>
+        <v>5.27</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>1.39</v>
@@ -5615,10 +5615,10 @@
         <v>1.38</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>21.49</v>
+        <v>21.48</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>-1.83</v>
+        <v>0.42</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>11.86</v>
@@ -5679,16 +5679,16 @@
         <v>1.15</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>42.25</v>
+        <v>42.21</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>-0.19</v>
+        <v>3.28</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>19.96</v>
+        <v>19.94</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>7.79</v>
+        <v>7.78</v>
       </c>
       <c r="L81" s="13" t="n">
         <v>151</v>
@@ -5743,19 +5743,19 @@
         <v>0.96</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>4.91</v>
+        <v>4.99</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>-2.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J82" s="8" t="n">
-        <v>12.27</v>
+        <v>12.47</v>
       </c>
       <c r="K82" s="8" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M82" s="8" t="n">
         <v>3.88</v>
@@ -5807,19 +5807,19 @@
         <v>0.9</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>-2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>22.48</v>
+        <v>22.74</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>3.46</v>
@@ -5871,19 +5871,19 @@
         <v>0.89</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>15.45</v>
+        <v>15.59</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>-0.9</v>
+        <v>0.52</v>
       </c>
       <c r="J84" s="8" t="n">
-        <v>9.34</v>
+        <v>9.43</v>
       </c>
       <c r="K84" s="8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M84" s="8" t="n">
         <v>4.31</v>
@@ -5935,19 +5935,19 @@
         <v>0.87</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>32.66</v>
+        <v>32.42</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>-2.68</v>
+        <v>1.28</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>18.04</v>
+        <v>17.91</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>3.96</v>
@@ -5999,19 +5999,19 @@
         <v>0.84</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>8.6</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I86" s="8" t="n">
-        <v>-0.92</v>
+        <v>0.83</v>
       </c>
       <c r="J86" s="8" t="n">
-        <v>21.29</v>
+        <v>21.12</v>
       </c>
       <c r="K86" s="8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M86" s="8" t="n">
         <v>3.5</v>
@@ -6063,19 +6063,19 @@
         <v>0.67</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>46.55</v>
+        <v>48.14</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>-0.73</v>
+        <v>2.56</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>22.51</v>
+        <v>23.28</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>4.28</v>
+        <v>4.43</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>2.51</v>
@@ -6127,16 +6127,16 @@
         <v>0.65</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>6.76</v>
+        <v>6.79</v>
       </c>
       <c r="I88" s="8" t="n">
-        <v>-1.74</v>
+        <v>1.95</v>
       </c>
       <c r="J88" s="8" t="n">
-        <v>14.47</v>
+        <v>14.54</v>
       </c>
       <c r="K88" s="8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="L88" s="9" t="n">
         <v>47</v>
@@ -6191,19 +6191,19 @@
         <v>0.37</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>154.3</v>
+        <v>151.11</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>0.02</v>
+        <v>0.91</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>23.87</v>
+        <v>23.38</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>1871</v>
+        <v>1832</v>
       </c>
       <c r="M89" s="12" t="n">
         <v>1.83</v>
@@ -6255,16 +6255,16 @@
         <v>0.19</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>9.550000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="I90" s="8" t="n">
-        <v>-0.52</v>
+        <v>1.17</v>
       </c>
       <c r="J90" s="8" t="n">
-        <v>17.83</v>
+        <v>17.78</v>
       </c>
       <c r="K90" s="8" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L90" s="9" t="n">
         <v>50</v>
@@ -6319,16 +6319,16 @@
         <v>0.15</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>49.14</v>
+        <v>49.35</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>28.28</v>
+        <v>28.4</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="L91" s="13" t="n">
         <v>47</v>
@@ -6383,19 +6383,19 @@
         <v>0</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>10.11</v>
+        <v>10.25</v>
       </c>
       <c r="I92" s="8" t="n">
-        <v>-0.79</v>
+        <v>2.4</v>
       </c>
       <c r="J92" s="8" t="n">
-        <v>14.07</v>
+        <v>14.26</v>
       </c>
       <c r="K92" s="8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M92" s="8" t="n">
         <v>2.15</v>
@@ -6447,19 +6447,19 @@
         <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>4.61</v>
+        <v>4.72</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>-1.5</v>
+        <v>3.06</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>26.27</v>
+        <v>26.9</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>1.19</v>
@@ -6511,19 +6511,19 @@
         <v>0</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>5.39</v>
+        <v>5.41</v>
       </c>
       <c r="I94" s="8" t="n">
-        <v>-1.64</v>
+        <v>1.5</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>20.43</v>
+        <v>20.51</v>
       </c>
       <c r="K94" s="8" t="n">
         <v>1.21</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M94" s="8" t="n">
         <v>2.82</v>
@@ -6575,16 +6575,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>25.45</v>
+        <v>25.76</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>-0.93</v>
+        <v>1.54</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>12.87</v>
+        <v>13.03</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="L95" s="13" t="n">
         <v>60</v>
@@ -6639,16 +6639,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="I96" s="8" t="n">
-        <v>-0.9</v>
+        <v>1.37</v>
       </c>
       <c r="J96" s="8" t="n">
-        <v>12.8</v>
+        <v>12.83</v>
       </c>
       <c r="K96" s="8" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="L96" s="9" t="n">
         <v>88</v>
@@ -6703,19 +6703,19 @@
         <v>0</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>-1.34</v>
+        <v>3.07</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>44.75</v>
+        <v>45.97</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>3.06</v>
@@ -6767,13 +6767,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>11.32</v>
+        <v>11.28</v>
       </c>
       <c r="I98" s="8" t="n">
-        <v>-1.82</v>
+        <v>-0.27</v>
       </c>
       <c r="J98" s="8" t="n">
-        <v>23.75</v>
+        <v>23.66</v>
       </c>
       <c r="K98" s="8" t="n">
         <v>0.9</v>
@@ -6831,19 +6831,19 @@
         <v>0</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>19.75</v>
+        <v>20.19</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>7.57</v>
+        <v>2.96</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>95.37</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M99" s="12" t="n">
         <v>1.77</v>
@@ -6895,19 +6895,19 @@
         <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>12.01</v>
+        <v>13.11</v>
       </c>
       <c r="I100" s="8" t="n">
-        <v>-1.15</v>
+        <v>9.98</v>
       </c>
       <c r="J100" s="8" t="n">
-        <v>20.19</v>
+        <v>22.04</v>
       </c>
       <c r="K100" s="8" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="M100" s="8" t="n">
         <v>1.75</v>
@@ -6959,19 +6959,19 @@
         <v>0</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>12.56</v>
+        <v>12.36</v>
       </c>
       <c r="I101" s="12" t="n">
-        <v>-0.87</v>
+        <v>-0.24</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>24.13</v>
+        <v>23.74</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M101" s="12" t="n">
         <v>3.26</v>
@@ -7023,19 +7023,19 @@
         <v>1.13</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="I102" s="8" t="n">
-        <v>0</v>
+        <v>-1.06</v>
       </c>
       <c r="J102" s="8" t="n">
-        <v>15.49</v>
+        <v>15.11</v>
       </c>
       <c r="K102" s="8" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="M102" s="8" t="n">
         <v>3.91</v>
@@ -7087,19 +7087,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>9.84</v>
+        <v>9.49</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>-0.2</v>
+        <v>-2.37</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>32.41</v>
+        <v>31.26</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M103" s="12" t="n">
         <v>5</v>
@@ -7151,19 +7151,19 @@
         <v>0.59</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>20.65</v>
+        <v>20.18</v>
       </c>
       <c r="I104" s="8" t="n">
-        <v>-0.24</v>
+        <v>-1.27</v>
       </c>
       <c r="J104" s="8" t="n">
-        <v>12.67</v>
+        <v>12.38</v>
       </c>
       <c r="K104" s="8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M104" s="8" t="n">
         <v>0.75</v>
@@ -7215,19 +7215,19 @@
         <v>1.78</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>10.85</v>
+        <v>10.52</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>0.18</v>
+        <v>-1.87</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M105" s="12" t="n">
         <v>3.71</v>
@@ -7279,19 +7279,19 @@
         <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>4.64</v>
+        <v>4.59</v>
       </c>
       <c r="I106" s="8" t="n">
-        <v>-0.64</v>
+        <v>-0.43</v>
       </c>
       <c r="J106" s="8" t="n">
-        <v>13.53</v>
+        <v>13.38</v>
       </c>
       <c r="K106" s="8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M106" s="8" t="n">
         <v>2.31</v>
@@ -7343,19 +7343,19 @@
         <v>0</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>9.449999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I107" s="12" t="n">
-        <v>-1.25</v>
+        <v>-1.59</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>28.65</v>
+        <v>28.13</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="L107" s="13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M107" s="12" t="n">
         <v>3.28</v>
@@ -7407,19 +7407,19 @@
         <v>0</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>35.2</v>
+        <v>34.81</v>
       </c>
       <c r="I108" s="8" t="n">
-        <v>2.09</v>
+        <v>-0.26</v>
       </c>
       <c r="J108" s="8" t="n">
-        <v>23.43</v>
+        <v>23.17</v>
       </c>
       <c r="K108" s="8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>2649</v>
+        <v>2620</v>
       </c>
       <c r="M108" s="8" t="n">
         <v>1.04</v>
@@ -7471,19 +7471,19 @@
         <v>2.54</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>30.17</v>
+        <v>30.02</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>10.4</v>
+        <v>10.34</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="M109" s="12" t="n">
         <v>4.69</v>
@@ -7535,19 +7535,19 @@
         <v>1.69</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="I110" s="8" t="n">
-        <v>-0.68</v>
+        <v>-3.22</v>
       </c>
       <c r="J110" s="8" t="n">
-        <v>28.24</v>
+        <v>27.65</v>
       </c>
       <c r="K110" s="8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M110" s="8" t="n">
         <v>5.21</v>
@@ -7599,19 +7599,19 @@
         <v>1.47</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>7.93</v>
+        <v>7.88</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>-0.88</v>
+        <v>-0.25</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>9.34</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M111" s="12" t="n">
         <v>5.27</v>
@@ -7663,19 +7663,19 @@
         <v>0.93</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>4.66</v>
+        <v>4.56</v>
       </c>
       <c r="I112" s="8" t="n">
-        <v>-1.06</v>
+        <v>-1.51</v>
       </c>
       <c r="J112" s="8" t="n">
-        <v>12.99</v>
+        <v>12.71</v>
       </c>
       <c r="K112" s="8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M112" s="8" t="n">
         <v>8.02</v>
@@ -7727,19 +7727,19 @@
         <v>2.32</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>86.56999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>6.97</v>
+        <v>3.11</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>29.03</v>
+        <v>30.01</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>7.7</v>
+        <v>7.96</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>1358</v>
+        <v>1404</v>
       </c>
       <c r="M113" s="12" t="n">
         <v>3.1</v>
@@ -7791,19 +7791,19 @@
         <v>0.98</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>16.7</v>
+        <v>16.19</v>
       </c>
       <c r="I114" s="8" t="n">
-        <v>1.09</v>
+        <v>-2.35</v>
       </c>
       <c r="J114" s="8" t="n">
-        <v>53.41</v>
+        <v>51.78</v>
       </c>
       <c r="K114" s="8" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="M114" s="8" t="n">
         <v>0.61</v>
@@ -7855,19 +7855,19 @@
         <v>0.78</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>6.91</v>
+        <v>6.85</v>
       </c>
       <c r="I115" s="12" t="n">
         <v>-0.58</v>
       </c>
       <c r="J115" s="12" t="n">
-        <v>11.11</v>
+        <v>11.01</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M115" s="12" t="n">
         <v>6.42</v>
@@ -7919,19 +7919,19 @@
         <v>2.67</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>23.14</v>
+        <v>23.62</v>
       </c>
       <c r="I116" s="8" t="n">
-        <v>0.22</v>
+        <v>0.64</v>
       </c>
       <c r="J116" s="8" t="n">
-        <v>13.5</v>
+        <v>13.78</v>
       </c>
       <c r="K116" s="8" t="n">
-        <v>3.46</v>
+        <v>3.53</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>1697</v>
+        <v>1732</v>
       </c>
       <c r="M116" s="8" t="n">
         <v>3.01</v>
@@ -7983,19 +7983,19 @@
         <v>2.54</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>25.26</v>
+        <v>25.75</v>
       </c>
       <c r="I117" s="12" t="n">
-        <v>0.24</v>
+        <v>1.5</v>
       </c>
       <c r="J117" s="12" t="n">
-        <v>14.52</v>
+        <v>14.8</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>851</v>
+        <v>867</v>
       </c>
       <c r="M117" s="12" t="n">
         <v>1.97</v>
@@ -8047,19 +8047,19 @@
         <v>1.24</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>13</v>
+        <v>12.77</v>
       </c>
       <c r="I118" s="8" t="n">
-        <v>1.56</v>
+        <v>-0.62</v>
       </c>
       <c r="J118" s="8" t="n">
-        <v>26.57</v>
+        <v>26.1</v>
       </c>
       <c r="K118" s="8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="M118" s="8" t="n">
         <v>1.58</v>
@@ -8111,19 +8111,19 @@
         <v>0.46</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>74.45</v>
+        <v>75.53</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>17.71</v>
+        <v>17.96</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>2331</v>
+        <v>2364</v>
       </c>
       <c r="M119" s="12" t="n">
         <v>1.68</v>
@@ -8175,16 +8175,16 @@
         <v>0.05</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>20.31</v>
+        <v>20.6</v>
       </c>
       <c r="I120" s="8" t="n">
-        <v>2.47</v>
+        <v>0.49</v>
       </c>
       <c r="J120" s="8" t="n">
-        <v>14.15</v>
+        <v>14.35</v>
       </c>
       <c r="K120" s="8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="L120" s="9" t="n">
         <v>33</v>
@@ -8239,19 +8239,19 @@
         <v>0</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>11.67</v>
+        <v>11.55</v>
       </c>
       <c r="I121" s="12" t="n">
-        <v>1.13</v>
+        <v>0.17</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>11.16</v>
+        <v>11.05</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M121" s="12" t="n">
         <v>6.26</v>
@@ -8303,19 +8303,19 @@
         <v>0</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>18.6</v>
+        <v>18.38</v>
       </c>
       <c r="I122" s="8" t="n">
-        <v>4.26</v>
+        <v>-1.24</v>
       </c>
       <c r="J122" s="8" t="n">
-        <v>16.5</v>
+        <v>16.31</v>
       </c>
       <c r="K122" s="8" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M122" s="8" t="n">
         <v>1.61</v>
@@ -8367,13 +8367,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>13.26</v>
+        <v>13.24</v>
       </c>
       <c r="I123" s="12" t="n">
-        <v>1.92</v>
+        <v>1.07</v>
       </c>
       <c r="J123" s="12" t="n">
-        <v>21.9</v>
+        <v>21.86</v>
       </c>
       <c r="K123" s="12" t="n">
         <v>1.36</v>
@@ -8431,19 +8431,19 @@
         <v>10.26</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>40.27</v>
+        <v>40.11</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>-0.62</v>
+        <v>-0.35</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>7.73</v>
+        <v>7.7</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>1.48</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>2256</v>
+        <v>2247</v>
       </c>
       <c r="M124" s="4" t="n">
         <v>7.09</v>
@@ -8495,19 +8495,19 @@
         <v>1.78</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>85.47</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>0.39</v>
+        <v>-2.38</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>14.75</v>
+        <v>14.38</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>6520</v>
+        <v>6354</v>
       </c>
       <c r="M125" s="4" t="n">
         <v>4.91</v>
@@ -8559,19 +8559,19 @@
         <v>1.69</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>41.52</v>
+        <v>41.01</v>
       </c>
       <c r="I126" s="8" t="n">
-        <v>-1.33</v>
+        <v>-0.77</v>
       </c>
       <c r="J126" s="8" t="n">
-        <v>16.41</v>
+        <v>16.2</v>
       </c>
       <c r="K126" s="8" t="n">
-        <v>6.58</v>
+        <v>6.5</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M126" s="8" t="n">
         <v>6.03</v>
@@ -8623,19 +8623,19 @@
         <v>1.28</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>15.71</v>
+        <v>15.24</v>
       </c>
       <c r="I127" s="12" t="n">
-        <v>-0.63</v>
+        <v>-1.3</v>
       </c>
       <c r="J127" s="12" t="n">
-        <v>12.14</v>
+        <v>11.78</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M127" s="12" t="n">
         <v>6.27</v>
@@ -8687,19 +8687,19 @@
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>22.34</v>
+        <v>21.93</v>
       </c>
       <c r="I128" s="8" t="n">
-        <v>-0.67</v>
+        <v>-0.86</v>
       </c>
       <c r="J128" s="8" t="n">
-        <v>11.19</v>
+        <v>10.99</v>
       </c>
       <c r="K128" s="8" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>2095</v>
+        <v>2057</v>
       </c>
       <c r="M128" s="8" t="n">
         <v>1.16</v>
@@ -8751,16 +8751,16 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="I129" s="12" t="n">
-        <v>-0.6</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J129" s="12" t="n">
-        <v>17.15</v>
+        <v>16.95</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="L129" s="13" t="n">
         <v>51</v>
@@ -8815,19 +8815,19 @@
         <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>27.22</v>
+        <v>26.42</v>
       </c>
       <c r="I130" s="8" t="n">
-        <v>1.57</v>
+        <v>-1.64</v>
       </c>
       <c r="J130" s="8" t="n">
-        <v>12.18</v>
+        <v>11.83</v>
       </c>
       <c r="K130" s="8" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="M130" s="8" t="n">
         <v>4.52</v>
@@ -8879,19 +8879,19 @@
         <v>0</v>
       </c>
       <c r="H131" s="12" t="n">
-        <v>27.23</v>
+        <v>25.18</v>
       </c>
       <c r="I131" s="12" t="n">
-        <v>-0.26</v>
+        <v>-1.1</v>
       </c>
       <c r="J131" s="12" t="n">
-        <v>14.26</v>
+        <v>13.19</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="M131" s="12" t="n">
         <v>3.23</v>
@@ -8943,19 +8943,19 @@
         <v>1.91</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-1.29</v>
+        <v>-1.09</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>0.39</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>1892</v>
+        <v>1868</v>
       </c>
       <c r="M132" s="4" t="n">
         <v>5.78</v>
@@ -9007,19 +9007,19 @@
         <v>2.1</v>
       </c>
       <c r="H133" s="12" t="n">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="I133" s="12" t="n">
-        <v>-1.28</v>
+        <v>-1.3</v>
       </c>
       <c r="J133" s="12" t="n">
-        <v>5.15</v>
+        <v>5.03</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M133" s="12" t="n">
         <v>5.65</v>
@@ -9071,19 +9071,19 @@
         <v>2.41</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>8.609999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="I134" s="8" t="n">
-        <v>-1.03</v>
+        <v>-2.34</v>
       </c>
       <c r="J134" s="8" t="n">
-        <v>10.67</v>
+        <v>10.33</v>
       </c>
       <c r="K134" s="8" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>749</v>
+        <v>725</v>
       </c>
       <c r="M134" s="8" t="n">
         <v>5.45</v>
@@ -9135,19 +9135,19 @@
         <v>1.93</v>
       </c>
       <c r="H135" s="12" t="n">
-        <v>5.47</v>
+        <v>5.4</v>
       </c>
       <c r="I135" s="12" t="n">
-        <v>-2.15</v>
+        <v>-0.55</v>
       </c>
       <c r="J135" s="12" t="n">
-        <v>7.89</v>
+        <v>7.79</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M135" s="12" t="n">
         <v>7.43</v>
@@ -9199,19 +9199,19 @@
         <v>1.42</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>6.21</v>
+        <v>6.16</v>
       </c>
       <c r="I136" s="8" t="n">
-        <v>-0.64</v>
+        <v>-0.65</v>
       </c>
       <c r="J136" s="8" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="K136" s="8" t="n">
         <v>0.31</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="M136" s="8" t="n">
         <v>4.68</v>
@@ -9263,19 +9263,19 @@
         <v>1.66</v>
       </c>
       <c r="H137" s="12" t="n">
-        <v>5.17</v>
+        <v>5.07</v>
       </c>
       <c r="I137" s="12" t="n">
-        <v>-0.39</v>
+        <v>-0.78</v>
       </c>
       <c r="J137" s="12" t="n">
-        <v>16.93</v>
+        <v>16.6</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M137" s="12" t="n">
         <v>4.02</v>
@@ -9327,19 +9327,19 @@
         <v>1.38</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>7.82</v>
+        <v>7.8</v>
       </c>
       <c r="I138" s="8" t="n">
-        <v>-1.01</v>
+        <v>-0.13</v>
       </c>
       <c r="J138" s="8" t="n">
-        <v>7.73</v>
+        <v>7.71</v>
       </c>
       <c r="K138" s="8" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="L138" s="9" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M138" s="8" t="n">
         <v>6.02</v>
@@ -9391,19 +9391,19 @@
         <v>1.16</v>
       </c>
       <c r="H139" s="12" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="I139" s="12" t="n">
-        <v>-0.66</v>
+        <v>-0.22</v>
       </c>
       <c r="J139" s="12" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="M139" s="12" t="n">
         <v>3.64</v>
@@ -9455,19 +9455,19 @@
         <v>1.01</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>6.14</v>
+        <v>6.06</v>
       </c>
       <c r="I140" s="8" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="J140" s="8" t="n">
-        <v>7.44</v>
+        <v>7.34</v>
       </c>
       <c r="K140" s="8" t="n">
         <v>0.34</v>
       </c>
       <c r="L140" s="9" t="n">
-        <v>996</v>
+        <v>983</v>
       </c>
       <c r="M140" s="8" t="n">
         <v>3.09</v>
@@ -9519,19 +9519,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H141" s="12" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="I141" s="12" t="n">
-        <v>-1.65</v>
+        <v>-0.85</v>
       </c>
       <c r="J141" s="12" t="n">
-        <v>9.84</v>
+        <v>9.68</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M141" s="12" t="n">
         <v>3.05</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="I142" s="8" t="n">
-        <v>1.53</v>
+        <v>-1.75</v>
       </c>
       <c r="J142" s="8" t="n">
-        <v>26.05</v>
+        <v>25.72</v>
       </c>
       <c r="K142" s="8" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="L142" s="9" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M142" s="8" t="n">
         <v>3.27</v>
@@ -9647,19 +9647,19 @@
         <v>0</v>
       </c>
       <c r="H143" s="12" t="n">
-        <v>7.3</v>
+        <v>7.11</v>
       </c>
       <c r="I143" s="12" t="n">
-        <v>-1.08</v>
+        <v>-1.93</v>
       </c>
       <c r="J143" s="12" t="n">
-        <v>34.55</v>
+        <v>33.65</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M143" s="12" t="n">
         <v>0.68</v>
@@ -9711,19 +9711,19 @@
         <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="I144" s="8" t="n">
-        <v>-1.26</v>
+        <v>-1.29</v>
       </c>
       <c r="J144" s="8" t="n">
-        <v>14.73</v>
+        <v>14.42</v>
       </c>
       <c r="K144" s="8" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="L144" s="9" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="M144" s="8" t="n">
         <v>1.49</v>
@@ -9775,10 +9775,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="12" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="I145" s="12" t="n">
-        <v>0.13</v>
+        <v>-0.9</v>
       </c>
       <c r="J145" s="12" t="n">
         <v>7.21</v>
@@ -9839,13 +9839,13 @@
         <v>1.87</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>7.41</v>
+        <v>7.43</v>
       </c>
       <c r="I146" s="8" t="n">
-        <v>-0.4</v>
+        <v>-2.49</v>
       </c>
       <c r="J146" s="8" t="n">
-        <v>20.81</v>
+        <v>20.87</v>
       </c>
       <c r="K146" s="8" t="n">
         <v>0.74</v>
@@ -9903,19 +9903,19 @@
         <v>5.27</v>
       </c>
       <c r="H147" s="12" t="n">
-        <v>13.75</v>
+        <v>14.39</v>
       </c>
       <c r="I147" s="12" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="J147" s="12" t="n">
-        <v>22.61</v>
+        <v>23.66</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="L147" s="13" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="M147" s="12" t="n">
         <v>3.63</v>
@@ -9967,19 +9967,19 @@
         <v>1.5</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>17.74</v>
+        <v>17.78</v>
       </c>
       <c r="I148" s="8" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="J148" s="8" t="n">
-        <v>12.05</v>
+        <v>12.08</v>
       </c>
       <c r="K148" s="8" t="n">
         <v>0.49</v>
       </c>
       <c r="L148" s="9" t="n">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="M148" s="8" t="n">
         <v>4.58</v>
@@ -10031,19 +10031,19 @@
         <v>0.86</v>
       </c>
       <c r="H149" s="12" t="n">
-        <v>12.82</v>
+        <v>12.4</v>
       </c>
       <c r="I149" s="12" t="n">
-        <v>-0.47</v>
+        <v>-1.98</v>
       </c>
       <c r="J149" s="12" t="n">
-        <v>14.2</v>
+        <v>13.73</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="L149" s="13" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M149" s="12" t="n">
         <v>4.49</v>
@@ -10095,19 +10095,19 @@
         <v>0.96</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>7.79</v>
+        <v>7.67</v>
       </c>
       <c r="I150" s="8" t="n">
-        <v>-0.13</v>
+        <v>-0.52</v>
       </c>
       <c r="J150" s="8" t="n">
-        <v>7.64</v>
+        <v>7.52</v>
       </c>
       <c r="K150" s="8" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L150" s="9" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M150" s="8" t="n">
         <v>4.05</v>
@@ -10159,19 +10159,19 @@
         <v>2.18</v>
       </c>
       <c r="H151" s="12" t="n">
-        <v>18.46</v>
+        <v>18.35</v>
       </c>
       <c r="I151" s="12" t="n">
-        <v>-0.75</v>
+        <v>-0.33</v>
       </c>
       <c r="J151" s="12" t="n">
-        <v>15.54</v>
+        <v>15.45</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="L151" s="13" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M151" s="12" t="n">
         <v>5.57</v>
@@ -10223,13 +10223,13 @@
         <v>0.42</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="I152" s="8" t="n">
-        <v>-0.59</v>
+        <v>-1.75</v>
       </c>
       <c r="J152" s="8" t="n">
-        <v>39.18</v>
+        <v>39.29</v>
       </c>
       <c r="K152" s="8" t="n">
         <v>0.5600000000000001</v>
@@ -10287,19 +10287,19 @@
         <v>1.1</v>
       </c>
       <c r="H153" s="12" t="n">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="I153" s="12" t="n">
-        <v>0.78</v>
+        <v>0.57</v>
       </c>
       <c r="J153" s="12" t="n">
-        <v>244.89</v>
+        <v>252.02</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="L153" s="13" t="n">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="M153" s="12" t="n">
         <v>3.88</v>
@@ -10351,19 +10351,19 @@
         <v>2.41</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>41.02</v>
+        <v>42.77</v>
       </c>
       <c r="I154" s="8" t="n">
-        <v>7.35</v>
+        <v>7.65</v>
       </c>
       <c r="J154" s="8" t="n">
-        <v>16.45</v>
+        <v>17.15</v>
       </c>
       <c r="K154" s="8" t="n">
-        <v>4.36</v>
+        <v>4.55</v>
       </c>
       <c r="L154" s="9" t="n">
-        <v>978</v>
+        <v>1019</v>
       </c>
       <c r="M154" s="8" t="n">
         <v>0.26</v>
@@ -10415,19 +10415,19 @@
         <v>2.31</v>
       </c>
       <c r="H155" s="12" t="n">
-        <v>13.46</v>
+        <v>13.53</v>
       </c>
       <c r="I155" s="12" t="n">
-        <v>2.28</v>
+        <v>0.97</v>
       </c>
       <c r="J155" s="12" t="n">
-        <v>10.42</v>
+        <v>10.48</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="L155" s="13" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="M155" s="12" t="n">
         <v>4.17</v>
@@ -10479,19 +10479,19 @@
         <v>2</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>24.22</v>
+        <v>26.15</v>
       </c>
       <c r="I156" s="8" t="n">
-        <v>7.36</v>
+        <v>2.71</v>
       </c>
       <c r="J156" s="8" t="n">
-        <v>18.29</v>
+        <v>19.75</v>
       </c>
       <c r="K156" s="8" t="n">
-        <v>4.54</v>
+        <v>4.9</v>
       </c>
       <c r="L156" s="9" t="n">
-        <v>672</v>
+        <v>725</v>
       </c>
       <c r="M156" s="8" t="n">
         <v>2.05</v>
@@ -10543,19 +10543,19 @@
         <v>2.52</v>
       </c>
       <c r="H157" s="12" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="I157" s="12" t="n">
-        <v>1.99</v>
+        <v>1.37</v>
       </c>
       <c r="J157" s="12" t="n">
-        <v>8.56</v>
+        <v>8.73</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="L157" s="13" t="n">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="M157" s="12" t="n">
         <v>3.07</v>
@@ -10607,19 +10607,19 @@
         <v>6.45</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I158" s="8" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="J158" s="8" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="K158" s="8" t="n">
         <v>2.08</v>
       </c>
       <c r="L158" s="9" t="n">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="M158" s="8" t="n">
         <v>2.7</v>
@@ -10671,19 +10671,19 @@
         <v>1.25</v>
       </c>
       <c r="H159" s="12" t="n">
-        <v>48.06</v>
+        <v>48.5</v>
       </c>
       <c r="I159" s="12" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="J159" s="12" t="n">
-        <v>27.01</v>
+        <v>27.26</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="L159" s="13" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M159" s="12" t="n">
         <v>1.55</v>
@@ -10735,16 +10735,16 @@
         <v>0.34</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>5.16</v>
+        <v>5.09</v>
       </c>
       <c r="I160" s="8" t="n">
-        <v>-1.15</v>
+        <v>-1.17</v>
       </c>
       <c r="J160" s="8" t="n">
-        <v>17.33</v>
+        <v>17.09</v>
       </c>
       <c r="K160" s="8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="L160" s="9" t="n">
         <v>64</v>
@@ -10799,19 +10799,19 @@
         <v>2.8</v>
       </c>
       <c r="H161" s="12" t="n">
-        <v>43.27</v>
+        <v>46.77</v>
       </c>
       <c r="I161" s="12" t="n">
-        <v>9.99</v>
+        <v>3.91</v>
       </c>
       <c r="J161" s="12" t="n">
-        <v>28.6</v>
+        <v>30.91</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>9.6</v>
+        <v>10.38</v>
       </c>
       <c r="L161" s="13" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M161" s="12" t="n">
         <v>1.25</v>
@@ -10863,19 +10863,19 @@
         <v>2.65</v>
       </c>
       <c r="H162" s="8" t="n">
-        <v>23.02</v>
+        <v>23.53</v>
       </c>
       <c r="I162" s="8" t="n">
-        <v>4.87</v>
+        <v>2.89</v>
       </c>
       <c r="J162" s="8" t="n">
-        <v>21.14</v>
+        <v>21.61</v>
       </c>
       <c r="K162" s="8" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="L162" s="9" t="n">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="M162" s="8" t="n">
         <v>3.81</v>
@@ -10927,13 +10927,13 @@
         <v>2.5</v>
       </c>
       <c r="H163" s="12" t="n">
-        <v>11.5</v>
+        <v>11.46</v>
       </c>
       <c r="I163" s="12" t="n">
-        <v>1.05</v>
+        <v>0.35</v>
       </c>
       <c r="J163" s="12" t="n">
-        <v>9.65</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K163" s="12" t="n">
         <v>1.87</v>
@@ -10991,19 +10991,19 @@
         <v>0.14</v>
       </c>
       <c r="H164" s="8" t="n">
-        <v>18.34</v>
+        <v>18.83</v>
       </c>
       <c r="I164" s="8" t="n">
-        <v>7.19</v>
+        <v>-1.98</v>
       </c>
       <c r="J164" s="8" t="n">
-        <v>27.45</v>
+        <v>26.38</v>
       </c>
       <c r="K164" s="8" t="n">
-        <v>5.63</v>
+        <v>5.43</v>
       </c>
       <c r="L164" s="9" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M164" s="8" t="n">
         <v>2.67</v>
@@ -11055,19 +11055,19 @@
         <v>1.43</v>
       </c>
       <c r="H165" s="12" t="n">
-        <v>16.04</v>
+        <v>15.83</v>
       </c>
       <c r="I165" s="12" t="n">
-        <v>0.31</v>
+        <v>-1.37</v>
       </c>
       <c r="J165" s="12" t="n">
-        <v>6.99</v>
+        <v>6.9</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="L165" s="13" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M165" s="12" t="n">
         <v>7.74</v>
@@ -11119,16 +11119,16 @@
         <v>1.41</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>17.15</v>
+        <v>17.04</v>
       </c>
       <c r="I166" s="8" t="n">
-        <v>0.35</v>
+        <v>0.71</v>
       </c>
       <c r="J166" s="8" t="n">
-        <v>9.43</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K166" s="8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="L166" s="9" t="n">
         <v>79</v>
@@ -11183,19 +11183,19 @@
         <v>1.64</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>-1.43</v>
+        <v>-0.83</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>13.88</v>
+        <v>13.73</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M167" s="4" t="n">
         <v>6.09</v>
@@ -11247,19 +11247,19 @@
         <v>1.62</v>
       </c>
       <c r="H168" s="8" t="n">
-        <v>7.29</v>
+        <v>7.2</v>
       </c>
       <c r="I168" s="8" t="n">
-        <v>-0.68</v>
+        <v>-0.96</v>
       </c>
       <c r="J168" s="8" t="n">
-        <v>14.55</v>
+        <v>14.37</v>
       </c>
       <c r="K168" s="8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="L168" s="9" t="n">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="M168" s="8" t="n">
         <v>5.26</v>
@@ -11311,19 +11311,19 @@
         <v>1.39</v>
       </c>
       <c r="H169" s="12" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="I169" s="12" t="n">
-        <v>-1.38</v>
+        <v>-0.2</v>
       </c>
       <c r="J169" s="12" t="n">
-        <v>14.52</v>
+        <v>14.32</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="L169" s="13" t="n">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="M169" s="12" t="n">
         <v>3.33</v>
@@ -11375,19 +11375,19 @@
         <v>1.1</v>
       </c>
       <c r="H170" s="8" t="n">
-        <v>5.95</v>
+        <v>5.88</v>
       </c>
       <c r="I170" s="8" t="n">
-        <v>-1.33</v>
+        <v>-0.84</v>
       </c>
       <c r="J170" s="8" t="n">
-        <v>12.64</v>
+        <v>12.49</v>
       </c>
       <c r="K170" s="8" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="L170" s="9" t="n">
-        <v>1708</v>
+        <v>1687</v>
       </c>
       <c r="M170" s="8" t="n">
         <v>5.19</v>
@@ -11439,19 +11439,19 @@
         <v>2.39</v>
       </c>
       <c r="H171" s="12" t="n">
-        <v>9.470000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I171" s="12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.86</v>
       </c>
       <c r="J171" s="12" t="n">
-        <v>23.59</v>
+        <v>23.66</v>
       </c>
       <c r="K171" s="12" t="n">
         <v>1.85</v>
       </c>
       <c r="L171" s="13" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M171" s="12" t="n">
         <v>3.23</v>
@@ -11503,19 +11503,19 @@
         <v>1.57</v>
       </c>
       <c r="H172" s="8" t="n">
-        <v>51.78</v>
+        <v>52.03</v>
       </c>
       <c r="I172" s="8" t="n">
-        <v>2.74</v>
+        <v>0.48</v>
       </c>
       <c r="J172" s="8" t="n">
-        <v>23.85</v>
+        <v>23.96</v>
       </c>
       <c r="K172" s="8" t="n">
-        <v>9.550000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L172" s="9" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M172" s="8" t="n">
         <v>3.53</v>
@@ -11567,19 +11567,19 @@
         <v>1.11</v>
       </c>
       <c r="H173" s="12" t="n">
-        <v>15.54</v>
+        <v>15.33</v>
       </c>
       <c r="I173" s="12" t="n">
-        <v>-0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J173" s="12" t="n">
-        <v>18.87</v>
+        <v>18.61</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>5.69</v>
+        <v>5.62</v>
       </c>
       <c r="L173" s="13" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M173" s="12" t="n">
         <v>4.42</v>
@@ -11631,19 +11631,19 @@
         <v>1.04</v>
       </c>
       <c r="H174" s="8" t="n">
-        <v>311.17</v>
+        <v>340</v>
       </c>
       <c r="I174" s="8" t="n">
-        <v>3.28</v>
+        <v>7.8</v>
       </c>
       <c r="J174" s="8" t="n">
-        <v>86.88</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="K174" s="8" t="n">
-        <v>12.75</v>
+        <v>13.93</v>
       </c>
       <c r="L174" s="9" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="M174" s="8" t="n">
         <v>0.32</v>
@@ -11695,13 +11695,13 @@
         <v>0.29</v>
       </c>
       <c r="H175" s="12" t="n">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="I175" s="12" t="n">
-        <v>0.9</v>
+        <v>-0.28</v>
       </c>
       <c r="J175" s="12" t="n">
-        <v>17.44</v>
+        <v>17.46</v>
       </c>
       <c r="K175" s="12" t="n">
         <v>2.76</v>
@@ -11759,19 +11759,19 @@
         <v>0.24</v>
       </c>
       <c r="H176" s="8" t="n">
-        <v>13.69</v>
+        <v>13.33</v>
       </c>
       <c r="I176" s="8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="J176" s="8" t="n">
-        <v>19.61</v>
+        <v>19.09</v>
       </c>
       <c r="K176" s="8" t="n">
-        <v>6.21</v>
+        <v>6.04</v>
       </c>
       <c r="L176" s="9" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M176" s="8" t="n">
         <v>3.33</v>
@@ -11823,16 +11823,16 @@
         <v>0.06</v>
       </c>
       <c r="H177" s="12" t="n">
-        <v>20.37</v>
+        <v>20.49</v>
       </c>
       <c r="I177" s="12" t="n">
-        <v>3.93</v>
+        <v>0.1</v>
       </c>
       <c r="J177" s="12" t="n">
-        <v>46.28</v>
+        <v>46.55</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="L177" s="13" t="n">
         <v>33</v>
@@ -11887,19 +11887,19 @@
         <v>0</v>
       </c>
       <c r="H178" s="8" t="n">
-        <v>8.68</v>
+        <v>8.56</v>
       </c>
       <c r="I178" s="8" t="n">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="J178" s="8" t="n">
-        <v>-410.52</v>
+        <v>-404.85</v>
       </c>
       <c r="K178" s="8" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L178" s="9" t="n">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="M178" s="8" t="n">
         <v>0</v>
@@ -11951,19 +11951,19 @@
         <v>0</v>
       </c>
       <c r="H179" s="12" t="n">
-        <v>13.53</v>
+        <v>13.49</v>
       </c>
       <c r="I179" s="12" t="n">
-        <v>2.97</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J179" s="12" t="n">
-        <v>19.31</v>
+        <v>19.25</v>
       </c>
       <c r="K179" s="12" t="n">
         <v>2.17</v>
       </c>
       <c r="L179" s="13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M179" s="12" t="n">
         <v>0.44</v>
@@ -12015,16 +12015,16 @@
         <v>0</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="I180" s="8" t="n">
-        <v>-0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J180" s="8" t="n">
-        <v>17.04</v>
+        <v>16.94</v>
       </c>
       <c r="K180" s="8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="L180" s="9" t="n">
         <v>104</v>
@@ -12079,19 +12079,19 @@
         <v>0</v>
       </c>
       <c r="H181" s="12" t="n">
-        <v>7.46</v>
+        <v>7.37</v>
       </c>
       <c r="I181" s="12" t="n">
-        <v>0.95</v>
+        <v>-1.34</v>
       </c>
       <c r="J181" s="12" t="n">
-        <v>17.98</v>
+        <v>17.76</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="L181" s="13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M181" s="12" t="n">
         <v>1.61</v>
@@ -12143,19 +12143,19 @@
         <v>0</v>
       </c>
       <c r="H182" s="8" t="n">
-        <v>10.72</v>
+        <v>10.52</v>
       </c>
       <c r="I182" s="8" t="n">
-        <v>3.18</v>
+        <v>-0.47</v>
       </c>
       <c r="J182" s="8" t="n">
-        <v>17.75</v>
+        <v>17.42</v>
       </c>
       <c r="K182" s="8" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="L182" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M182" s="8" t="n">
         <v>2.33</v>
@@ -12207,19 +12207,19 @@
         <v>0</v>
       </c>
       <c r="H183" s="12" t="n">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="I183" s="12" t="n">
-        <v>-0.7</v>
+        <v>-0.95</v>
       </c>
       <c r="J183" s="12" t="n">
-        <v>26.26</v>
+        <v>25.64</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="L183" s="13" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M183" s="12" t="n">
         <v>1.76</v>
@@ -12271,16 +12271,16 @@
         <v>0</v>
       </c>
       <c r="H184" s="8" t="n">
-        <v>5.36</v>
+        <v>5.32</v>
       </c>
       <c r="I184" s="8" t="n">
-        <v>4.28</v>
+        <v>-1.85</v>
       </c>
       <c r="J184" s="8" t="n">
-        <v>19.93</v>
+        <v>19.78</v>
       </c>
       <c r="K184" s="8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="L184" s="9" t="n">
         <v>51</v>
@@ -12335,19 +12335,19 @@
         <v>0</v>
       </c>
       <c r="H185" s="12" t="n">
-        <v>32.38</v>
+        <v>31.61</v>
       </c>
       <c r="I185" s="12" t="n">
-        <v>0.4</v>
+        <v>-1.47</v>
       </c>
       <c r="J185" s="12" t="n">
-        <v>13.02</v>
+        <v>12.71</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="L185" s="13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M185" s="12" t="n">
         <v>2.53</v>
@@ -12399,19 +12399,19 @@
         <v>0</v>
       </c>
       <c r="H186" s="8" t="n">
-        <v>13.06</v>
+        <v>12.8</v>
       </c>
       <c r="I186" s="8" t="n">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="J186" s="8" t="n">
-        <v>15.77</v>
+        <v>15.46</v>
       </c>
       <c r="K186" s="8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="L186" s="9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M186" s="8" t="n">
         <v>6.13</v>
@@ -12463,19 +12463,19 @@
         <v>1.2</v>
       </c>
       <c r="H187" s="12" t="n">
-        <v>8.41</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I187" s="12" t="n">
-        <v>-0.36</v>
+        <v>-1.54</v>
       </c>
       <c r="J187" s="12" t="n">
-        <v>14.95</v>
+        <v>14.73</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="L187" s="13" t="n">
-        <v>985</v>
+        <v>971</v>
       </c>
       <c r="M187" s="12" t="n">
         <v>2.23</v>
@@ -12527,19 +12527,19 @@
         <v>1.76</v>
       </c>
       <c r="H188" s="8" t="n">
-        <v>16.09</v>
+        <v>16</v>
       </c>
       <c r="I188" s="8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="J188" s="8" t="n">
-        <v>7.07</v>
+        <v>7.03</v>
       </c>
       <c r="K188" s="8" t="n">
         <v>0.78</v>
       </c>
       <c r="L188" s="9" t="n">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="M188" s="8" t="n">
         <v>5.93</v>
@@ -12591,19 +12591,19 @@
         <v>9.31</v>
       </c>
       <c r="H189" s="12" t="n">
-        <v>15.97</v>
+        <v>15.57</v>
       </c>
       <c r="I189" s="12" t="n">
-        <v>-0.62</v>
+        <v>-0.95</v>
       </c>
       <c r="J189" s="12" t="n">
-        <v>15.08</v>
+        <v>14.7</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="L189" s="13" t="n">
-        <v>1366</v>
+        <v>1332</v>
       </c>
       <c r="M189" s="12" t="n">
         <v>2.08</v>
@@ -12655,19 +12655,19 @@
         <v>5.6</v>
       </c>
       <c r="H190" s="8" t="n">
-        <v>10.86</v>
+        <v>10.43</v>
       </c>
       <c r="I190" s="8" t="n">
-        <v>-1.09</v>
+        <v>-0.76</v>
       </c>
       <c r="J190" s="8" t="n">
-        <v>12.35</v>
+        <v>11.86</v>
       </c>
       <c r="K190" s="8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="L190" s="9" t="n">
-        <v>1248</v>
+        <v>1199</v>
       </c>
       <c r="M190" s="8" t="n">
         <v>0</v>
@@ -12719,19 +12719,19 @@
         <v>3.35</v>
       </c>
       <c r="H191" s="12" t="n">
-        <v>30.22</v>
+        <v>30.07</v>
       </c>
       <c r="I191" s="12" t="n">
-        <v>5.52</v>
+        <v>2.35</v>
       </c>
       <c r="J191" s="12" t="n">
-        <v>23.1</v>
+        <v>22.98</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L191" s="13" t="n">
-        <v>2611</v>
+        <v>2598</v>
       </c>
       <c r="M191" s="12" t="n">
         <v>1.18</v>
@@ -12783,19 +12783,19 @@
         <v>2.25</v>
       </c>
       <c r="H192" s="8" t="n">
-        <v>246.48</v>
+        <v>253.76</v>
       </c>
       <c r="I192" s="8" t="n">
-        <v>-0.01</v>
+        <v>0.43</v>
       </c>
       <c r="J192" s="8" t="n">
-        <v>29.65</v>
+        <v>30.53</v>
       </c>
       <c r="K192" s="8" t="n">
-        <v>7.43</v>
+        <v>7.65</v>
       </c>
       <c r="L192" s="9" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="M192" s="8" t="n">
         <v>1.19</v>
@@ -12847,19 +12847,19 @@
         <v>0.82</v>
       </c>
       <c r="H193" s="12" t="n">
-        <v>7.56</v>
+        <v>7.34</v>
       </c>
       <c r="I193" s="12" t="n">
-        <v>-0.79</v>
+        <v>-0.54</v>
       </c>
       <c r="J193" s="12" t="n">
-        <v>24.39</v>
+        <v>23.68</v>
       </c>
       <c r="K193" s="12" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="L193" s="13" t="n">
-        <v>749</v>
+        <v>728</v>
       </c>
       <c r="M193" s="12" t="n">
         <v>2.12</v>
@@ -12911,13 +12911,13 @@
         <v>0.7</v>
       </c>
       <c r="H194" s="8" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="I194" s="8" t="n">
-        <v>-0.92</v>
+        <v>0.47</v>
       </c>
       <c r="J194" s="8" t="n">
-        <v>9.17</v>
+        <v>9.1</v>
       </c>
       <c r="K194" s="8" t="n">
         <v>0.74</v>
@@ -12975,19 +12975,19 @@
         <v>0</v>
       </c>
       <c r="H195" s="12" t="n">
-        <v>14.57</v>
+        <v>13.72</v>
       </c>
       <c r="I195" s="12" t="n">
-        <v>1.32</v>
+        <v>-2.07</v>
       </c>
       <c r="J195" s="12" t="n">
-        <v>18.56</v>
+        <v>17.48</v>
       </c>
       <c r="K195" s="12" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="L195" s="13" t="n">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="M195" s="12" t="n">
         <v>4.76</v>
@@ -13039,19 +13039,19 @@
         <v>0</v>
       </c>
       <c r="H196" s="8" t="n">
-        <v>10.27</v>
+        <v>10.14</v>
       </c>
       <c r="I196" s="8" t="n">
-        <v>-0.39</v>
+        <v>-0.59</v>
       </c>
       <c r="J196" s="8" t="n">
-        <v>15.91</v>
+        <v>15.71</v>
       </c>
       <c r="K196" s="8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="L196" s="9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M196" s="8" t="n">
         <v>0.97</v>
@@ -13103,16 +13103,16 @@
         <v>0</v>
       </c>
       <c r="H197" s="12" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="I197" s="12" t="n">
-        <v>-0.98</v>
+        <v>-1.78</v>
       </c>
       <c r="J197" s="12" t="n">
-        <v>19.64</v>
+        <v>19.33</v>
       </c>
       <c r="K197" s="12" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="L197" s="13" t="n">
         <v>44</v>
@@ -13167,19 +13167,19 @@
         <v>0</v>
       </c>
       <c r="H198" s="8" t="n">
-        <v>8.18</v>
+        <v>7.94</v>
       </c>
       <c r="I198" s="8" t="n">
-        <v>-0.49</v>
+        <v>-0.87</v>
       </c>
       <c r="J198" s="8" t="n">
-        <v>17.38</v>
+        <v>16.87</v>
       </c>
       <c r="K198" s="8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="L198" s="9" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M198" s="8" t="n">
         <v>4.28</v>
@@ -13231,19 +13231,19 @@
         <v>0</v>
       </c>
       <c r="H199" s="12" t="n">
-        <v>12.04</v>
+        <v>11.7</v>
       </c>
       <c r="I199" s="12" t="n">
-        <v>2.12</v>
+        <v>-1.1</v>
       </c>
       <c r="J199" s="12" t="n">
-        <v>15.1</v>
+        <v>14.68</v>
       </c>
       <c r="K199" s="12" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="L199" s="13" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M199" s="12" t="n">
         <v>1.91</v>
@@ -13295,19 +13295,19 @@
         <v>2.65</v>
       </c>
       <c r="H200" s="4" t="n">
-        <v>43</v>
+        <v>43.94</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>-0.35</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J200" s="4" t="n">
-        <v>18.09</v>
+        <v>18.48</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>9326</v>
+        <v>9530</v>
       </c>
       <c r="M200" s="4" t="n">
         <v>4.4</v>
@@ -13359,19 +13359,19 @@
         <v>3.32</v>
       </c>
       <c r="H201" s="12" t="n">
-        <v>14.76</v>
+        <v>16.16</v>
       </c>
       <c r="I201" s="12" t="n">
-        <v>0.14</v>
+        <v>-0.49</v>
       </c>
       <c r="J201" s="12" t="n">
-        <v>37.51</v>
+        <v>41.07</v>
       </c>
       <c r="K201" s="12" t="n">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="L201" s="13" t="n">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="M201" s="12" t="n">
         <v>1.24</v>
@@ -13423,19 +13423,19 @@
         <v>2.97</v>
       </c>
       <c r="H202" s="8" t="n">
-        <v>12.24</v>
+        <v>13</v>
       </c>
       <c r="I202" s="8" t="n">
-        <v>-0.57</v>
+        <v>-1.66</v>
       </c>
       <c r="J202" s="8" t="n">
-        <v>18.11</v>
+        <v>19.23</v>
       </c>
       <c r="K202" s="8" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="L202" s="9" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="M202" s="8" t="n">
         <v>2.81</v>
@@ -13487,19 +13487,19 @@
         <v>2.61</v>
       </c>
       <c r="H203" s="12" t="n">
-        <v>16.24</v>
+        <v>17.36</v>
       </c>
       <c r="I203" s="12" t="n">
-        <v>0.43</v>
+        <v>-2.36</v>
       </c>
       <c r="J203" s="12" t="n">
-        <v>16.4</v>
+        <v>17.53</v>
       </c>
       <c r="K203" s="12" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="L203" s="13" t="n">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="M203" s="12" t="n">
         <v>3.33</v>
@@ -13551,19 +13551,19 @@
         <v>3.31</v>
       </c>
       <c r="H204" s="8" t="n">
-        <v>19.34</v>
+        <v>21.18</v>
       </c>
       <c r="I204" s="8" t="n">
-        <v>2</v>
+        <v>-0.42</v>
       </c>
       <c r="J204" s="8" t="n">
-        <v>19.07</v>
+        <v>20.88</v>
       </c>
       <c r="K204" s="8" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="L204" s="9" t="n">
-        <v>1941</v>
+        <v>2126</v>
       </c>
       <c r="M204" s="8" t="n">
         <v>2.48</v>
@@ -13615,19 +13615,19 @@
         <v>2.43</v>
       </c>
       <c r="H205" s="4" t="n">
-        <v>23.89</v>
+        <v>25.08</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>-0.13</v>
+        <v>0.8</v>
       </c>
       <c r="J205" s="4" t="n">
-        <v>14.32</v>
+        <v>15.04</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>2316</v>
+        <v>2432</v>
       </c>
       <c r="M205" s="4" t="n">
         <v>3.82</v>
@@ -13679,19 +13679,19 @@
         <v>5.91</v>
       </c>
       <c r="H206" s="8" t="n">
-        <v>27.11</v>
+        <v>27.5</v>
       </c>
       <c r="I206" s="8" t="n">
-        <v>1.8</v>
+        <v>-1.04</v>
       </c>
       <c r="J206" s="8" t="n">
-        <v>14.46</v>
+        <v>14.67</v>
       </c>
       <c r="K206" s="8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="L206" s="9" t="n">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="M206" s="8" t="n">
         <v>4.82</v>
@@ -13743,19 +13743,19 @@
         <v>3.23</v>
       </c>
       <c r="H207" s="12" t="n">
-        <v>5.37</v>
+        <v>5.68</v>
       </c>
       <c r="I207" s="12" t="n">
-        <v>-0.37</v>
+        <v>1.61</v>
       </c>
       <c r="J207" s="12" t="n">
-        <v>38.64</v>
+        <v>40.87</v>
       </c>
       <c r="K207" s="12" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="L207" s="13" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="M207" s="12" t="n">
         <v>1.16</v>
@@ -13807,19 +13807,19 @@
         <v>2.73</v>
       </c>
       <c r="H208" s="8" t="n">
-        <v>15</v>
+        <v>16.35</v>
       </c>
       <c r="I208" s="8" t="n">
-        <v>1.42</v>
+        <v>-0.91</v>
       </c>
       <c r="J208" s="8" t="n">
-        <v>30.95</v>
+        <v>33.73</v>
       </c>
       <c r="K208" s="8" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
       <c r="L208" s="9" t="n">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="M208" s="8" t="n">
         <v>1.65</v>
@@ -13871,19 +13871,19 @@
         <v>2.49</v>
       </c>
       <c r="H209" s="12" t="n">
-        <v>8.109999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="I209" s="12" t="n">
-        <v>1.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J209" s="12" t="n">
-        <v>100.3</v>
+        <v>110.19</v>
       </c>
       <c r="K209" s="12" t="n">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
       <c r="L209" s="13" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="M209" s="12" t="n">
         <v>0.75</v>
@@ -13935,19 +13935,19 @@
         <v>1.1</v>
       </c>
       <c r="H210" s="8" t="n">
-        <v>7.9</v>
+        <v>8.17</v>
       </c>
       <c r="I210" s="8" t="n">
-        <v>-0.13</v>
+        <v>-1.09</v>
       </c>
       <c r="J210" s="8" t="n">
-        <v>-50.31</v>
+        <v>-52.03</v>
       </c>
       <c r="K210" s="8" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="L210" s="9" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M210" s="8" t="n">
         <v>3.16</v>
@@ -13999,19 +13999,19 @@
         <v>0.89</v>
       </c>
       <c r="H211" s="12" t="n">
-        <v>6.93</v>
+        <v>7.01</v>
       </c>
       <c r="I211" s="12" t="n">
-        <v>0.87</v>
+        <v>0.29</v>
       </c>
       <c r="J211" s="12" t="n">
-        <v>-16.99</v>
+        <v>-17.19</v>
       </c>
       <c r="K211" s="12" t="n">
         <v>0.68</v>
       </c>
       <c r="L211" s="13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M211" s="12" t="n">
         <v>0</v>
@@ -14063,19 +14063,19 @@
         <v>0.83</v>
       </c>
       <c r="H212" s="8" t="n">
-        <v>5.6</v>
+        <v>5.42</v>
       </c>
       <c r="I212" s="8" t="n">
-        <v>-2.44</v>
+        <v>-2.52</v>
       </c>
       <c r="J212" s="8" t="n">
-        <v>-42.56</v>
+        <v>-41.19</v>
       </c>
       <c r="K212" s="8" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="L212" s="9" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M212" s="8" t="n">
         <v>0.35</v>
@@ -14127,19 +14127,19 @@
         <v>2.87</v>
       </c>
       <c r="H213" s="12" t="n">
-        <v>11.56</v>
+        <v>13.37</v>
       </c>
       <c r="I213" s="12" t="n">
-        <v>3.58</v>
+        <v>5.11</v>
       </c>
       <c r="J213" s="12" t="n">
-        <v>29.96</v>
+        <v>34.65</v>
       </c>
       <c r="K213" s="12" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="L213" s="13" t="n">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="M213" s="12" t="n">
         <v>2.12</v>
@@ -14191,19 +14191,19 @@
         <v>1.88</v>
       </c>
       <c r="H214" s="8" t="n">
-        <v>13.34</v>
+        <v>13.99</v>
       </c>
       <c r="I214" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.48</v>
       </c>
       <c r="J214" s="8" t="n">
-        <v>9.960000000000001</v>
+        <v>10.45</v>
       </c>
       <c r="K214" s="8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="L214" s="9" t="n">
-        <v>1769</v>
+        <v>1855</v>
       </c>
       <c r="M214" s="8" t="n">
         <v>3.07</v>
@@ -14255,19 +14255,19 @@
         <v>1.38</v>
       </c>
       <c r="H215" s="12" t="n">
-        <v>6.46</v>
+        <v>6.61</v>
       </c>
       <c r="I215" s="12" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="J215" s="12" t="n">
-        <v>27.62</v>
+        <v>28.27</v>
       </c>
       <c r="K215" s="12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="L215" s="13" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M215" s="12" t="n">
         <v>1.94</v>
@@ -14319,19 +14319,19 @@
         <v>1.22</v>
       </c>
       <c r="H216" s="8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I216" s="8" t="n">
-        <v>0.36</v>
+        <v>-0.58</v>
       </c>
       <c r="J216" s="8" t="n">
-        <v>19.18</v>
+        <v>19.29</v>
       </c>
       <c r="K216" s="8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="L216" s="9" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M216" s="8" t="n">
         <v>2.75</v>
@@ -14383,19 +14383,19 @@
         <v>2.57</v>
       </c>
       <c r="H217" s="12" t="n">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="I217" s="12" t="n">
-        <v>-1.28</v>
+        <v>-1.05</v>
       </c>
       <c r="J217" s="12" t="n">
-        <v>44.23</v>
+        <v>45</v>
       </c>
       <c r="K217" s="12" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L217" s="13" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M217" s="12" t="n">
         <v>2.11</v>
@@ -14447,19 +14447,19 @@
         <v>1.54</v>
       </c>
       <c r="H218" s="8" t="n">
-        <v>8.49</v>
+        <v>8.58</v>
       </c>
       <c r="I218" s="8" t="n">
-        <v>-0.35</v>
+        <v>-1.61</v>
       </c>
       <c r="J218" s="8" t="n">
-        <v>45.26</v>
+        <v>45.74</v>
       </c>
       <c r="K218" s="8" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L218" s="9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M218" s="8" t="n">
         <v>3.5</v>
@@ -14511,19 +14511,19 @@
         <v>5.08</v>
       </c>
       <c r="H219" s="12" t="n">
-        <v>25.86</v>
+        <v>25.32</v>
       </c>
       <c r="I219" s="12" t="n">
-        <v>-0.08</v>
+        <v>-0.28</v>
       </c>
       <c r="J219" s="12" t="n">
-        <v>12.07</v>
+        <v>11.82</v>
       </c>
       <c r="K219" s="12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="L219" s="13" t="n">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="M219" s="12" t="n">
         <v>2.38</v>
@@ -14575,19 +14575,19 @@
         <v>3.87</v>
       </c>
       <c r="H220" s="8" t="n">
-        <v>83.76000000000001</v>
+        <v>84.22</v>
       </c>
       <c r="I220" s="8" t="n">
-        <v>1.55</v>
+        <v>0.86</v>
       </c>
       <c r="J220" s="8" t="n">
-        <v>29.19</v>
+        <v>29.35</v>
       </c>
       <c r="K220" s="8" t="n">
-        <v>10.74</v>
+        <v>10.8</v>
       </c>
       <c r="L220" s="9" t="n">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="M220" s="8" t="n">
         <v>3.55</v>
@@ -14639,19 +14639,19 @@
         <v>1</v>
       </c>
       <c r="H221" s="12" t="n">
-        <v>36.93</v>
+        <v>37.89</v>
       </c>
       <c r="I221" s="12" t="n">
-        <v>2.41</v>
+        <v>4.21</v>
       </c>
       <c r="J221" s="12" t="n">
-        <v>23.65</v>
+        <v>24.27</v>
       </c>
       <c r="K221" s="12" t="n">
-        <v>5.51</v>
+        <v>5.65</v>
       </c>
       <c r="L221" s="13" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M221" s="12" t="n">
         <v>1.47</v>
@@ -14703,19 +14703,19 @@
         <v>0</v>
       </c>
       <c r="H222" s="8" t="n">
-        <v>28.46</v>
+        <v>30.27</v>
       </c>
       <c r="I222" s="8" t="n">
-        <v>1.93</v>
+        <v>4.31</v>
       </c>
       <c r="J222" s="8" t="n">
-        <v>43.23</v>
+        <v>45.98</v>
       </c>
       <c r="K222" s="8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="L222" s="9" t="n">
-        <v>646</v>
+        <v>687</v>
       </c>
       <c r="M222" s="8" t="n">
         <v>1.06</v>
@@ -14767,19 +14767,19 @@
         <v>0</v>
       </c>
       <c r="H223" s="12" t="n">
-        <v>22.63</v>
+        <v>22.11</v>
       </c>
       <c r="I223" s="12" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="J223" s="12" t="n">
-        <v>17.65</v>
+        <v>17.25</v>
       </c>
       <c r="K223" s="12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="L223" s="13" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="M223" s="12" t="n">
         <v>2.43</v>
@@ -14831,19 +14831,19 @@
         <v>0</v>
       </c>
       <c r="H224" s="8" t="n">
-        <v>23.48</v>
+        <v>22.69</v>
       </c>
       <c r="I224" s="8" t="n">
-        <v>-1.47</v>
+        <v>-0.74</v>
       </c>
       <c r="J224" s="8" t="n">
-        <v>22.34</v>
+        <v>21.59</v>
       </c>
       <c r="K224" s="8" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="L224" s="9" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M224" s="8" t="n">
         <v>1.95</v>
@@ -14895,19 +14895,19 @@
         <v>0</v>
       </c>
       <c r="H225" s="12" t="n">
-        <v>33.91</v>
+        <v>33.07</v>
       </c>
       <c r="I225" s="12" t="n">
-        <v>0.36</v>
+        <v>-0.06</v>
       </c>
       <c r="J225" s="12" t="n">
-        <v>7.52</v>
+        <v>7.34</v>
       </c>
       <c r="K225" s="12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="L225" s="13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M225" s="12" t="n">
         <v>1.36</v>
@@ -14959,19 +14959,19 @@
         <v>6.21</v>
       </c>
       <c r="H226" s="8" t="n">
-        <v>4.87</v>
+        <v>4.86</v>
       </c>
       <c r="I226" s="8" t="n">
-        <v>2.1</v>
+        <v>0.83</v>
       </c>
       <c r="J226" s="8" t="n">
-        <v>20.02</v>
+        <v>19.98</v>
       </c>
       <c r="K226" s="8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="L226" s="9" t="n">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="M226" s="8" t="n">
         <v>1.9</v>
@@ -15023,19 +15023,19 @@
         <v>4.18</v>
       </c>
       <c r="H227" s="12" t="n">
-        <v>122.79</v>
+        <v>138</v>
       </c>
       <c r="I227" s="12" t="n">
-        <v>9.41</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J227" s="12" t="n">
-        <v>75.92</v>
+        <v>85.33</v>
       </c>
       <c r="K227" s="12" t="n">
-        <v>18.66</v>
+        <v>20.97</v>
       </c>
       <c r="L227" s="13" t="n">
-        <v>2983</v>
+        <v>3352</v>
       </c>
       <c r="M227" s="12" t="n">
         <v>1.14</v>
@@ -15087,19 +15087,19 @@
         <v>2.65</v>
       </c>
       <c r="H228" s="8" t="n">
-        <v>62.56</v>
+        <v>66.45</v>
       </c>
       <c r="I228" s="8" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="J228" s="8" t="n">
-        <v>53.71</v>
+        <v>57.04</v>
       </c>
       <c r="K228" s="8" t="n">
-        <v>11.47</v>
+        <v>12.19</v>
       </c>
       <c r="L228" s="9" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="M228" s="8" t="n">
         <v>0.51</v>
@@ -15151,19 +15151,19 @@
         <v>2.45</v>
       </c>
       <c r="H229" s="12" t="n">
-        <v>91.01000000000001</v>
+        <v>96.05</v>
       </c>
       <c r="I229" s="12" t="n">
-        <v>4.85</v>
+        <v>2.15</v>
       </c>
       <c r="J229" s="12" t="n">
-        <v>36.08</v>
+        <v>38.08</v>
       </c>
       <c r="K229" s="12" t="n">
-        <v>5.13</v>
+        <v>5.41</v>
       </c>
       <c r="L229" s="13" t="n">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="M229" s="12" t="n">
         <v>1.1</v>
@@ -15215,19 +15215,19 @@
         <v>1.34</v>
       </c>
       <c r="H230" s="8" t="n">
-        <v>199</v>
+        <v>203.87</v>
       </c>
       <c r="I230" s="8" t="n">
-        <v>5.14</v>
+        <v>0.43</v>
       </c>
       <c r="J230" s="8" t="n">
-        <v>72.58</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="K230" s="8" t="n">
-        <v>17.41</v>
+        <v>17.83</v>
       </c>
       <c r="L230" s="9" t="n">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="M230" s="8" t="n">
         <v>0.51</v>
@@ -15279,19 +15279,19 @@
         <v>0.67</v>
       </c>
       <c r="H231" s="12" t="n">
-        <v>349.18</v>
+        <v>377.5</v>
       </c>
       <c r="I231" s="12" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="J231" s="12" t="n">
-        <v>65.44</v>
+        <v>70.75</v>
       </c>
       <c r="K231" s="12" t="n">
-        <v>14.45</v>
+        <v>15.63</v>
       </c>
       <c r="L231" s="13" t="n">
-        <v>2378</v>
+        <v>2571</v>
       </c>
       <c r="M231" s="12" t="n">
         <v>0.78</v>
@@ -15343,19 +15343,19 @@
         <v>0</v>
       </c>
       <c r="H232" s="8" t="n">
-        <v>12.55</v>
+        <v>12.63</v>
       </c>
       <c r="I232" s="8" t="n">
-        <v>0.8</v>
+        <v>0.32</v>
       </c>
       <c r="J232" s="8" t="n">
-        <v>18.18</v>
+        <v>18.3</v>
       </c>
       <c r="K232" s="8" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="L232" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M232" s="8" t="n">
         <v>1.59</v>
@@ -15407,19 +15407,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H233" s="4" t="n">
-        <v>30.69</v>
+        <v>31.35</v>
       </c>
       <c r="I233" s="4" t="n">
-        <v>-2.76</v>
+        <v>1.26</v>
       </c>
       <c r="J233" s="4" t="n">
-        <v>11.7</v>
+        <v>11.95</v>
       </c>
       <c r="K233" s="4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>14587</v>
+        <v>14901</v>
       </c>
       <c r="M233" s="4" t="n">
         <v>3.55</v>
@@ -15471,19 +15471,19 @@
         <v>2.8</v>
       </c>
       <c r="H234" s="4" t="n">
-        <v>10.63</v>
+        <v>10.8</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>-2.12</v>
+        <v>1.12</v>
       </c>
       <c r="J234" s="4" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="K234" s="4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>19455</v>
+        <v>19766</v>
       </c>
       <c r="M234" s="4" t="n">
         <v>4.24</v>
@@ -15535,19 +15535,19 @@
         <v>2.07</v>
       </c>
       <c r="H235" s="12" t="n">
-        <v>4.98</v>
+        <v>5.1</v>
       </c>
       <c r="I235" s="12" t="n">
-        <v>-2.35</v>
+        <v>0.39</v>
       </c>
       <c r="J235" s="12" t="n">
-        <v>16.94</v>
+        <v>17.35</v>
       </c>
       <c r="K235" s="12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="L235" s="13" t="n">
-        <v>6022</v>
+        <v>6167</v>
       </c>
       <c r="M235" s="12" t="n">
         <v>3.8</v>
@@ -15599,16 +15599,16 @@
         <v>2.03</v>
       </c>
       <c r="H236" s="8" t="n">
-        <v>26.69</v>
+        <v>26.47</v>
       </c>
       <c r="I236" s="8" t="n">
-        <v>2.07</v>
+        <v>-0.45</v>
       </c>
       <c r="J236" s="8" t="n">
-        <v>20.44</v>
+        <v>20.27</v>
       </c>
       <c r="K236" s="8" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="L236" s="9" t="n">
         <v>43</v>
@@ -15663,19 +15663,19 @@
         <v>1.28</v>
       </c>
       <c r="H237" s="12" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="I237" s="12" t="n">
-        <v>-1.78</v>
+        <v>-0.51</v>
       </c>
       <c r="J237" s="12" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="K237" s="12" t="n">
         <v>1.37</v>
       </c>
       <c r="L237" s="13" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M237" s="12" t="n">
         <v>3.77</v>
@@ -15727,16 +15727,16 @@
         <v>0.48</v>
       </c>
       <c r="H238" s="8" t="n">
-        <v>8.75</v>
+        <v>8.66</v>
       </c>
       <c r="I238" s="8" t="n">
-        <v>0.34</v>
+        <v>-0.57</v>
       </c>
       <c r="J238" s="8" t="n">
-        <v>19.57</v>
+        <v>19.37</v>
       </c>
       <c r="K238" s="8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="L238" s="9" t="n">
         <v>48</v>
@@ -15791,19 +15791,19 @@
         <v>2.73</v>
       </c>
       <c r="H239" s="12" t="n">
-        <v>7.57</v>
+        <v>7.64</v>
       </c>
       <c r="I239" s="12" t="n">
-        <v>-1.56</v>
+        <v>0.13</v>
       </c>
       <c r="J239" s="12" t="n">
-        <v>13.64</v>
+        <v>13.77</v>
       </c>
       <c r="K239" s="12" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="L239" s="13" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M239" s="12" t="n">
         <v>5.61</v>
@@ -15858,7 +15858,7 @@
         <v>6.07</v>
       </c>
       <c r="I240" s="8" t="n">
-        <v>-0.98</v>
+        <v>0.17</v>
       </c>
       <c r="J240" s="8" t="n">
         <v>13.37</v>
@@ -15919,19 +15919,19 @@
         <v>1.04</v>
       </c>
       <c r="H241" s="12" t="n">
-        <v>12.77</v>
+        <v>12.69</v>
       </c>
       <c r="I241" s="12" t="n">
-        <v>0.24</v>
+        <v>-0.55</v>
       </c>
       <c r="J241" s="12" t="n">
-        <v>12.11</v>
+        <v>12.04</v>
       </c>
       <c r="K241" s="12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="L241" s="13" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M241" s="12" t="n">
         <v>6.97</v>
@@ -15983,19 +15983,19 @@
         <v>0.84</v>
       </c>
       <c r="H242" s="8" t="n">
-        <v>6.12</v>
+        <v>6.02</v>
       </c>
       <c r="I242" s="8" t="n">
-        <v>-0.16</v>
+        <v>-1.31</v>
       </c>
       <c r="J242" s="8" t="n">
-        <v>16.66</v>
+        <v>16.39</v>
       </c>
       <c r="K242" s="8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="L242" s="9" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M242" s="8" t="n">
         <v>4.83</v>
@@ -16047,13 +16047,13 @@
         <v>0.48</v>
       </c>
       <c r="H243" s="12" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="I243" s="12" t="n">
-        <v>-0.49</v>
+        <v>-2.63</v>
       </c>
       <c r="J243" s="12" t="n">
-        <v>14.66</v>
+        <v>14.58</v>
       </c>
       <c r="K243" s="12" t="n">
         <v>1.29</v>
@@ -16111,19 +16111,19 @@
         <v>2.1</v>
       </c>
       <c r="H244" s="8" t="n">
-        <v>17.08</v>
+        <v>17.26</v>
       </c>
       <c r="I244" s="8" t="n">
-        <v>4.53</v>
+        <v>0.99</v>
       </c>
       <c r="J244" s="8" t="n">
-        <v>64.72</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K244" s="8" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="L244" s="9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M244" s="8" t="n">
         <v>0.73</v>
@@ -16175,19 +16175,19 @@
         <v>1.9</v>
       </c>
       <c r="H245" s="12" t="n">
-        <v>25.89</v>
+        <v>24.72</v>
       </c>
       <c r="I245" s="12" t="n">
-        <v>2.33</v>
+        <v>-3.48</v>
       </c>
       <c r="J245" s="12" t="n">
-        <v>24.4</v>
+        <v>23.3</v>
       </c>
       <c r="K245" s="12" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="L245" s="13" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="M245" s="12" t="n">
         <v>4.69</v>
@@ -16239,19 +16239,19 @@
         <v>1.55</v>
       </c>
       <c r="H246" s="8" t="n">
-        <v>7.93</v>
+        <v>7.78</v>
       </c>
       <c r="I246" s="8" t="n">
-        <v>3.12</v>
+        <v>0.65</v>
       </c>
       <c r="J246" s="8" t="n">
-        <v>43.73</v>
+        <v>42.91</v>
       </c>
       <c r="K246" s="8" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="L246" s="9" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M246" s="8" t="n">
         <v>1.92</v>
@@ -16303,19 +16303,19 @@
         <v>1.34</v>
       </c>
       <c r="H247" s="12" t="n">
-        <v>8.43</v>
+        <v>8.09</v>
       </c>
       <c r="I247" s="12" t="n">
-        <v>3.18</v>
+        <v>-0.74</v>
       </c>
       <c r="J247" s="12" t="n">
-        <v>17.43</v>
+        <v>14.69</v>
       </c>
       <c r="K247" s="12" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="L247" s="13" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="M247" s="12" t="n">
         <v>5.01</v>
@@ -16367,19 +16367,19 @@
         <v>2.37</v>
       </c>
       <c r="H248" s="8" t="n">
-        <v>33.6</v>
+        <v>33.24</v>
       </c>
       <c r="I248" s="8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="J248" s="8" t="n">
-        <v>26.2</v>
+        <v>25.91</v>
       </c>
       <c r="K248" s="8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="L248" s="9" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M248" s="8" t="n">
         <v>1.88</v>
@@ -16431,19 +16431,19 @@
         <v>5.89</v>
       </c>
       <c r="H249" s="12" t="n">
-        <v>38.44</v>
+        <v>37.21</v>
       </c>
       <c r="I249" s="12" t="n">
-        <v>-0.49</v>
+        <v>-0.64</v>
       </c>
       <c r="J249" s="12" t="n">
-        <v>21.44</v>
+        <v>20.75</v>
       </c>
       <c r="K249" s="12" t="n">
-        <v>4.18</v>
+        <v>4.04</v>
       </c>
       <c r="L249" s="13" t="n">
-        <v>3523</v>
+        <v>3410</v>
       </c>
       <c r="M249" s="12" t="n">
         <v>3.05</v>
@@ -16495,19 +16495,19 @@
         <v>2.29</v>
       </c>
       <c r="H250" s="8" t="n">
-        <v>107.6</v>
+        <v>104.7</v>
       </c>
       <c r="I250" s="8" t="n">
-        <v>2</v>
+        <v>-1.69</v>
       </c>
       <c r="J250" s="8" t="n">
-        <v>37.18</v>
+        <v>36.18</v>
       </c>
       <c r="K250" s="8" t="n">
-        <v>7.45</v>
+        <v>7.24</v>
       </c>
       <c r="L250" s="9" t="n">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="M250" s="8" t="n">
         <v>2.48</v>
@@ -16559,19 +16559,19 @@
         <v>4.47</v>
       </c>
       <c r="H251" s="12" t="n">
-        <v>242.33</v>
+        <v>238.69</v>
       </c>
       <c r="I251" s="12" t="n">
-        <v>3.78</v>
+        <v>-0.12</v>
       </c>
       <c r="J251" s="12" t="n">
-        <v>54.6</v>
+        <v>53.78</v>
       </c>
       <c r="K251" s="12" t="n">
-        <v>26.09</v>
+        <v>25.7</v>
       </c>
       <c r="L251" s="13" t="n">
-        <v>1824</v>
+        <v>1796</v>
       </c>
       <c r="M251" s="12" t="n">
         <v>2.21</v>
@@ -16623,19 +16623,19 @@
         <v>2.8</v>
       </c>
       <c r="H252" s="8" t="n">
-        <v>279.15</v>
+        <v>266.47</v>
       </c>
       <c r="I252" s="8" t="n">
-        <v>1.71</v>
+        <v>-0.24</v>
       </c>
       <c r="J252" s="8" t="n">
-        <v>35.69</v>
+        <v>34.07</v>
       </c>
       <c r="K252" s="8" t="n">
-        <v>8.84</v>
+        <v>8.44</v>
       </c>
       <c r="L252" s="9" t="n">
-        <v>1295</v>
+        <v>1236</v>
       </c>
       <c r="M252" s="8" t="n">
         <v>0.46</v>
@@ -16687,19 +16687,19 @@
         <v>0.2</v>
       </c>
       <c r="H253" s="12" t="n">
-        <v>28.98</v>
+        <v>29.68</v>
       </c>
       <c r="I253" s="12" t="n">
-        <v>-0.86</v>
+        <v>1.4</v>
       </c>
       <c r="J253" s="12" t="n">
-        <v>43.56</v>
+        <v>44.61</v>
       </c>
       <c r="K253" s="12" t="n">
-        <v>7.98</v>
+        <v>8.17</v>
       </c>
       <c r="L253" s="13" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M253" s="12" t="n">
         <v>2.13</v>
@@ -16751,19 +16751,19 @@
         <v>2.68</v>
       </c>
       <c r="H254" s="8" t="n">
-        <v>41.49</v>
+        <v>40.78</v>
       </c>
       <c r="I254" s="8" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="J254" s="8" t="n">
-        <v>18.01</v>
+        <v>17.7</v>
       </c>
       <c r="K254" s="8" t="n">
-        <v>5.24</v>
+        <v>5.15</v>
       </c>
       <c r="L254" s="9" t="n">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="M254" s="8" t="n">
         <v>4.55</v>
@@ -16815,19 +16815,19 @@
         <v>0.57</v>
       </c>
       <c r="H255" s="12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="I255" s="12" t="n">
-        <v>-0.59</v>
+        <v>-2.16</v>
       </c>
       <c r="J255" s="12" t="n">
-        <v>9.59</v>
+        <v>9.23</v>
       </c>
       <c r="K255" s="12" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="L255" s="13" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M255" s="12" t="n">
         <v>9.26</v>
@@ -16879,19 +16879,19 @@
         <v>0.19</v>
       </c>
       <c r="H256" s="8" t="n">
-        <v>33.04</v>
+        <v>32.09</v>
       </c>
       <c r="I256" s="8" t="n">
-        <v>1.16</v>
+        <v>-1.84</v>
       </c>
       <c r="J256" s="8" t="n">
-        <v>18.66</v>
+        <v>18.14</v>
       </c>
       <c r="K256" s="8" t="n">
-        <v>4.43</v>
+        <v>4.31</v>
       </c>
       <c r="L256" s="9" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M256" s="8" t="n">
         <v>2.53</v>
@@ -16943,19 +16943,19 @@
         <v>0</v>
       </c>
       <c r="H257" s="12" t="n">
-        <v>9.630000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="I257" s="12" t="n">
-        <v>0.31</v>
+        <v>-0.72</v>
       </c>
       <c r="J257" s="12" t="n">
-        <v>42.07</v>
+        <v>42.33</v>
       </c>
       <c r="K257" s="12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="L257" s="13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M257" s="12" t="n">
         <v>0.83</v>
@@ -17007,16 +17007,16 @@
         <v>0</v>
       </c>
       <c r="H258" s="8" t="n">
-        <v>9.050000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="I258" s="8" t="n">
-        <v>-0.55</v>
+        <v>-1.21</v>
       </c>
       <c r="J258" s="8" t="n">
-        <v>19.74</v>
+        <v>19.65</v>
       </c>
       <c r="K258" s="8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L258" s="9" t="n">
         <v>50</v>
@@ -17071,19 +17071,19 @@
         <v>1.75</v>
       </c>
       <c r="H259" s="12" t="n">
-        <v>95.98999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="I259" s="12" t="n">
-        <v>-0.45</v>
+        <v>-1.14</v>
       </c>
       <c r="J259" s="12" t="n">
-        <v>15.33</v>
+        <v>15.23</v>
       </c>
       <c r="K259" s="12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="L259" s="13" t="n">
-        <v>20818</v>
+        <v>20679</v>
       </c>
       <c r="M259" s="12" t="n">
         <v>4.83</v>
@@ -17135,19 +17135,19 @@
         <v>1.37</v>
       </c>
       <c r="H260" s="8" t="n">
-        <v>6.23</v>
+        <v>6.18</v>
       </c>
       <c r="I260" s="8" t="n">
-        <v>-0.95</v>
+        <v>-1.9</v>
       </c>
       <c r="J260" s="8" t="n">
-        <v>18</v>
+        <v>17.86</v>
       </c>
       <c r="K260" s="8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="L260" s="9" t="n">
-        <v>5701</v>
+        <v>5655</v>
       </c>
       <c r="M260" s="8" t="n">
         <v>4.32</v>
@@ -17199,19 +17199,19 @@
         <v>4.27</v>
       </c>
       <c r="H261" s="12" t="n">
-        <v>39.43</v>
+        <v>39.02</v>
       </c>
       <c r="I261" s="12" t="n">
-        <v>-0.55</v>
+        <v>-1.59</v>
       </c>
       <c r="J261" s="12" t="n">
-        <v>18.54</v>
+        <v>18.35</v>
       </c>
       <c r="K261" s="12" t="n">
-        <v>5.99</v>
+        <v>5.93</v>
       </c>
       <c r="L261" s="13" t="n">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="M261" s="12" t="n">
         <v>4.63</v>
@@ -17263,19 +17263,19 @@
         <v>2.79</v>
       </c>
       <c r="H262" s="8" t="n">
-        <v>312.4</v>
+        <v>333.5</v>
       </c>
       <c r="I262" s="8" t="n">
-        <v>10</v>
+        <v>1.6</v>
       </c>
       <c r="J262" s="8" t="n">
-        <v>223.51</v>
+        <v>238.6</v>
       </c>
       <c r="K262" s="8" t="n">
-        <v>18.17</v>
+        <v>19.4</v>
       </c>
       <c r="L262" s="9" t="n">
-        <v>2586</v>
+        <v>2761</v>
       </c>
       <c r="M262" s="8" t="n">
         <v>0.1</v>
@@ -17327,19 +17327,19 @@
         <v>0.76</v>
       </c>
       <c r="H263" s="12" t="n">
-        <v>4.39</v>
+        <v>4.3</v>
       </c>
       <c r="I263" s="12" t="n">
-        <v>-1.79</v>
+        <v>-1.83</v>
       </c>
       <c r="J263" s="12" t="n">
-        <v>15.85</v>
+        <v>15.53</v>
       </c>
       <c r="K263" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L263" s="13" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="M263" s="12" t="n">
         <v>3.67</v>
@@ -17391,19 +17391,19 @@
         <v>0</v>
       </c>
       <c r="H264" s="8" t="n">
-        <v>12.14</v>
+        <v>11.93</v>
       </c>
       <c r="I264" s="8" t="n">
-        <v>-0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="J264" s="8" t="n">
-        <v>16.18</v>
+        <v>15.9</v>
       </c>
       <c r="K264" s="8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="L264" s="9" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M264" s="8" t="n">
         <v>3.71</v>
@@ -17455,19 +17455,19 @@
         <v>3.75</v>
       </c>
       <c r="H265" s="12" t="n">
-        <v>14.16</v>
+        <v>13.88</v>
       </c>
       <c r="I265" s="12" t="n">
-        <v>-1.19</v>
+        <v>-1.56</v>
       </c>
       <c r="J265" s="12" t="n">
-        <v>11.8</v>
+        <v>11.57</v>
       </c>
       <c r="K265" s="12" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="L265" s="13" t="n">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="M265" s="12" t="n">
         <v>4.31</v>
@@ -17519,19 +17519,19 @@
         <v>2.42</v>
       </c>
       <c r="H266" s="8" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="I266" s="8" t="n">
-        <v>0.41</v>
+        <v>-2.62</v>
       </c>
       <c r="J266" s="8" t="n">
-        <v>10.42</v>
+        <v>10.32</v>
       </c>
       <c r="K266" s="8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="L266" s="9" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M266" s="8" t="n">
         <v>5.09</v>
@@ -17583,19 +17583,19 @@
         <v>2.33</v>
       </c>
       <c r="H267" s="12" t="n">
-        <v>12.17</v>
+        <v>12.06</v>
       </c>
       <c r="I267" s="12" t="n">
-        <v>-1.46</v>
+        <v>-0.66</v>
       </c>
       <c r="J267" s="12" t="n">
-        <v>13.31</v>
+        <v>13.19</v>
       </c>
       <c r="K267" s="12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="L267" s="13" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M267" s="12" t="n">
         <v>5.49</v>
@@ -17647,19 +17647,19 @@
         <v>1.6</v>
       </c>
       <c r="H268" s="4" t="n">
-        <v>5.86</v>
+        <v>5.79</v>
       </c>
       <c r="I268" s="4" t="n">
-        <v>-1.35</v>
+        <v>-1.03</v>
       </c>
       <c r="J268" s="4" t="n">
-        <v>12.59</v>
+        <v>12.44</v>
       </c>
       <c r="K268" s="4" t="n">
         <v>0.62</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>1276</v>
+        <v>1261</v>
       </c>
       <c r="M268" s="4" t="n">
         <v>4.89</v>
@@ -17711,19 +17711,19 @@
         <v>0</v>
       </c>
       <c r="H269" s="12" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="I269" s="12" t="n">
-        <v>0.26</v>
+        <v>-1.06</v>
       </c>
       <c r="J269" s="12" t="n">
-        <v>34.98</v>
+        <v>34.43</v>
       </c>
       <c r="K269" s="12" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="L269" s="13" t="n">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M269" s="12" t="n">
         <v>1.06</v>
@@ -17775,19 +17775,19 @@
         <v>0</v>
       </c>
       <c r="H270" s="8" t="n">
-        <v>6.41</v>
+        <v>6.3</v>
       </c>
       <c r="I270" s="8" t="n">
-        <v>0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="J270" s="8" t="n">
-        <v>13.18</v>
+        <v>12.96</v>
       </c>
       <c r="K270" s="8" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L270" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M270" s="8" t="n">
         <v>3.12</v>
@@ -17839,19 +17839,19 @@
         <v>2.41</v>
       </c>
       <c r="H271" s="12" t="n">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="I271" s="12" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="J271" s="12" t="n">
-        <v>6.35</v>
+        <v>6.36</v>
       </c>
       <c r="K271" s="12" t="n">
         <v>0.53</v>
       </c>
       <c r="L271" s="13" t="n">
-        <v>6124</v>
+        <v>6132</v>
       </c>
       <c r="M271" s="12" t="n">
         <v>4.52</v>
@@ -17903,19 +17903,19 @@
         <v>2.4</v>
       </c>
       <c r="H272" s="8" t="n">
-        <v>7.52</v>
+        <v>7.53</v>
       </c>
       <c r="I272" s="8" t="n">
-        <v>-1.83</v>
+        <v>-0.53</v>
       </c>
       <c r="J272" s="8" t="n">
-        <v>7.22</v>
+        <v>7.23</v>
       </c>
       <c r="K272" s="8" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="L272" s="9" t="n">
-        <v>26802</v>
+        <v>26837</v>
       </c>
       <c r="M272" s="8" t="n">
         <v>3.88</v>
@@ -17967,19 +17967,19 @@
         <v>2.76</v>
       </c>
       <c r="H273" s="12" t="n">
-        <v>9.279999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="I273" s="12" t="n">
-        <v>-1.49</v>
+        <v>-0.54</v>
       </c>
       <c r="J273" s="12" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="K273" s="12" t="n">
         <v>0.53</v>
       </c>
       <c r="L273" s="13" t="n">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="M273" s="12" t="n">
         <v>5.5</v>
@@ -18031,19 +18031,19 @@
         <v>2.62</v>
       </c>
       <c r="H274" s="8" t="n">
-        <v>5.73</v>
+        <v>5.77</v>
       </c>
       <c r="I274" s="8" t="n">
-        <v>-1.55</v>
+        <v>-0.35</v>
       </c>
       <c r="J274" s="8" t="n">
-        <v>7.53</v>
+        <v>7.58</v>
       </c>
       <c r="K274" s="8" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L274" s="9" t="n">
-        <v>18463</v>
+        <v>18592</v>
       </c>
       <c r="M274" s="8" t="n">
         <v>3.73</v>
@@ -18095,19 +18095,19 @@
         <v>2.54</v>
       </c>
       <c r="H275" s="4" t="n">
-        <v>17.89</v>
+        <v>17.94</v>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-1</v>
+        <v>-0.17</v>
       </c>
       <c r="J275" s="4" t="n">
-        <v>5.65</v>
+        <v>5.66</v>
       </c>
       <c r="K275" s="4" t="n">
         <v>0.86</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M275" s="4" t="n">
         <v>4.98</v>
@@ -18159,19 +18159,19 @@
         <v>2.39</v>
       </c>
       <c r="H276" s="8" t="n">
-        <v>11.6</v>
+        <v>11.67</v>
       </c>
       <c r="I276" s="8" t="n">
-        <v>1.22</v>
+        <v>-0.68</v>
       </c>
       <c r="J276" s="8" t="n">
-        <v>5.89</v>
+        <v>5.93</v>
       </c>
       <c r="K276" s="8" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="L276" s="9" t="n">
-        <v>2129</v>
+        <v>2142</v>
       </c>
       <c r="M276" s="8" t="n">
         <v>4.77</v>
@@ -18223,19 +18223,19 @@
         <v>2.37</v>
       </c>
       <c r="H277" s="12" t="n">
-        <v>7.55</v>
+        <v>7.47</v>
       </c>
       <c r="I277" s="12" t="n">
-        <v>-2.45</v>
+        <v>-1.06</v>
       </c>
       <c r="J277" s="12" t="n">
-        <v>5.9</v>
+        <v>5.84</v>
       </c>
       <c r="K277" s="12" t="n">
         <v>0.57</v>
       </c>
       <c r="L277" s="13" t="n">
-        <v>4201</v>
+        <v>4157</v>
       </c>
       <c r="M277" s="12" t="n">
         <v>4.87</v>
@@ -18287,19 +18287,19 @@
         <v>2.35</v>
       </c>
       <c r="H278" s="8" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
       <c r="I278" s="8" t="n">
-        <v>-1.37</v>
+        <v>-0.4</v>
       </c>
       <c r="J278" s="8" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="K278" s="8" t="n">
         <v>0.38</v>
       </c>
       <c r="L278" s="9" t="n">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="M278" s="8" t="n">
         <v>5.33</v>
@@ -18351,19 +18351,19 @@
         <v>2.34</v>
       </c>
       <c r="H279" s="12" t="n">
-        <v>6.78</v>
+        <v>6.75</v>
       </c>
       <c r="I279" s="12" t="n">
-        <v>-1.6</v>
+        <v>-0.88</v>
       </c>
       <c r="J279" s="12" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="K279" s="12" t="n">
         <v>0.34</v>
       </c>
       <c r="L279" s="13" t="n">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="M279" s="12" t="n">
         <v>6.03</v>
@@ -18415,19 +18415,19 @@
         <v>2.08</v>
       </c>
       <c r="H280" s="8" t="n">
-        <v>6.48</v>
+        <v>6.46</v>
       </c>
       <c r="I280" s="8" t="n">
-        <v>-1.97</v>
+        <v>-0.62</v>
       </c>
       <c r="J280" s="8" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="K280" s="8" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L280" s="9" t="n">
-        <v>22679</v>
+        <v>22609</v>
       </c>
       <c r="M280" s="8" t="n">
         <v>3.62</v>
@@ -18479,19 +18479,19 @@
         <v>2.19</v>
       </c>
       <c r="H281" s="12" t="n">
-        <v>4.96</v>
+        <v>4.97</v>
       </c>
       <c r="I281" s="12" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="J281" s="12" t="n">
-        <v>6.78</v>
+        <v>6.79</v>
       </c>
       <c r="K281" s="12" t="n">
         <v>0.58</v>
       </c>
       <c r="L281" s="13" t="n">
-        <v>5957</v>
+        <v>5969</v>
       </c>
       <c r="M281" s="12" t="n">
         <v>4.21</v>
@@ -18543,10 +18543,10 @@
         <v>2.14</v>
       </c>
       <c r="H282" s="4" t="n">
-        <v>38.94</v>
+        <v>38.93</v>
       </c>
       <c r="I282" s="4" t="n">
-        <v>-0.87</v>
+        <v>-0.1</v>
       </c>
       <c r="J282" s="4" t="n">
         <v>6.51</v>
@@ -18555,7 +18555,7 @@
         <v>0.89</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>9821</v>
+        <v>9818</v>
       </c>
       <c r="M282" s="4" t="n">
         <v>5.09</v>
@@ -18607,19 +18607,19 @@
         <v>2.64</v>
       </c>
       <c r="H283" s="12" t="n">
-        <v>9.960000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="I283" s="12" t="n">
-        <v>-1.39</v>
+        <v>-0.2</v>
       </c>
       <c r="J283" s="12" t="n">
-        <v>7.62</v>
+        <v>7.72</v>
       </c>
       <c r="K283" s="12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L283" s="13" t="n">
-        <v>26055</v>
+        <v>26395</v>
       </c>
       <c r="M283" s="12" t="n">
         <v>3.58</v>
@@ -18674,7 +18674,7 @@
         <v>11.23</v>
       </c>
       <c r="I284" s="8" t="n">
-        <v>-1.23</v>
+        <v>-0.44</v>
       </c>
       <c r="J284" s="8" t="n">
         <v>6.23</v>
@@ -18738,7 +18738,7 @@
         <v>6.46</v>
       </c>
       <c r="I285" s="12" t="n">
-        <v>-0.46</v>
+        <v>-0.31</v>
       </c>
       <c r="J285" s="12" t="n">
         <v>5.82</v>
@@ -18799,19 +18799,19 @@
         <v>2.21</v>
       </c>
       <c r="H286" s="8" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="I286" s="8" t="n">
-        <v>-1.12</v>
+        <v>0.28</v>
       </c>
       <c r="J286" s="8" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="K286" s="8" t="n">
         <v>0.27</v>
       </c>
       <c r="L286" s="9" t="n">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="M286" s="8" t="n">
         <v>5.22</v>
@@ -18863,19 +18863,19 @@
         <v>2.31</v>
       </c>
       <c r="H287" s="12" t="n">
-        <v>8.369999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="I287" s="12" t="n">
-        <v>-2.33</v>
+        <v>-0.6</v>
       </c>
       <c r="J287" s="12" t="n">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
       <c r="K287" s="12" t="n">
         <v>0.62</v>
       </c>
       <c r="L287" s="13" t="n">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="M287" s="12" t="n">
         <v>5.06</v>
@@ -18927,19 +18927,19 @@
         <v>2.3</v>
       </c>
       <c r="H288" s="8" t="n">
-        <v>18.36</v>
+        <v>18.39</v>
       </c>
       <c r="I288" s="8" t="n">
-        <v>-1.08</v>
+        <v>-0.49</v>
       </c>
       <c r="J288" s="8" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
       <c r="K288" s="8" t="n">
         <v>0.47</v>
       </c>
       <c r="L288" s="9" t="n">
-        <v>3886</v>
+        <v>3892</v>
       </c>
       <c r="M288" s="8" t="n">
         <v>5.64</v>
@@ -18991,19 +18991,19 @@
         <v>2.22</v>
       </c>
       <c r="H289" s="12" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="I289" s="12" t="n">
-        <v>-1.92</v>
+        <v>-0.33</v>
       </c>
       <c r="J289" s="12" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="K289" s="12" t="n">
         <v>0.36</v>
       </c>
       <c r="L289" s="13" t="n">
-        <v>1814</v>
+        <v>1802</v>
       </c>
       <c r="M289" s="12" t="n">
         <v>5.52</v>
@@ -19055,19 +19055,19 @@
         <v>2.07</v>
       </c>
       <c r="H290" s="8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I290" s="8" t="n">
-        <v>-1.67</v>
+        <v>-1.02</v>
       </c>
       <c r="J290" s="8" t="n">
-        <v>6.22</v>
+        <v>6.14</v>
       </c>
       <c r="K290" s="8" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="L290" s="9" t="n">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="M290" s="8" t="n">
         <v>4.32</v>
@@ -19119,19 +19119,19 @@
         <v>2.6</v>
       </c>
       <c r="H291" s="12" t="n">
-        <v>11.25</v>
+        <v>11.2</v>
       </c>
       <c r="I291" s="12" t="n">
-        <v>-1.66</v>
+        <v>-0.62</v>
       </c>
       <c r="J291" s="12" t="n">
-        <v>5.07</v>
+        <v>5.05</v>
       </c>
       <c r="K291" s="12" t="n">
         <v>0.48</v>
       </c>
       <c r="L291" s="13" t="n">
-        <v>2183</v>
+        <v>2173</v>
       </c>
       <c r="M291" s="12" t="n">
         <v>5.12</v>
@@ -19183,19 +19183,19 @@
         <v>2.06</v>
       </c>
       <c r="H292" s="8" t="n">
-        <v>7.43</v>
+        <v>7.27</v>
       </c>
       <c r="I292" s="8" t="n">
-        <v>-1.72</v>
+        <v>-1.36</v>
       </c>
       <c r="J292" s="8" t="n">
-        <v>7.31</v>
+        <v>7.15</v>
       </c>
       <c r="K292" s="8" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="L292" s="9" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M292" s="8" t="n">
         <v>3.21</v>
@@ -19247,19 +19247,19 @@
         <v>2.01</v>
       </c>
       <c r="H293" s="12" t="n">
-        <v>10.96</v>
+        <v>10.79</v>
       </c>
       <c r="I293" s="12" t="n">
-        <v>-1.62</v>
+        <v>-1.46</v>
       </c>
       <c r="J293" s="12" t="n">
-        <v>6.64</v>
+        <v>6.54</v>
       </c>
       <c r="K293" s="12" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L293" s="13" t="n">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="M293" s="12" t="n">
         <v>3.92</v>
@@ -19311,19 +19311,19 @@
         <v>2.19</v>
       </c>
       <c r="H294" s="8" t="n">
-        <v>9.31</v>
+        <v>9.26</v>
       </c>
       <c r="I294" s="8" t="n">
-        <v>-1.38</v>
+        <v>-0.86</v>
       </c>
       <c r="J294" s="8" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="K294" s="8" t="n">
         <v>0.51</v>
       </c>
       <c r="L294" s="9" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M294" s="8" t="n">
         <v>4.51</v>
@@ -19375,19 +19375,19 @@
         <v>2.02</v>
       </c>
       <c r="H295" s="12" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="I295" s="12" t="n">
-        <v>-1.33</v>
+        <v>-1.13</v>
       </c>
       <c r="J295" s="12" t="n">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="K295" s="12" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="L295" s="13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M295" s="12" t="n">
         <v>4.8</v>
@@ -19439,19 +19439,19 @@
         <v>1.88</v>
       </c>
       <c r="H296" s="8" t="n">
-        <v>6.15</v>
+        <v>6.23</v>
       </c>
       <c r="I296" s="8" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="J296" s="8" t="n">
-        <v>6.41</v>
+        <v>6.49</v>
       </c>
       <c r="K296" s="8" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="L296" s="9" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M296" s="8" t="n">
         <v>3.91</v>
@@ -19503,19 +19503,19 @@
         <v>1.81</v>
       </c>
       <c r="H297" s="12" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I297" s="12" t="n">
-        <v>-0.6</v>
+        <v>-0.12</v>
       </c>
       <c r="J297" s="12" t="n">
-        <v>6.74</v>
+        <v>6.69</v>
       </c>
       <c r="K297" s="12" t="n">
         <v>0.72</v>
       </c>
       <c r="L297" s="13" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M297" s="12" t="n">
         <v>4.24</v>
@@ -19567,19 +19567,19 @@
         <v>1.72</v>
       </c>
       <c r="H298" s="8" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="I298" s="8" t="n">
-        <v>-1.46</v>
+        <v>-0.99</v>
       </c>
       <c r="J298" s="8" t="n">
-        <v>5.31</v>
+        <v>5.25</v>
       </c>
       <c r="K298" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="L298" s="9" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M298" s="8" t="n">
         <v>5.3</v>
@@ -19631,19 +19631,19 @@
         <v>0.88</v>
       </c>
       <c r="H299" s="12" t="n">
-        <v>5.66</v>
+        <v>5.6</v>
       </c>
       <c r="I299" s="12" t="n">
-        <v>-1.05</v>
+        <v>-0.71</v>
       </c>
       <c r="J299" s="12" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="K299" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="L299" s="13" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M299" s="12" t="n">
         <v>5.19</v>
@@ -19695,19 +19695,19 @@
         <v>1.44</v>
       </c>
       <c r="H300" s="8" t="n">
-        <v>16.15</v>
+        <v>16.03</v>
       </c>
       <c r="I300" s="8" t="n">
-        <v>0.06</v>
+        <v>-0.93</v>
       </c>
       <c r="J300" s="8" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="K300" s="8" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="L300" s="9" t="n">
-        <v>1171</v>
+        <v>1162</v>
       </c>
       <c r="M300" s="8" t="n">
         <v>4.01</v>
@@ -19759,19 +19759,19 @@
         <v>0.98</v>
       </c>
       <c r="H301" s="12" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="I301" s="12" t="n">
-        <v>-1.35</v>
+        <v>-1.83</v>
       </c>
       <c r="J301" s="12" t="n">
-        <v>6.79</v>
+        <v>6.63</v>
       </c>
       <c r="K301" s="12" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="L301" s="13" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="M301" s="12" t="n">
         <v>3.62</v>
@@ -19823,19 +19823,19 @@
         <v>0.62</v>
       </c>
       <c r="H302" s="8" t="n">
-        <v>5.52</v>
+        <v>5.41</v>
       </c>
       <c r="I302" s="8" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="J302" s="8" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="K302" s="8" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="L302" s="9" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M302" s="8" t="n">
         <v>4.25</v>
@@ -19887,19 +19887,19 @@
         <v>0.61</v>
       </c>
       <c r="H303" s="12" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="I303" s="12" t="n">
-        <v>-1.14</v>
+        <v>-1.54</v>
       </c>
       <c r="J303" s="12" t="n">
-        <v>7.61</v>
+        <v>7.46</v>
       </c>
       <c r="K303" s="12" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="L303" s="13" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M303" s="12" t="n">
         <v>3.76</v>
@@ -19951,19 +19951,19 @@
         <v>0.51</v>
       </c>
       <c r="H304" s="8" t="n">
-        <v>6.22</v>
+        <v>6.12</v>
       </c>
       <c r="I304" s="8" t="n">
-        <v>-1.11</v>
+        <v>-1.45</v>
       </c>
       <c r="J304" s="8" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="K304" s="8" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="L304" s="9" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M304" s="8" t="n">
         <v>4.2</v>
@@ -20015,19 +20015,19 @@
         <v>0.5</v>
       </c>
       <c r="H305" s="12" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="I305" s="12" t="n">
-        <v>-1.61</v>
+        <v>-1.4</v>
       </c>
       <c r="J305" s="12" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="K305" s="12" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="L305" s="13" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M305" s="12" t="n">
         <v>4.76</v>
@@ -20079,10 +20079,10 @@
         <v>1.51</v>
       </c>
       <c r="H306" s="8" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="I306" s="8" t="n">
-        <v>-1.49</v>
+        <v>-0.43</v>
       </c>
       <c r="J306" s="8" t="n">
         <v>6.13</v>
@@ -20091,7 +20091,7 @@
         <v>0.42</v>
       </c>
       <c r="L306" s="9" t="n">
-        <v>3084</v>
+        <v>3081</v>
       </c>
       <c r="M306" s="8" t="n">
         <v>4.42</v>
@@ -20143,19 +20143,19 @@
         <v>2.07</v>
       </c>
       <c r="H307" s="12" t="n">
-        <v>6.37</v>
+        <v>6.39</v>
       </c>
       <c r="I307" s="12" t="n">
-        <v>1.27</v>
+        <v>-0.16</v>
       </c>
       <c r="J307" s="12" t="n">
-        <v>11.21</v>
+        <v>11.25</v>
       </c>
       <c r="K307" s="12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="L307" s="13" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M307" s="12" t="n">
         <v>4.59</v>
@@ -20207,19 +20207,19 @@
         <v>1.91</v>
       </c>
       <c r="H308" s="8" t="n">
-        <v>54.02</v>
+        <v>53.38</v>
       </c>
       <c r="I308" s="8" t="n">
-        <v>0.17</v>
+        <v>-0.22</v>
       </c>
       <c r="J308" s="8" t="n">
-        <v>7.37</v>
+        <v>7.28</v>
       </c>
       <c r="K308" s="8" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="L308" s="9" t="n">
-        <v>9782</v>
+        <v>9666</v>
       </c>
       <c r="M308" s="8" t="n">
         <v>4.92</v>
@@ -20271,19 +20271,19 @@
         <v>2.22</v>
       </c>
       <c r="H309" s="12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="I309" s="12" t="n">
-        <v>1.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J309" s="12" t="n">
-        <v>11.79</v>
+        <v>11.82</v>
       </c>
       <c r="K309" s="12" t="n">
         <v>1.41</v>
       </c>
       <c r="L309" s="13" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M309" s="12" t="n">
         <v>3.49</v>
@@ -20335,19 +20335,19 @@
         <v>1.5</v>
       </c>
       <c r="H310" s="8" t="n">
-        <v>63.31</v>
+        <v>60.5</v>
       </c>
       <c r="I310" s="8" t="n">
-        <v>1.64</v>
+        <v>0.22</v>
       </c>
       <c r="J310" s="8" t="n">
-        <v>5.35</v>
+        <v>5.11</v>
       </c>
       <c r="K310" s="8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="L310" s="9" t="n">
-        <v>1975</v>
+        <v>1887</v>
       </c>
       <c r="M310" s="8" t="n">
         <v>7.48</v>
@@ -20399,19 +20399,19 @@
         <v>0.9</v>
       </c>
       <c r="H311" s="12" t="n">
-        <v>7.89</v>
+        <v>7.72</v>
       </c>
       <c r="I311" s="12" t="n">
-        <v>0.51</v>
+        <v>-0.26</v>
       </c>
       <c r="J311" s="12" t="n">
-        <v>9.52</v>
+        <v>9.31</v>
       </c>
       <c r="K311" s="12" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="L311" s="13" t="n">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="M311" s="12" t="n">
         <v>2.8</v>
@@ -20463,19 +20463,19 @@
         <v>2.79</v>
       </c>
       <c r="H312" s="4" t="n">
-        <v>25.33</v>
+        <v>24.2</v>
       </c>
       <c r="I312" s="4" t="n">
-        <v>-0.74</v>
+        <v>-4.65</v>
       </c>
       <c r="J312" s="4" t="n">
-        <v>16.69</v>
+        <v>15.94</v>
       </c>
       <c r="K312" s="4" t="n">
-        <v>4.41</v>
+        <v>4.22</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>878</v>
+        <v>838</v>
       </c>
       <c r="M312" s="4" t="n">
         <v>5.58</v>
@@ -20527,19 +20527,19 @@
         <v>1.58</v>
       </c>
       <c r="H313" s="12" t="n">
-        <v>26.37</v>
+        <v>26.19</v>
       </c>
       <c r="I313" s="12" t="n">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="J313" s="12" t="n">
-        <v>13.8</v>
+        <v>13.71</v>
       </c>
       <c r="K313" s="12" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="L313" s="13" t="n">
-        <v>1668</v>
+        <v>1657</v>
       </c>
       <c r="M313" s="12" t="n">
         <v>5.09</v>
@@ -20591,19 +20591,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="H314" s="8" t="n">
-        <v>1306.45</v>
+        <v>1310.91</v>
       </c>
       <c r="I314" s="8" t="n">
-        <v>-1.65</v>
+        <v>0.18</v>
       </c>
       <c r="J314" s="8" t="n">
-        <v>19.74</v>
+        <v>19.81</v>
       </c>
       <c r="K314" s="8" t="n">
-        <v>7.01</v>
+        <v>7.04</v>
       </c>
       <c r="L314" s="9" t="n">
-        <v>16332</v>
+        <v>16387</v>
       </c>
       <c r="M314" s="8" t="n">
         <v>3.85</v>
@@ -20655,19 +20655,19 @@
         <v>2.54</v>
       </c>
       <c r="H315" s="12" t="n">
-        <v>50.57</v>
+        <v>49.26</v>
       </c>
       <c r="I315" s="12" t="n">
-        <v>0.02</v>
+        <v>-1.28</v>
       </c>
       <c r="J315" s="12" t="n">
-        <v>17.06</v>
+        <v>16.62</v>
       </c>
       <c r="K315" s="12" t="n">
-        <v>7.45</v>
+        <v>7.26</v>
       </c>
       <c r="L315" s="13" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M315" s="12" t="n">
         <v>2.69</v>
@@ -20719,19 +20719,19 @@
         <v>1.38</v>
       </c>
       <c r="H316" s="8" t="n">
-        <v>44.77</v>
+        <v>44.07</v>
       </c>
       <c r="I316" s="8" t="n">
-        <v>-2.33</v>
+        <v>0.23</v>
       </c>
       <c r="J316" s="8" t="n">
-        <v>18.12</v>
+        <v>17.83</v>
       </c>
       <c r="K316" s="8" t="n">
-        <v>17.37</v>
+        <v>17.09</v>
       </c>
       <c r="L316" s="9" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M316" s="8" t="n">
         <v>5.37</v>
@@ -20783,19 +20783,19 @@
         <v>1.84</v>
       </c>
       <c r="H317" s="12" t="n">
-        <v>36.97</v>
+        <v>36.38</v>
       </c>
       <c r="I317" s="12" t="n">
-        <v>-0.96</v>
+        <v>-0.47</v>
       </c>
       <c r="J317" s="12" t="n">
-        <v>29.72</v>
+        <v>29.24</v>
       </c>
       <c r="K317" s="12" t="n">
-        <v>5.79</v>
+        <v>5.7</v>
       </c>
       <c r="L317" s="13" t="n">
-        <v>2163</v>
+        <v>2129</v>
       </c>
       <c r="M317" s="12" t="n">
         <v>2.76</v>
@@ -20847,19 +20847,19 @@
         <v>1.37</v>
       </c>
       <c r="H318" s="4" t="n">
-        <v>75.5</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="I318" s="4" t="n">
-        <v>-1.8</v>
+        <v>0.79</v>
       </c>
       <c r="J318" s="4" t="n">
-        <v>23.26</v>
+        <v>23.13</v>
       </c>
       <c r="K318" s="4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>2931</v>
+        <v>2914</v>
       </c>
       <c r="M318" s="4" t="n">
         <v>6.61</v>
@@ -20911,13 +20911,13 @@
         <v>1.36</v>
       </c>
       <c r="H319" s="12" t="n">
-        <v>20.08</v>
+        <v>20.11</v>
       </c>
       <c r="I319" s="12" t="n">
-        <v>-0.99</v>
+        <v>0.75</v>
       </c>
       <c r="J319" s="12" t="n">
-        <v>30.67</v>
+        <v>30.72</v>
       </c>
       <c r="K319" s="12" t="n">
         <v>1.15</v>
@@ -20975,19 +20975,19 @@
         <v>1.23</v>
       </c>
       <c r="H320" s="8" t="n">
-        <v>10.3</v>
+        <v>10.09</v>
       </c>
       <c r="I320" s="8" t="n">
-        <v>0.49</v>
+        <v>-0.1</v>
       </c>
       <c r="J320" s="8" t="n">
-        <v>23.89</v>
+        <v>23.4</v>
       </c>
       <c r="K320" s="8" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="L320" s="9" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M320" s="8" t="n">
         <v>4.31</v>
@@ -21039,19 +21039,19 @@
         <v>1.07</v>
       </c>
       <c r="H321" s="12" t="n">
-        <v>11.75</v>
+        <v>11.5</v>
       </c>
       <c r="I321" s="12" t="n">
-        <v>-1.34</v>
+        <v>-0.26</v>
       </c>
       <c r="J321" s="12" t="n">
-        <v>17.65</v>
+        <v>17.27</v>
       </c>
       <c r="K321" s="12" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="L321" s="13" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M321" s="12" t="n">
         <v>3.45</v>
@@ -21103,19 +21103,19 @@
         <v>0.98</v>
       </c>
       <c r="H322" s="8" t="n">
-        <v>19.84</v>
+        <v>19.38</v>
       </c>
       <c r="I322" s="8" t="n">
-        <v>0.46</v>
+        <v>-0.67</v>
       </c>
       <c r="J322" s="8" t="n">
-        <v>24.51</v>
+        <v>23.94</v>
       </c>
       <c r="K322" s="8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="L322" s="9" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M322" s="8" t="n">
         <v>4.89</v>
@@ -21167,19 +21167,19 @@
         <v>0.85</v>
       </c>
       <c r="H323" s="12" t="n">
-        <v>54.02</v>
+        <v>53.58</v>
       </c>
       <c r="I323" s="12" t="n">
-        <v>-1.21</v>
+        <v>0.04</v>
       </c>
       <c r="J323" s="12" t="n">
-        <v>15.75</v>
+        <v>15.63</v>
       </c>
       <c r="K323" s="12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="L323" s="13" t="n">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="M323" s="12" t="n">
         <v>4.2</v>
@@ -21231,19 +21231,19 @@
         <v>0.75</v>
       </c>
       <c r="H324" s="8" t="n">
-        <v>14.83</v>
+        <v>14.17</v>
       </c>
       <c r="I324" s="8" t="n">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
       <c r="J324" s="8" t="n">
-        <v>21.14</v>
+        <v>20.2</v>
       </c>
       <c r="K324" s="8" t="n">
-        <v>3.79</v>
+        <v>3.62</v>
       </c>
       <c r="L324" s="9" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="M324" s="8" t="n">
         <v>3.63</v>
@@ -21295,19 +21295,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H325" s="12" t="n">
-        <v>12.13</v>
+        <v>12.05</v>
       </c>
       <c r="I325" s="12" t="n">
-        <v>-1.06</v>
+        <v>0.08</v>
       </c>
       <c r="J325" s="12" t="n">
-        <v>25.06</v>
+        <v>24.89</v>
       </c>
       <c r="K325" s="12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="L325" s="13" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M325" s="12" t="n">
         <v>1.59</v>
@@ -21359,16 +21359,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H326" s="8" t="n">
-        <v>85.11</v>
+        <v>85.17</v>
       </c>
       <c r="I326" s="8" t="n">
-        <v>-0.8</v>
+        <v>1.37</v>
       </c>
       <c r="J326" s="8" t="n">
-        <v>18.57</v>
+        <v>18.58</v>
       </c>
       <c r="K326" s="8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="L326" s="9" t="n">
         <v>284</v>
@@ -21423,19 +21423,19 @@
         <v>0.12</v>
       </c>
       <c r="H327" s="12" t="n">
-        <v>12.98</v>
+        <v>12.88</v>
       </c>
       <c r="I327" s="12" t="n">
-        <v>1.01</v>
+        <v>0.23</v>
       </c>
       <c r="J327" s="12" t="n">
-        <v>18.85</v>
+        <v>18.7</v>
       </c>
       <c r="K327" s="12" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="L327" s="13" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M327" s="12" t="n">
         <v>4.38</v>
@@ -21487,19 +21487,19 @@
         <v>0.11</v>
       </c>
       <c r="H328" s="8" t="n">
-        <v>19.07</v>
+        <v>18.92</v>
       </c>
       <c r="I328" s="8" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="J328" s="8" t="n">
-        <v>16.14</v>
+        <v>16.01</v>
       </c>
       <c r="K328" s="8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="L328" s="9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M328" s="8" t="n">
         <v>6.18</v>
@@ -21551,16 +21551,16 @@
         <v>0.08</v>
       </c>
       <c r="H329" s="12" t="n">
-        <v>10.71</v>
+        <v>10.65</v>
       </c>
       <c r="I329" s="12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="J329" s="12" t="n">
-        <v>19.6</v>
+        <v>19.49</v>
       </c>
       <c r="K329" s="12" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="L329" s="13" t="n">
         <v>48</v>
@@ -21615,19 +21615,19 @@
         <v>0</v>
       </c>
       <c r="H330" s="8" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="I330" s="8" t="n">
-        <v>-0.31</v>
+        <v>-0.95</v>
       </c>
       <c r="J330" s="8" t="n">
-        <v>14.79</v>
+        <v>14.51</v>
       </c>
       <c r="K330" s="8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="L330" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M330" s="8" t="n">
         <v>3.27</v>
